--- a/streams.xlsx
+++ b/streams.xlsx
@@ -1,27 +1,18 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20417"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Users\73415\Downloads\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C284D428-4603-4A02-B636-33946374EE7F}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
-  <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="21570" windowHeight="7185" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
-  </bookViews>
   <sheets>
-    <sheet name="2026" sheetId="1" r:id="rId1"/>
-    <sheet name="2025" sheetId="2" r:id="rId2"/>
+    <sheet state="visible" name="2026" sheetId="1" r:id="rId5"/>
+    <sheet state="visible" name="2025" sheetId="2" r:id="rId6"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <definedNames/>
+  <calcPr/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="188" uniqueCount="157">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="387" uniqueCount="305">
   <si>
     <t>id</t>
   </si>
@@ -47,21 +38,30 @@
     <t>【 生物名師】幽李鈴</t>
   </si>
   <si>
+    <t>【幽李鈴】將在12/20 21:00 初配信啦！💗</t>
+  </si>
+  <si>
     <t>https://www.youtube.com/watch?v=v0BAHTKUHho</t>
   </si>
   <si>
-    <t>【幽李鈴】將在12/20 21:00 初配信啦！💗</t>
-  </si>
-  <si>
     <t>https://www.youtube.com/watch?v=jd0h91vnRxU</t>
   </si>
   <si>
+    <t>前導</t>
+  </si>
+  <si>
     <t>Twitch</t>
   </si>
   <si>
     <t>1⧸1 115年 生物老師 幽李鈴 第八節</t>
   </si>
   <si>
+    <t>【一人捉迷藏】恐怖！直播片段丟失！？</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=y_6XDNwD-Ks</t>
+  </si>
+  <si>
     <t>【直播取消】感冒休養跟大家請個假！</t>
   </si>
   <si>
@@ -77,70 +77,76 @@
     <t>https://www.youtube.com/watch?v=dUhUhvbywD0</t>
   </si>
   <si>
-    <t>前導</t>
-  </si>
-  <si>
-    <t>【一人捉迷藏】恐怖！直播片段丟失！？</t>
-  </si>
-  <si>
-    <t>https://www.youtube.com/watch?v=y_6XDNwD-Ks</t>
+    <t>?????</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=BH_IHRUDy_Q</t>
   </si>
   <si>
     <t>直播異動, 連動</t>
   </si>
   <si>
+    <t>【神回】直擊！醫院幽靈失蹤事件！</t>
+  </si>
+  <si>
     <t>亞洛赫</t>
   </si>
   <si>
+    <t>https://www.youtube.com/watch?v=d0N94cT487Y</t>
+  </si>
+  <si>
     <t>大便糖速吃...我後悔了</t>
   </si>
   <si>
-    <t>?????</t>
-  </si>
-  <si>
-    <t>https://www.youtube.com/watch?v=BH_IHRUDy_Q</t>
-  </si>
-  <si>
     <t>https://www.youtube.com/watch?v=v_O4YV6wZtk</t>
   </si>
   <si>
-    <t>【神回】直擊！醫院幽靈失蹤事件！</t>
+    <t>【初配信】初次見面！！我是幽李鈴！！</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=Yp2QhS2g0tU</t>
   </si>
   <si>
     <t>QA, 棉花糖</t>
   </si>
   <si>
-    <t>https://www.youtube.com/watch?v=d0N94cT487Y</t>
-  </si>
-  <si>
     <t>【A/S/M/R】嗯哼～♡人家是新手～♡【 NO Sleep /Relax /Whispering】</t>
   </si>
   <si>
     <t>https://www.youtube.com/watch?v=Vp-lbw9r880</t>
   </si>
   <si>
+    <t>【後日談QA】治安不好的棉花糖很多呢各位</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=kiGVfQRxg5w</t>
+  </si>
+  <si>
     <t>ASMR</t>
   </si>
   <si>
-    <t>【初配信】初次見面！！我是幽李鈴！！</t>
-  </si>
-  <si>
-    <t>https://www.youtube.com/watch?v=Yp2QhS2g0tU</t>
-  </si>
-  <si>
     <t>【會員限定】秘密</t>
   </si>
   <si>
     <t>https://www.youtube.com/watch?v=KIAUz5M13wo</t>
   </si>
   <si>
+    <t>【聖誕初連動】非誠勿擾，今晚能不能配對成功？ft.亞洛赫</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=G9uRcuHZTdM</t>
+  </si>
+  <si>
+    <t>連動</t>
+  </si>
+  <si>
     <t>會限</t>
   </si>
   <si>
-    <t>【後日談QA】治安不好的棉花糖很多呢各位</t>
-  </si>
-  <si>
-    <t>https://www.youtube.com/watch?v=kiGVfQRxg5w</t>
+    <t>改成在圖奇開破防歌回！</t>
+  </si>
+  <si>
+    <t>https://x.com/U00Vtuber/status/2004465037411602451</t>
   </si>
   <si>
     <t>【觀眾CALL IN】 夾子音醫院聯賽</t>
@@ -149,10 +155,13 @@
     <t>https://www.youtube.com/watch?v=HunY1CF0ezs</t>
   </si>
   <si>
-    <t>【聖誕初連動】非誠勿擾，今晚能不能配對成功？ft.亞洛赫</t>
-  </si>
-  <si>
-    <t>https://www.youtube.com/watch?v=G9uRcuHZTdM</t>
+    <t>X, 歌回, Twitch</t>
+  </si>
+  <si>
+    <t>【收益化慶祝酒雜】今天跟大家喝到掛！！！🥂乾杯！！！</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=3wkLHKQ5Uqo</t>
   </si>
   <si>
     <t>Twitch, 觀眾CALL IN</t>
@@ -167,28 +176,31 @@
     <t>https://www.youtube.com/watch?v=0IHJxtZ_8XE</t>
   </si>
   <si>
-    <t>連動</t>
-  </si>
-  <si>
-    <t>改成在圖奇開破防歌回！</t>
-  </si>
-  <si>
-    <t>https://x.com/U00Vtuber/status/2004465037411602451</t>
+    <t>酒雜</t>
+  </si>
+  <si>
+    <t>【觀眾CALL IN】進DC還要面試真的假的啦！？</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=3VejobEf1WM</t>
+  </si>
+  <si>
+    <t>觀眾CALL IN</t>
+  </si>
+  <si>
+    <t>【會員限定】看沒看到的履歷！！順便跨年啦！！！</t>
   </si>
   <si>
     <t>手語讓觀眾猜出說甚麼才能宣傳新周邊！？(※禁止說話)</t>
   </si>
   <si>
+    <t>https://www.youtube.com/watch?v=7LmRg4qqk4M</t>
+  </si>
+  <si>
     <t>https://www.youtube.com/watch?v=HMSuYD7A6Pw</t>
   </si>
   <si>
-    <t>X, 歌回, Twitch</t>
-  </si>
-  <si>
-    <t>【收益化慶祝酒雜】今天跟大家喝到掛！！！🥂乾杯！！！</t>
-  </si>
-  <si>
-    <t>https://www.youtube.com/watch?v=3wkLHKQ5Uqo</t>
+    <t>會限, 直播異動</t>
   </si>
   <si>
     <t>【觀眾參加型】 賭神降臨</t>
@@ -197,15 +209,6 @@
     <t>https://www.youtube.com/watch?v=GOTc2xgBHq4</t>
   </si>
   <si>
-    <t>酒雜</t>
-  </si>
-  <si>
-    <t>【觀眾CALL IN】進DC還要面試真的假的啦！？</t>
-  </si>
-  <si>
-    <t>https://www.youtube.com/watch?v=3VejobEf1WM</t>
-  </si>
-  <si>
     <t>Twitch, 直播異動, 觀眾參加型</t>
   </si>
   <si>
@@ -218,15 +221,6 @@
     <t>https://www.youtube.com/watch?v=Q3ffqBot4OI</t>
   </si>
   <si>
-    <t>觀眾CALL IN</t>
-  </si>
-  <si>
-    <t>【會員限定】看沒看到的履歷！！順便跨年啦！！！</t>
-  </si>
-  <si>
-    <t>https://www.youtube.com/watch?v=7LmRg4qqk4M</t>
-  </si>
-  <si>
     <t>Twitch, 直播異動</t>
   </si>
   <si>
@@ -239,9 +233,6 @@
     <t>https://www.youtube.com/watch?v=_2WOcF57GSI</t>
   </si>
   <si>
-    <t>會限, 直播異動</t>
-  </si>
-  <si>
     <t>【歌回】唱唱幾首喜歡的新歌</t>
   </si>
   <si>
@@ -492,45 +483,478 @@
   </si>
   <si>
     <t>3⧸16 我不要我不要我不要</t>
+  </si>
+  <si>
+    <t>【護理師Ｖ】邀請到我的前同事(現役醫生)大坦白！</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=j08yhVNkPJk</t>
+  </si>
+  <si>
+    <t>醫護</t>
+  </si>
+  <si>
+    <t>3⧸17 輔助瞄準開到10的孬種來玩遊戲了</t>
+  </si>
+  <si>
+    <t>https://www.twitch.tv/videos/2724688348</t>
+  </si>
+  <si>
+    <t>【🏮夜屋營夜中🍻】今晚來認識新的大姊姊！！！Ft. ‪@NKStellaEleanor‬ ‪@u00_Vtuber‬</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=umw0QFbirxA</t>
+  </si>
+  <si>
+    <t>連動, 別人家, 酒雜</t>
+  </si>
+  <si>
+    <t>黑銀夜烏, 史黛菈 埃蕾諾亞</t>
+  </si>
+  <si>
+    <t>【夜間巡房】二次會！今天要跟大家喝到爛醉？</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=KZ3xKfe8D00</t>
+  </si>
+  <si>
+    <t>因為昨天嘔吐其實有點灼傷喉嚨 今天早上還是不要開好好休息喉嚨…！</t>
+  </si>
+  <si>
+    <t>https://x.com/U00Vtuber/status/2035860731317641712</t>
+  </si>
+  <si>
+    <t>3⧸23 今天玩托里大冒險，和帕蘿妮、U00、橘編一起玩~</t>
+  </si>
+  <si>
+    <t>https://www.twitch.tv/letizia0120/video/2729577832</t>
+  </si>
+  <si>
+    <t>Twitch, 連動, 別人家</t>
+  </si>
+  <si>
+    <t>蕾蒂希婭, 帕蘿妮, 橘攸奈</t>
+  </si>
+  <si>
+    <t>【我媽來了】爆料大會！跟媽咪坦誠相對，今天究竟能不能圓滿下播！？</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=OIGtRk6JVS8</t>
+  </si>
+  <si>
+    <t>主播開始做街頭藝人了</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=gQGomfHYcFs</t>
+  </si>
+  <si>
+    <t>3⧸27 我快過世了</t>
+  </si>
+  <si>
+    <t>【歌回】曾經喜歡的那些歌曲，你是曲中人了嗎？</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=fyhiArNSYlI</t>
+  </si>
+  <si>
+    <t>Twitch, 歌回</t>
+  </si>
+  <si>
+    <t>3⧸27 時間管理大師</t>
+  </si>
+  <si>
+    <t>【酒雜女子會】約了上次露營的夥伴們暢聊暢飲！┊音羽りる</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=0318qA4bi98</t>
+  </si>
+  <si>
+    <t>Lilou, 史黛菈 埃蕾諾亞, 庫路路</t>
+  </si>
+  <si>
+    <t>【會員限定】猜猜我要幹嘛</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=Ny8gfYGmcd8</t>
+  </si>
+  <si>
+    <t>今天人不太舒服 圖奇早安台改明天喔！</t>
+  </si>
+  <si>
+    <t>https://x.com/U00Vtuber/status/2038406965563646253</t>
+  </si>
+  <si>
+    <t>裡面根本沒在玩遊戲啊！！！！</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=tpAusymoJ5I</t>
+  </si>
+  <si>
+    <t>3⧸31 慶祝我獲得˙紫勾勾 接下來就是獲得天下</t>
+  </si>
+  <si>
+    <t>【公審Vtuber聊天室膩梗】不忍了‼聊天室「這幾句」真的超膩‼😡🔥 Ft.妮卡沃爾、Aoi、兔姬、幽李鈴【薬袋アルマ／VTuber】</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=wtUcVjU81D0</t>
+  </si>
+  <si>
+    <t>薬袋アルマ, 妮卡沃爾, Aoi Hinamori, 兔姬</t>
+  </si>
+  <si>
+    <t>【生日紀念】我要動起來啦！！！！</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=EzLcHd3jD9Y</t>
+  </si>
+  <si>
+    <t>【夜間巡房】生日當然要喝酒聊到早上！！！只要我還沒睡今天就是我生日</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=jJEbJhYUmpU</t>
+  </si>
+  <si>
+    <t>【神的選拔遊戲】這是一場神賜的晚宴，也是一場人性的審判 初賽第三場 偽善者的餐桌</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=BroGEqgKpT8</t>
+  </si>
+  <si>
+    <t>水羽 ほむら, 雪迎, 朔Sakuro, 宵Yoruno, 朧Oboro, 海克莉獅, 森森鈴蘭, 瑪格麗特 · 諾爾絲</t>
+  </si>
+  <si>
+    <t>【神的選拔遊戲】看不見的花色，躲不過的背叛—在信任與謊言的牢房裡，你敢相信誰？決賽 單人牢房</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=sF1e4ks119k</t>
+  </si>
+  <si>
+    <t>水羽 ほむら, 朔Sakuro, 宵Yoruno, 朧Oboro, 瓦西瓦瓦, 銀刻, 祈Iruni, 裴妮大姊姊, 鷗麥麥麥, 悠蜜</t>
+  </si>
+  <si>
+    <t>Vtuber下場令人不勝唏噓</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=N6VkENwF-Sg</t>
+  </si>
+  <si>
+    <t>4⧸6  你現在在嘲笑一個贏家</t>
+  </si>
+  <si>
+    <t>4⧸7 用自瞄10打這ˇ遊戲是我對觀眾的尊重</t>
+  </si>
+  <si>
+    <t>https://www.twitch.tv/videos/2742177120</t>
+  </si>
+  <si>
+    <t>【朋友夢想生活 試玩版】商業CP營業中</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=1hxdIF6Uiyw</t>
+  </si>
+  <si>
+    <t>4⧸8 商業CP營業中</t>
+  </si>
+  <si>
+    <t>【人生遊戲】人生重啟怎麼那麼難！財富自由就靠這回了😊 ft.‪@NKKururun‬、‪@NKStellaEleanor‬ 、 ‪@u00_Vtuber‬ 【 虎屋レイ / Vtuber 】</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=KeE97dFKUJs</t>
+  </si>
+  <si>
+    <t>虎屋レイ, 史黛菈 埃蕾諾亞, 庫路路</t>
+  </si>
+  <si>
+    <t>🔞頻道最黑暗的一天(安全模式會走光...)【櫻境物語x榨Ｏ病棟】</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=hquwVj_FQ4Y</t>
+  </si>
+  <si>
+    <t>工商</t>
+  </si>
+  <si>
+    <t>怎麼那麼多歌回阿</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=f8TplxOC-1Q</t>
+  </si>
+  <si>
+    <t>4⧸13 警報誤發 請勿那個</t>
+  </si>
+  <si>
+    <t>【災難公關】今天一定要洗刷社恐的名號 ft.很多人</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=br58_n6wpRY</t>
+  </si>
+  <si>
+    <t>亞洛赫, 洛可洛斯特, 黑銀夜烏, 灰妲, 貓祭, Aoi Hinamori, 希妮·亞里絲</t>
+  </si>
+  <si>
+    <t>4⧸14 今天一定要洗刷社恐的名號 ft.很多人 !周邊 !dc !yt</t>
+  </si>
+  <si>
+    <t>【奏摺】因為臣發現開刀前有點工作累積沒弄 今天將不會開台😍</t>
+  </si>
+  <si>
+    <t>https://x.com/U00Vtuber/status/2044390917717856295</t>
+  </si>
+  <si>
+    <t>【奏摺】還沒處理完 所以今天也容我消失一天🥹</t>
+  </si>
+  <si>
+    <t>https://x.com/U00Vtuber/status/2044743900985008505</t>
+  </si>
+  <si>
+    <t>我動刀了</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=YAttpmHJB0c</t>
+  </si>
+  <si>
+    <t>4⧸18 第一次開刀ㄌ</t>
+  </si>
+  <si>
+    <t>【生日企劃】今天連線邀請一拖拉庫人來幫我辦慶生派對｜諾鴉・奈菲墨｜</t>
+  </si>
+  <si>
+    <t>https://youtu.be/ndjtD3GVxtg?t=6782</t>
+  </si>
+  <si>
+    <t>別人家</t>
+  </si>
+  <si>
+    <t>諾鴉・奈菲墨</t>
+  </si>
+  <si>
+    <t>✧該誰說詞了#04✧我重生了，這一世我是一名火辣護士！！||希妮·亞里絲🤍SinnieAris✨ ‪@uchififi‬ ‪@u00_Vtuber‬ ‪@AoiHinamoriCh‬</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=57_XbTgSrs8</t>
+  </si>
+  <si>
+    <t>希妮·亞里絲, Aoi Hinamori, 羽芝扉扉</t>
+  </si>
+  <si>
+    <t>5⧸3 幽李鈴你在狗叫什麼 !手機殼 !官網</t>
+  </si>
+  <si>
+    <t>https://www.twitch.tv/videos/2762858494</t>
+  </si>
+  <si>
+    <t>【人生遊戲】跟新朋朋一起玩遊戲！重生之後我要做大女主 ft. 史黛菈、幽李鈴、Aoi【奇露琪露 Kirukiru】</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=GE9j9o3lQZQ</t>
+  </si>
+  <si>
+    <t>奇露琪露, 史黛菈 埃蕾諾亞, Aoi Hinamori</t>
+  </si>
+  <si>
+    <t>【通靈之戰】各方靈能者齊聚一堂，角逐最佳靈能者之位！ft.幽李鈴/真理果/羽芝扉扉/煌Kirali【瓦西瓦瓦 / Vaswawa】</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=5ORwZjOEgFU</t>
+  </si>
+  <si>
+    <t>瓦西瓦瓦, 真理果, 羽芝扉扉, 煌Kirali</t>
+  </si>
+  <si>
+    <t>5⧸23 #跑步接力歌回2 線上跑路 ｜ !手機殼 !官網 !DC</t>
+  </si>
+  <si>
+    <t>https://www.twitch.tv/videos/2778900185</t>
+  </si>
+  <si>
+    <t>Twitch, 歌回, 接力</t>
+  </si>
+  <si>
+    <t>【特別企劃】不准笑ASMR♡誰會先忍不住笑出來？【羽芝扉扉 Uchi Fifi】</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=ZlHAwVwidVQ</t>
+  </si>
+  <si>
+    <t>羽芝扉扉, 麵音白湯, 夢寐愛姆, 瓦西瓦瓦, 崎塔</t>
+  </si>
+  <si>
+    <t>6⧸10  出生到現在第一次打麻將 還幫遊戲配音 好羞恥我真的不敢聽 #天月麻雀 !手機殼 !官網</t>
+  </si>
+  <si>
+    <t>https://www.twitch.tv/videos/2793248277</t>
+  </si>
+  <si>
+    <t>Twitch, 工商</t>
+  </si>
+  <si>
+    <t>【會員限定】喝點小酒跟你們說說心裡話【幽李鈴／Uririn】</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=lU14OrwDTVM</t>
+  </si>
+  <si>
+    <t>會限, 酒雜</t>
+  </si>
+  <si>
+    <t>6⧸14  我將登基成為大王 !手機殼 !官網</t>
+  </si>
+  <si>
+    <t>https://www.twitch.tv/videos/2796370720</t>
+  </si>
+  <si>
+    <t>6⧸25  我非常憤怒我相當憤怒   !手機殼 !官網</t>
+  </si>
+  <si>
+    <t>https://www.twitch.tv/videos/2805004582</t>
+  </si>
+  <si>
+    <t>Twitch, 酒雜</t>
+  </si>
+  <si>
+    <t>【2026以聲傳豬系列★台V霹靂火】DIKA豚足姬 (·⚇·)❤️‍🔥我若是袂爽，我會送你一桶汽油、一支番仔火❤️‍🔥今仔日絕對是台灣上Hito ê 配信節目!!!</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=-Z9coQ4RyEE</t>
+  </si>
+  <si>
+    <t>DIKA豚足姬, 凌潮, 熙歌, 真理果, 伍一</t>
+  </si>
+  <si>
+    <t>消失兩個月，我...（養狗了）</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=feZ2gizB5C8</t>
+  </si>
+  <si>
+    <t>7⧸13  喔嗨喲學妹  !手機殼 !官網</t>
+  </si>
+  <si>
+    <t>https://www.twitch.tv/videos/2818713649</t>
+  </si>
+  <si>
+    <t>【會員限定】偷偷摸摸講秘密</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=PyCcTrwdr9Q</t>
+  </si>
+  <si>
+    <t>會限, 雜談, 歌回</t>
+  </si>
+  <si>
+    <t>📢直播異動通知📢 阿金吃了不該吃的東西 現在要緊急帶他去看醫生 考慮到回來可能還要觀察一下所以晚上台先取消🙏🙏</t>
+  </si>
+  <si>
+    <t>https://x.com/U00Vtuber/status/2078431711214571541</t>
+  </si>
+  <si>
+    <t>7⧸19 精神上支持閃電日本隊 經濟上支持西班牙隊  ｜ 一日賭徒 晚點看世界盃 !指令 !手機殼 !官網</t>
+  </si>
+  <si>
+    <t>https://www.twitch.tv/videos/2823869944</t>
+  </si>
+  <si>
+    <t>7⧸21 狗尿地毯還沒洗   !指令 !手機殼 !官網</t>
+  </si>
+  <si>
+    <t>https://www.twitch.tv/videos/2825431894</t>
+  </si>
+  <si>
+    <t>【嘻嘻哈哈通知】今天開始到7/31 我要出國啦！！！</t>
+  </si>
+  <si>
+    <t>https://x.com/U00Vtuber/status/2080840467936334254</t>
+  </si>
+  <si>
+    <t>X</t>
+  </si>
+  <si>
+    <t>【完蛋】出國喝醉不小心曝光...</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=nHnCx2NXl6E</t>
+  </si>
+  <si>
+    <t>【急】會員快來幫我想辦法【幽李鈴／Uririn】</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=0-ISidVOhoM</t>
+  </si>
+  <si>
+    <t>【七夕企劃】新詩x聲音演出，才子詩詠佳人戲，預告第二部！ | 🌙鯨諾whalefall🐋 | #whalefall #鯨諾</t>
+  </si>
+  <si>
+    <t>https://youtu.be/Z-_aXBF3Mhg?t=44</t>
+  </si>
+  <si>
+    <t>鯨諾</t>
+  </si>
+  <si>
+    <t>【對到眼20次】就當作新男友介紹給我媽【幽李鈴／Uririn】</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=icqz9tf0tkY</t>
+  </si>
+  <si>
+    <t>【公審】駭入觀眾電腦看裡面有什麼...！？【幽李鈴／Uririn】</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=muVj8LhiZ8E</t>
+  </si>
+  <si>
+    <t>【二週年新衣裝紀念合唱（下）】一生一次大合唱今天又要和V朋朋帶來哪些歌曲呢🔥🔥 | 知花Chika</t>
+  </si>
+  <si>
+    <t>https://youtu.be/bZn2uiXpNvE?t=13311</t>
+  </si>
+  <si>
+    <t>知花</t>
+  </si>
+  <si>
+    <t>🔞也許是跟各位最後一次見面...（沒有安全模式）</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=7_0pPSK_PFs</t>
+  </si>
+  <si>
+    <t>8⧸15 我在凶宅的第一天   !指令 !手機殼 !官網</t>
+  </si>
+  <si>
+    <t>https://www.twitch.tv/videos/2846934918</t>
+  </si>
+  <si>
+    <t>丟錢在西門町街頭...十萬訂閱才可以撿回來</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=hnMnC_Cqlyk</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <numFmts count="1">
-    <numFmt numFmtId="176" formatCode="m/d"/>
+    <numFmt numFmtId="164" formatCode="m/d"/>
   </numFmts>
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="4">
     <font>
-      <sz val="10"/>
+      <sz val="10.0"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="10"/>
       <color theme="1"/>
       <name val="Arial"/>
       <scheme val="minor"/>
     </font>
     <font>
       <u/>
-      <sz val="10"/>
       <color rgb="FF0000FF"/>
-      <name val="Arial"/>
     </font>
     <font>
-      <sz val="10"/>
       <color theme="1"/>
       <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <name val="Arial"/>
-      <family val="3"/>
-      <charset val="136"/>
-      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
@@ -538,43 +962,48 @@
       <patternFill patternType="none"/>
     </fill>
     <fill>
-      <patternFill patternType="gray125"/>
+      <patternFill patternType="lightGray"/>
     </fill>
   </fills>
   <borders count="1">
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
+    <border/>
   </borders>
   <cellStyleXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
   <cellXfs count="6">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="176" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="1" numFmtId="164" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+      <alignment readingOrder="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0" vertical="bottom"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment vertical="bottom"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="一般" xfId="0" builtinId="0"/>
+    <cellStyle xfId="0" name="Normal" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
 </file>
 
 <file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
@@ -582,7 +1011,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Sheets">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheets">
   <a:themeElements>
     <a:clrScheme name="Sheets">
       <a:dk1>
@@ -772,20 +1201,17 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
-  <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:G60"/>
-  <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -808,225 +1234,225 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="2">
       <c r="A2" s="1">
-        <v>12</v>
+        <v>12.0</v>
       </c>
       <c r="B2" s="2">
-        <v>46023</v>
+        <v>46023.0</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="3">
       <c r="A3" s="1">
-        <v>13</v>
+        <v>13.0</v>
       </c>
       <c r="B3" s="2">
-        <v>46025</v>
+        <v>46025.0</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="4">
       <c r="A4" s="1">
-        <v>14</v>
+        <v>14.0</v>
       </c>
       <c r="B4" s="2">
-        <v>46028</v>
+        <v>46028.0</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="5">
       <c r="A5" s="1">
-        <v>15</v>
+        <v>15.0</v>
       </c>
       <c r="B5" s="2">
-        <v>46030</v>
+        <v>46030.0</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="6">
       <c r="A6" s="1">
-        <v>16</v>
+        <v>16.0</v>
       </c>
       <c r="B6" s="2">
-        <v>46032</v>
+        <v>46032.0</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="7">
       <c r="A7" s="1">
-        <v>17</v>
+        <v>17.0</v>
       </c>
       <c r="B7" s="2">
-        <v>46035</v>
+        <v>46035.0</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="8">
       <c r="A8" s="1">
-        <v>18</v>
+        <v>18.0</v>
       </c>
       <c r="B8" s="2">
-        <v>46037</v>
+        <v>46037.0</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="9">
       <c r="A9" s="1">
-        <v>19</v>
+        <v>19.0</v>
       </c>
       <c r="B9" s="2">
-        <v>46039</v>
+        <v>46039.0</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="10">
       <c r="A10" s="1">
-        <v>20</v>
+        <v>20.0</v>
       </c>
       <c r="B10" s="2">
-        <v>46042</v>
+        <v>46042.0</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>51</v>
+        <v>59</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="11">
       <c r="A11" s="1">
-        <v>21</v>
+        <v>21.0</v>
       </c>
       <c r="B11" s="2">
-        <v>46044</v>
+        <v>46044.0</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>56</v>
+        <v>63</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>57</v>
+        <v>64</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="12">
       <c r="A12" s="1">
-        <v>22</v>
+        <v>22.0</v>
       </c>
       <c r="B12" s="2">
-        <v>46045</v>
+        <v>46045.0</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="13">
       <c r="A13" s="1">
-        <v>23</v>
+        <v>23.0</v>
       </c>
       <c r="B13" s="2">
-        <v>46047</v>
+        <v>46047.0</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.2">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="14">
       <c r="A14" s="1">
-        <v>24</v>
+        <v>24.0</v>
       </c>
       <c r="B14" s="2">
-        <v>46048</v>
+        <v>46048.0</v>
       </c>
       <c r="C14" s="1" t="s">
         <v>73</v>
@@ -1041,12 +1467,12 @@
         <v>76</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="15">
       <c r="A15" s="1">
-        <v>25</v>
+        <v>25.0</v>
       </c>
       <c r="B15" s="2">
-        <v>46052</v>
+        <v>46052.0</v>
       </c>
       <c r="C15" s="4" t="s">
         <v>77</v>
@@ -1055,15 +1481,15 @@
         <v>78</v>
       </c>
       <c r="E15" s="5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.2">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="16">
       <c r="A16" s="1">
-        <v>26</v>
+        <v>26.0</v>
       </c>
       <c r="B16" s="2">
-        <v>46053</v>
+        <v>46053.0</v>
       </c>
       <c r="C16" s="1" t="s">
         <v>79</v>
@@ -1081,12 +1507,12 @@
         <v>83</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="17">
       <c r="A17" s="1">
-        <v>27</v>
+        <v>27.0</v>
       </c>
       <c r="B17" s="2">
-        <v>46054</v>
+        <v>46054.0</v>
       </c>
       <c r="C17" s="1" t="s">
         <v>84</v>
@@ -1098,12 +1524,12 @@
         <v>86</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="18">
       <c r="A18" s="1">
-        <v>28</v>
+        <v>28.0</v>
       </c>
       <c r="B18" s="2">
-        <v>46055</v>
+        <v>46055.0</v>
       </c>
       <c r="C18" s="1" t="s">
         <v>87</v>
@@ -1112,18 +1538,18 @@
         <v>88</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G18" s="1" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="19">
       <c r="A19" s="1">
-        <v>29</v>
+        <v>29.0</v>
       </c>
       <c r="B19" s="2">
-        <v>46056</v>
+        <v>46056.0</v>
       </c>
       <c r="C19" s="1" t="s">
         <v>90</v>
@@ -1135,12 +1561,12 @@
         <v>92</v>
       </c>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="20">
       <c r="A20" s="1">
-        <v>30</v>
+        <v>30.0</v>
       </c>
       <c r="B20" s="2">
-        <v>46058</v>
+        <v>46058.0</v>
       </c>
       <c r="C20" s="1" t="s">
         <v>93</v>
@@ -1149,18 +1575,18 @@
         <v>94</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G20" s="1" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="21">
       <c r="A21" s="1">
-        <v>31</v>
+        <v>31.0</v>
       </c>
       <c r="B21" s="2">
-        <v>46060</v>
+        <v>46060.0</v>
       </c>
       <c r="C21" s="4" t="s">
         <v>96</v>
@@ -1169,15 +1595,15 @@
         <v>97</v>
       </c>
       <c r="E21" s="5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.2">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="22">
       <c r="A22" s="1">
-        <v>32</v>
+        <v>32.0</v>
       </c>
       <c r="B22" s="2">
-        <v>46062</v>
+        <v>46062.0</v>
       </c>
       <c r="C22" s="1" t="s">
         <v>98</v>
@@ -1186,18 +1612,18 @@
         <v>99</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G22" s="1" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="23">
       <c r="A23" s="1">
-        <v>33</v>
+        <v>33.0</v>
       </c>
       <c r="B23" s="2">
-        <v>46065</v>
+        <v>46065.0</v>
       </c>
       <c r="C23" s="4" t="s">
         <v>101</v>
@@ -1206,15 +1632,15 @@
         <v>102</v>
       </c>
       <c r="E23" s="5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.2">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="24">
       <c r="A24" s="1">
-        <v>34</v>
+        <v>34.0</v>
       </c>
       <c r="B24" s="2">
-        <v>46066</v>
+        <v>46066.0</v>
       </c>
       <c r="C24" s="1" t="s">
         <v>103</v>
@@ -1223,12 +1649,12 @@
         <v>104</v>
       </c>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="25">
       <c r="A25" s="1">
-        <v>35</v>
+        <v>35.0</v>
       </c>
       <c r="B25" s="2">
-        <v>46067</v>
+        <v>46067.0</v>
       </c>
       <c r="C25" s="1" t="s">
         <v>105</v>
@@ -1240,15 +1666,15 @@
         <v>107</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.2">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="26">
       <c r="A26" s="1">
-        <v>36</v>
+        <v>36.0</v>
       </c>
       <c r="B26" s="2">
-        <v>46068</v>
+        <v>46068.0</v>
       </c>
       <c r="C26" s="4" t="s">
         <v>108</v>
@@ -1257,15 +1683,15 @@
         <v>109</v>
       </c>
       <c r="E26" s="5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.2">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="27">
       <c r="A27" s="1">
-        <v>37</v>
+        <v>37.0</v>
       </c>
       <c r="B27" s="2">
-        <v>46069</v>
+        <v>46069.0</v>
       </c>
       <c r="C27" s="1" t="s">
         <v>110</v>
@@ -1274,18 +1700,18 @@
         <v>111</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G27" s="1" t="s">
         <v>112</v>
       </c>
     </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="28">
       <c r="A28" s="1">
-        <v>38</v>
+        <v>38.0</v>
       </c>
       <c r="B28" s="2">
-        <v>46069</v>
+        <v>46069.0</v>
       </c>
       <c r="C28" s="1" t="s">
         <v>113</v>
@@ -1297,12 +1723,12 @@
         <v>115</v>
       </c>
     </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="29">
       <c r="A29" s="1">
-        <v>39</v>
+        <v>39.0</v>
       </c>
       <c r="B29" s="2">
-        <v>46074</v>
+        <v>46074.0</v>
       </c>
       <c r="C29" s="1" t="s">
         <v>116</v>
@@ -1311,15 +1737,15 @@
         <v>117</v>
       </c>
       <c r="E29" s="5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.2">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="30">
       <c r="A30" s="1">
-        <v>40</v>
+        <v>40.0</v>
       </c>
       <c r="B30" s="2">
-        <v>46076</v>
+        <v>46076.0</v>
       </c>
       <c r="C30" s="1" t="s">
         <v>118</v>
@@ -1328,18 +1754,18 @@
         <v>119</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G30" s="1" t="s">
         <v>120</v>
       </c>
     </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="31">
       <c r="A31" s="1">
-        <v>41</v>
+        <v>41.0</v>
       </c>
       <c r="B31" s="2">
-        <v>46077</v>
+        <v>46077.0</v>
       </c>
       <c r="C31" s="1" t="s">
         <v>121</v>
@@ -1348,18 +1774,18 @@
         <v>122</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G31" s="1" t="s">
         <v>123</v>
       </c>
     </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="32">
       <c r="A32" s="1">
-        <v>42</v>
+        <v>42.0</v>
       </c>
       <c r="B32" s="2">
-        <v>46081</v>
+        <v>46081.0</v>
       </c>
       <c r="C32" s="1" t="s">
         <v>124</v>
@@ -1371,12 +1797,12 @@
         <v>126</v>
       </c>
     </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="33">
       <c r="A33" s="1">
-        <v>43</v>
+        <v>43.0</v>
       </c>
       <c r="B33" s="2">
-        <v>46083</v>
+        <v>46083.0</v>
       </c>
       <c r="C33" s="1" t="s">
         <v>127</v>
@@ -1391,12 +1817,12 @@
         <v>130</v>
       </c>
     </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="34">
       <c r="A34" s="1">
-        <v>44</v>
+        <v>44.0</v>
       </c>
       <c r="B34" s="2">
-        <v>46086</v>
+        <v>46086.0</v>
       </c>
       <c r="C34" s="1" t="s">
         <v>131</v>
@@ -1411,12 +1837,12 @@
         <v>134</v>
       </c>
     </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="35">
       <c r="A35" s="1">
-        <v>45</v>
+        <v>45.0</v>
       </c>
       <c r="B35" s="2">
-        <v>46088</v>
+        <v>46088.0</v>
       </c>
       <c r="C35" s="1" t="s">
         <v>135</v>
@@ -1431,12 +1857,12 @@
         <v>138</v>
       </c>
     </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="36">
       <c r="A36" s="1">
-        <v>46</v>
+        <v>46.0</v>
       </c>
       <c r="B36" s="2">
-        <v>46090</v>
+        <v>46090.0</v>
       </c>
       <c r="C36" s="1" t="s">
         <v>139</v>
@@ -1445,18 +1871,18 @@
         <v>140</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G36" s="1" t="s">
         <v>139</v>
       </c>
     </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="37">
       <c r="A37" s="1">
-        <v>47</v>
+        <v>47.0</v>
       </c>
       <c r="B37" s="2">
-        <v>46094</v>
+        <v>46094.0</v>
       </c>
       <c r="C37" s="1" t="s">
         <v>141</v>
@@ -1471,12 +1897,12 @@
         <v>143</v>
       </c>
     </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="38">
       <c r="A38" s="1">
-        <v>48</v>
+        <v>48.0</v>
       </c>
       <c r="B38" s="2">
-        <v>46094</v>
+        <v>46094.0</v>
       </c>
       <c r="C38" s="1" t="s">
         <v>144</v>
@@ -1485,18 +1911,18 @@
         <v>145</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G38" s="1" t="s">
         <v>146</v>
       </c>
     </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="39">
       <c r="A39" s="1">
-        <v>49</v>
+        <v>49.0</v>
       </c>
       <c r="B39" s="2">
-        <v>46095</v>
+        <v>46095.0</v>
       </c>
       <c r="C39" s="1" t="s">
         <v>147</v>
@@ -1508,12 +1934,12 @@
         <v>149</v>
       </c>
     </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="40">
       <c r="A40" s="1">
-        <v>50</v>
+        <v>50.0</v>
       </c>
       <c r="B40" s="2">
-        <v>46096</v>
+        <v>46096.0</v>
       </c>
       <c r="C40" s="1" t="s">
         <v>150</v>
@@ -1528,12 +1954,12 @@
         <v>153</v>
       </c>
     </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="41">
       <c r="A41" s="1">
-        <v>51</v>
+        <v>51.0</v>
       </c>
       <c r="B41" s="2">
-        <v>46097</v>
+        <v>46097.0</v>
       </c>
       <c r="C41" s="1" t="s">
         <v>154</v>
@@ -1548,159 +1974,1162 @@
         <v>156</v>
       </c>
     </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="42">
       <c r="A42" s="1">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.2">
+        <v>52.0</v>
+      </c>
+      <c r="B42" s="2">
+        <v>46097.0</v>
+      </c>
+      <c r="C42" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="D42" s="3" t="s">
+        <v>158</v>
+      </c>
+      <c r="E42" s="1" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="43">
       <c r="A43" s="1">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.2">
+        <v>53.0</v>
+      </c>
+      <c r="B43" s="2">
+        <v>46098.0</v>
+      </c>
+      <c r="C43" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="D43" s="3" t="s">
+        <v>161</v>
+      </c>
+      <c r="E43" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="G43" s="1" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="44">
       <c r="A44" s="1">
+        <v>54.0</v>
+      </c>
+      <c r="B44" s="2">
+        <v>46102.0</v>
+      </c>
+      <c r="C44" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="D44" s="3" t="s">
+        <v>163</v>
+      </c>
+      <c r="E44" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="F44" s="1" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="1">
+        <v>55.0</v>
+      </c>
+      <c r="B45" s="2">
+        <v>46103.0</v>
+      </c>
+      <c r="C45" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="D45" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="E45" s="1" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A45" s="1">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="46">
       <c r="A46" s="1">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.2">
+        <v>56.0</v>
+      </c>
+      <c r="B46" s="2">
+        <v>46104.0</v>
+      </c>
+      <c r="C46" s="1" t="s">
+        <v>168</v>
+      </c>
+      <c r="D46" s="3" t="s">
+        <v>169</v>
+      </c>
+      <c r="E46" s="5" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="47">
       <c r="A47" s="1">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="48" spans="1:7" x14ac:dyDescent="0.2">
+        <v>57.0</v>
+      </c>
+      <c r="B47" s="2">
+        <v>46104.0</v>
+      </c>
+      <c r="C47" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="D47" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="E47" s="1" t="s">
+        <v>172</v>
+      </c>
+      <c r="F47" s="1" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="48">
       <c r="A48" s="1">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="49" spans="1:1" x14ac:dyDescent="0.2">
+        <v>58.0</v>
+      </c>
+      <c r="B48" s="2">
+        <v>46106.0</v>
+      </c>
+      <c r="C48" s="1" t="s">
+        <v>174</v>
+      </c>
+      <c r="D48" s="3" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="49">
       <c r="A49" s="1">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="50" spans="1:1" x14ac:dyDescent="0.2">
+        <v>59.0</v>
+      </c>
+      <c r="B49" s="2">
+        <v>46108.0</v>
+      </c>
+      <c r="C49" s="1" t="s">
+        <v>176</v>
+      </c>
+      <c r="D49" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="E49" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="G49" s="1" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="50">
       <c r="A50" s="1">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="51" spans="1:1" x14ac:dyDescent="0.2">
+        <v>60.0</v>
+      </c>
+      <c r="B50" s="2">
+        <v>46108.0</v>
+      </c>
+      <c r="C50" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="D50" s="3" t="s">
+        <v>180</v>
+      </c>
+      <c r="E50" s="1" t="s">
+        <v>181</v>
+      </c>
+      <c r="G50" s="1" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="51">
       <c r="A51" s="1">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="52" spans="1:1" x14ac:dyDescent="0.2">
+        <v>61.0</v>
+      </c>
+      <c r="B51" s="2">
+        <v>46108.0</v>
+      </c>
+      <c r="C51" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="D51" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="E51" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="F51" s="1" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="52">
       <c r="A52" s="1">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="53" spans="1:1" x14ac:dyDescent="0.2">
+        <v>62.0</v>
+      </c>
+      <c r="B52" s="2">
+        <v>46109.0</v>
+      </c>
+      <c r="C52" s="1" t="s">
+        <v>186</v>
+      </c>
+      <c r="D52" s="3" t="s">
+        <v>187</v>
+      </c>
+      <c r="E52" s="1" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="53">
       <c r="A53" s="1">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="54" spans="1:1" x14ac:dyDescent="0.2">
+        <v>63.0</v>
+      </c>
+      <c r="B53" s="2">
+        <v>46111.0</v>
+      </c>
+      <c r="C53" s="1" t="s">
+        <v>188</v>
+      </c>
+      <c r="D53" s="3" t="s">
+        <v>189</v>
+      </c>
+      <c r="E53" s="5" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="54">
       <c r="A54" s="1">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="55" spans="1:1" x14ac:dyDescent="0.2">
+        <v>64.0</v>
+      </c>
+      <c r="B54" s="2">
+        <v>46112.0</v>
+      </c>
+      <c r="C54" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="D54" s="3" t="s">
+        <v>191</v>
+      </c>
+      <c r="E54" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="G54" s="1" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="55">
       <c r="A55" s="1">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="56" spans="1:1" x14ac:dyDescent="0.2">
+        <v>65.0</v>
+      </c>
+      <c r="B55" s="2">
+        <v>46112.0</v>
+      </c>
+      <c r="C55" s="1" t="s">
+        <v>193</v>
+      </c>
+      <c r="D55" s="3" t="s">
+        <v>194</v>
+      </c>
+      <c r="E55" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="F55" s="1" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="56">
       <c r="A56" s="1">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="57" spans="1:1" x14ac:dyDescent="0.2">
+        <v>66.0</v>
+      </c>
+      <c r="B56" s="2">
+        <v>46116.0</v>
+      </c>
+      <c r="C56" s="1" t="s">
+        <v>196</v>
+      </c>
+      <c r="D56" s="3" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="57">
       <c r="A57" s="1">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="58" spans="1:1" x14ac:dyDescent="0.2">
+        <v>67.0</v>
+      </c>
+      <c r="B57" s="2">
+        <v>46117.0</v>
+      </c>
+      <c r="C57" s="1" t="s">
+        <v>198</v>
+      </c>
+      <c r="D57" s="3" t="s">
+        <v>199</v>
+      </c>
+      <c r="E57" s="1" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="58">
       <c r="A58" s="1">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="59" spans="1:1" x14ac:dyDescent="0.2">
+        <v>68.0</v>
+      </c>
+      <c r="B58" s="2">
+        <v>46117.0</v>
+      </c>
+      <c r="C58" s="1" t="s">
+        <v>200</v>
+      </c>
+      <c r="D58" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="E58" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="F58" s="1" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="59">
       <c r="A59" s="1">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="60" spans="1:1" x14ac:dyDescent="0.2">
+        <v>69.0</v>
+      </c>
+      <c r="B59" s="2">
+        <v>46118.0</v>
+      </c>
+      <c r="C59" s="1" t="s">
+        <v>203</v>
+      </c>
+      <c r="D59" s="3" t="s">
+        <v>204</v>
+      </c>
+      <c r="E59" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="F59" s="1" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="60">
       <c r="A60" s="1">
-        <v>70</v>
+        <v>70.0</v>
+      </c>
+      <c r="B60" s="2">
+        <v>46118.0</v>
+      </c>
+      <c r="C60" s="1" t="s">
+        <v>206</v>
+      </c>
+      <c r="D60" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="E60" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="G60" s="1" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="1">
+        <v>71.0</v>
+      </c>
+      <c r="B61" s="2">
+        <v>46119.0</v>
+      </c>
+      <c r="C61" s="1" t="s">
+        <v>209</v>
+      </c>
+      <c r="D61" s="3" t="s">
+        <v>210</v>
+      </c>
+      <c r="E61" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="G61" s="1" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="1">
+        <v>72.0</v>
+      </c>
+      <c r="B62" s="2">
+        <v>46120.0</v>
+      </c>
+      <c r="C62" s="1" t="s">
+        <v>211</v>
+      </c>
+      <c r="D62" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="E62" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="F62" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="G62" s="1" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="1">
+        <v>73.0</v>
+      </c>
+      <c r="B63" s="2">
+        <v>46121.0</v>
+      </c>
+      <c r="C63" s="1" t="s">
+        <v>214</v>
+      </c>
+      <c r="D63" s="3" t="s">
+        <v>215</v>
+      </c>
+      <c r="E63" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="F63" s="1" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="1">
+        <v>74.0</v>
+      </c>
+      <c r="B64" s="2">
+        <v>46124.0</v>
+      </c>
+      <c r="C64" s="1" t="s">
+        <v>217</v>
+      </c>
+      <c r="D64" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="E64" s="1" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="1">
+        <v>75.0</v>
+      </c>
+      <c r="B65" s="2">
+        <v>46125.0</v>
+      </c>
+      <c r="C65" s="1" t="s">
+        <v>220</v>
+      </c>
+      <c r="D65" s="3" t="s">
+        <v>221</v>
+      </c>
+      <c r="E65" s="1" t="s">
+        <v>181</v>
+      </c>
+      <c r="G65" s="1" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="1">
+        <v>76.0</v>
+      </c>
+      <c r="B66" s="2">
+        <v>46126.0</v>
+      </c>
+      <c r="C66" s="1" t="s">
+        <v>223</v>
+      </c>
+      <c r="D66" s="3" t="s">
+        <v>224</v>
+      </c>
+      <c r="E66" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="F66" s="1" t="s">
+        <v>225</v>
+      </c>
+      <c r="G66" s="1" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="1">
+        <v>77.0</v>
+      </c>
+      <c r="B67" s="2">
+        <v>46127.0</v>
+      </c>
+      <c r="C67" s="1" t="s">
+        <v>227</v>
+      </c>
+      <c r="D67" s="3" t="s">
+        <v>228</v>
+      </c>
+      <c r="E67" s="5" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="1">
+        <v>78.0</v>
+      </c>
+      <c r="B68" s="2">
+        <v>46128.0</v>
+      </c>
+      <c r="C68" s="1" t="s">
+        <v>229</v>
+      </c>
+      <c r="D68" s="3" t="s">
+        <v>230</v>
+      </c>
+      <c r="E68" s="5" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="1">
+        <v>79.0</v>
+      </c>
+      <c r="B69" s="2">
+        <v>46130.0</v>
+      </c>
+      <c r="C69" s="1" t="s">
+        <v>231</v>
+      </c>
+      <c r="D69" s="3" t="s">
+        <v>232</v>
+      </c>
+      <c r="E69" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="G69" s="1" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="1">
+        <v>80.0</v>
+      </c>
+      <c r="B70" s="2">
+        <v>46139.0</v>
+      </c>
+      <c r="C70" s="1" t="s">
+        <v>234</v>
+      </c>
+      <c r="D70" s="3" t="s">
+        <v>235</v>
+      </c>
+      <c r="E70" s="1" t="s">
+        <v>236</v>
+      </c>
+      <c r="F70" s="1" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="1">
+        <v>81.0</v>
+      </c>
+      <c r="B71" s="2">
+        <v>46140.0</v>
+      </c>
+      <c r="C71" s="1" t="s">
+        <v>238</v>
+      </c>
+      <c r="D71" s="3" t="s">
+        <v>239</v>
+      </c>
+      <c r="E71" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="F71" s="1" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="1">
+        <v>82.0</v>
+      </c>
+      <c r="B72" s="2">
+        <v>46145.0</v>
+      </c>
+      <c r="C72" s="1" t="s">
+        <v>241</v>
+      </c>
+      <c r="D72" s="3" t="s">
+        <v>242</v>
+      </c>
+      <c r="E72" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="G72" s="1" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="1">
+        <v>83.0</v>
+      </c>
+      <c r="B73" s="2">
+        <v>46145.0</v>
+      </c>
+      <c r="C73" s="1" t="s">
+        <v>243</v>
+      </c>
+      <c r="D73" s="3" t="s">
+        <v>244</v>
+      </c>
+      <c r="E73" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="F73" s="1" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="1">
+        <v>84.0</v>
+      </c>
+      <c r="B74" s="2">
+        <v>46155.0</v>
+      </c>
+      <c r="C74" s="1" t="s">
+        <v>246</v>
+      </c>
+      <c r="D74" s="3" t="s">
+        <v>247</v>
+      </c>
+      <c r="E74" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="F74" s="1" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="1">
+        <v>85.0</v>
+      </c>
+      <c r="B75" s="2">
+        <v>46165.0</v>
+      </c>
+      <c r="C75" s="1" t="s">
+        <v>249</v>
+      </c>
+      <c r="D75" s="3" t="s">
+        <v>250</v>
+      </c>
+      <c r="E75" s="1" t="s">
+        <v>251</v>
+      </c>
+      <c r="G75" s="1" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="1">
+        <v>86.0</v>
+      </c>
+      <c r="B76" s="2">
+        <v>46178.0</v>
+      </c>
+      <c r="C76" s="1" t="s">
+        <v>252</v>
+      </c>
+      <c r="D76" s="3" t="s">
+        <v>253</v>
+      </c>
+      <c r="E76" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="F76" s="1" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="1">
+        <v>87.0</v>
+      </c>
+      <c r="B77" s="2">
+        <v>46183.0</v>
+      </c>
+      <c r="C77" s="1" t="s">
+        <v>255</v>
+      </c>
+      <c r="D77" s="3" t="s">
+        <v>256</v>
+      </c>
+      <c r="E77" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="G77" s="1" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="1">
+        <v>88.0</v>
+      </c>
+      <c r="B78" s="2">
+        <v>46184.0</v>
+      </c>
+      <c r="C78" s="1" t="s">
+        <v>258</v>
+      </c>
+      <c r="D78" s="3" t="s">
+        <v>259</v>
+      </c>
+      <c r="E78" s="1" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="1">
+        <v>89.0</v>
+      </c>
+      <c r="B79" s="2">
+        <v>46187.0</v>
+      </c>
+      <c r="C79" s="1" t="s">
+        <v>261</v>
+      </c>
+      <c r="D79" s="3" t="s">
+        <v>262</v>
+      </c>
+      <c r="E79" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="G79" s="1" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="1">
+        <v>90.0</v>
+      </c>
+      <c r="B80" s="2">
+        <v>46198.0</v>
+      </c>
+      <c r="C80" s="1" t="s">
+        <v>263</v>
+      </c>
+      <c r="D80" s="3" t="s">
+        <v>264</v>
+      </c>
+      <c r="E80" s="1" t="s">
+        <v>265</v>
+      </c>
+      <c r="G80" s="1" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="1">
+        <v>91.0</v>
+      </c>
+      <c r="B81" s="2">
+        <v>46199.0</v>
+      </c>
+      <c r="C81" s="1" t="s">
+        <v>266</v>
+      </c>
+      <c r="D81" s="3" t="s">
+        <v>267</v>
+      </c>
+      <c r="E81" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="F81" s="1" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="1">
+        <v>92.0</v>
+      </c>
+      <c r="B82" s="2">
+        <v>46215.0</v>
+      </c>
+      <c r="C82" s="1" t="s">
+        <v>269</v>
+      </c>
+      <c r="D82" s="3" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="1">
+        <v>93.0</v>
+      </c>
+      <c r="B83" s="2">
+        <v>46216.0</v>
+      </c>
+      <c r="C83" s="1" t="s">
+        <v>271</v>
+      </c>
+      <c r="D83" s="3" t="s">
+        <v>272</v>
+      </c>
+      <c r="E83" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="G83" s="1" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="1">
+        <v>94.0</v>
+      </c>
+      <c r="B84" s="2">
+        <v>46219.0</v>
+      </c>
+      <c r="C84" s="1" t="s">
+        <v>273</v>
+      </c>
+      <c r="D84" s="3" t="s">
+        <v>274</v>
+      </c>
+      <c r="E84" s="1" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="1">
+        <v>95.0</v>
+      </c>
+      <c r="B85" s="2">
+        <v>46221.0</v>
+      </c>
+      <c r="C85" s="1" t="s">
+        <v>276</v>
+      </c>
+      <c r="D85" s="3" t="s">
+        <v>277</v>
+      </c>
+      <c r="E85" s="5" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="1">
+        <v>96.0</v>
+      </c>
+      <c r="B86" s="2">
+        <v>46222.0</v>
+      </c>
+      <c r="C86" s="1" t="s">
+        <v>278</v>
+      </c>
+      <c r="D86" s="3" t="s">
+        <v>279</v>
+      </c>
+      <c r="E86" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="G86" s="1" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="1">
+        <v>97.0</v>
+      </c>
+      <c r="B87" s="2">
+        <v>46224.0</v>
+      </c>
+      <c r="C87" s="1" t="s">
+        <v>280</v>
+      </c>
+      <c r="D87" s="3" t="s">
+        <v>281</v>
+      </c>
+      <c r="E87" s="1" t="s">
+        <v>181</v>
+      </c>
+      <c r="G87" s="1" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="1">
+        <v>98.0</v>
+      </c>
+      <c r="B88" s="2">
+        <v>46228.0</v>
+      </c>
+      <c r="C88" s="1" t="s">
+        <v>282</v>
+      </c>
+      <c r="D88" s="3" t="s">
+        <v>283</v>
+      </c>
+      <c r="E88" s="1" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="1">
+        <v>99.0</v>
+      </c>
+      <c r="B89" s="2">
+        <v>46246.0</v>
+      </c>
+      <c r="C89" s="1" t="s">
+        <v>285</v>
+      </c>
+      <c r="D89" s="3" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="1">
+        <v>100.0</v>
+      </c>
+      <c r="B90" s="2">
+        <v>46246.0</v>
+      </c>
+      <c r="C90" s="1" t="s">
+        <v>287</v>
+      </c>
+      <c r="D90" s="3" t="s">
+        <v>288</v>
+      </c>
+      <c r="E90" s="1" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="1">
+        <v>101.0</v>
+      </c>
+      <c r="B91" s="2">
+        <v>46247.0</v>
+      </c>
+      <c r="C91" s="1" t="s">
+        <v>289</v>
+      </c>
+      <c r="D91" s="3" t="s">
+        <v>290</v>
+      </c>
+      <c r="E91" s="1" t="s">
+        <v>236</v>
+      </c>
+      <c r="F91" s="1" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="1">
+        <v>102.0</v>
+      </c>
+      <c r="B92" s="2">
+        <v>46247.0</v>
+      </c>
+      <c r="C92" s="1" t="s">
+        <v>292</v>
+      </c>
+      <c r="D92" s="3" t="s">
+        <v>293</v>
+      </c>
+      <c r="E92" s="1" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="1">
+        <v>103.0</v>
+      </c>
+      <c r="B93" s="2">
+        <v>46248.0</v>
+      </c>
+      <c r="C93" s="1" t="s">
+        <v>294</v>
+      </c>
+      <c r="D93" s="3" t="s">
+        <v>295</v>
+      </c>
+      <c r="E93" s="1" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="1">
+        <v>104.0</v>
+      </c>
+      <c r="B94" s="2">
+        <v>46248.0</v>
+      </c>
+      <c r="C94" s="1" t="s">
+        <v>296</v>
+      </c>
+      <c r="D94" s="3" t="s">
+        <v>297</v>
+      </c>
+      <c r="E94" s="1" t="s">
+        <v>236</v>
+      </c>
+      <c r="F94" s="1" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="1">
+        <v>105.0</v>
+      </c>
+      <c r="B95" s="2">
+        <v>46249.0</v>
+      </c>
+      <c r="C95" s="1" t="s">
+        <v>299</v>
+      </c>
+      <c r="D95" s="3" t="s">
+        <v>300</v>
+      </c>
+      <c r="E95" s="1" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="1">
+        <v>106.0</v>
+      </c>
+      <c r="B96" s="2">
+        <v>46249.0</v>
+      </c>
+      <c r="C96" s="1" t="s">
+        <v>301</v>
+      </c>
+      <c r="D96" s="3" t="s">
+        <v>302</v>
+      </c>
+      <c r="E96" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="G96" s="1" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="1">
+        <v>107.0</v>
+      </c>
+      <c r="B97" s="2">
+        <v>46250.0</v>
+      </c>
+      <c r="C97" s="1" t="s">
+        <v>303</v>
+      </c>
+      <c r="D97" s="3" t="s">
+        <v>304</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="4" type="noConversion"/>
   <hyperlinks>
-    <hyperlink ref="D2" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
-    <hyperlink ref="D3" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
-    <hyperlink ref="D4" r:id="rId3" xr:uid="{00000000-0004-0000-0000-000002000000}"/>
-    <hyperlink ref="D5" r:id="rId4" xr:uid="{00000000-0004-0000-0000-000003000000}"/>
-    <hyperlink ref="D6" r:id="rId5" xr:uid="{00000000-0004-0000-0000-000004000000}"/>
-    <hyperlink ref="D7" r:id="rId6" xr:uid="{00000000-0004-0000-0000-000005000000}"/>
-    <hyperlink ref="D8" r:id="rId7" xr:uid="{00000000-0004-0000-0000-000006000000}"/>
-    <hyperlink ref="D9" r:id="rId8" xr:uid="{00000000-0004-0000-0000-000007000000}"/>
-    <hyperlink ref="D10" r:id="rId9" xr:uid="{00000000-0004-0000-0000-000008000000}"/>
-    <hyperlink ref="D11" r:id="rId10" xr:uid="{00000000-0004-0000-0000-000009000000}"/>
-    <hyperlink ref="D12" r:id="rId11" xr:uid="{00000000-0004-0000-0000-00000A000000}"/>
-    <hyperlink ref="D13" r:id="rId12" xr:uid="{00000000-0004-0000-0000-00000B000000}"/>
-    <hyperlink ref="D14" r:id="rId13" xr:uid="{00000000-0004-0000-0000-00000C000000}"/>
-    <hyperlink ref="D15" r:id="rId14" xr:uid="{00000000-0004-0000-0000-00000D000000}"/>
-    <hyperlink ref="D16" r:id="rId15" xr:uid="{00000000-0004-0000-0000-00000E000000}"/>
-    <hyperlink ref="D17" r:id="rId16" xr:uid="{00000000-0004-0000-0000-00000F000000}"/>
-    <hyperlink ref="D18" r:id="rId17" xr:uid="{00000000-0004-0000-0000-000010000000}"/>
-    <hyperlink ref="D19" r:id="rId18" xr:uid="{00000000-0004-0000-0000-000011000000}"/>
-    <hyperlink ref="D20" r:id="rId19" xr:uid="{00000000-0004-0000-0000-000012000000}"/>
-    <hyperlink ref="D21" r:id="rId20" xr:uid="{00000000-0004-0000-0000-000013000000}"/>
-    <hyperlink ref="D22" r:id="rId21" xr:uid="{00000000-0004-0000-0000-000014000000}"/>
-    <hyperlink ref="D23" r:id="rId22" xr:uid="{00000000-0004-0000-0000-000015000000}"/>
-    <hyperlink ref="D24" r:id="rId23" xr:uid="{00000000-0004-0000-0000-000016000000}"/>
-    <hyperlink ref="D25" r:id="rId24" xr:uid="{00000000-0004-0000-0000-000017000000}"/>
-    <hyperlink ref="D26" r:id="rId25" xr:uid="{00000000-0004-0000-0000-000018000000}"/>
-    <hyperlink ref="D27" r:id="rId26" xr:uid="{00000000-0004-0000-0000-000019000000}"/>
-    <hyperlink ref="D28" r:id="rId27" xr:uid="{00000000-0004-0000-0000-00001A000000}"/>
-    <hyperlink ref="D29" r:id="rId28" xr:uid="{00000000-0004-0000-0000-00001B000000}"/>
-    <hyperlink ref="D30" r:id="rId29" xr:uid="{00000000-0004-0000-0000-00001C000000}"/>
-    <hyperlink ref="D31" r:id="rId30" xr:uid="{00000000-0004-0000-0000-00001D000000}"/>
-    <hyperlink ref="D32" r:id="rId31" xr:uid="{00000000-0004-0000-0000-00001E000000}"/>
-    <hyperlink ref="D33" r:id="rId32" xr:uid="{00000000-0004-0000-0000-00001F000000}"/>
-    <hyperlink ref="D34" r:id="rId33" xr:uid="{00000000-0004-0000-0000-000020000000}"/>
-    <hyperlink ref="D35" r:id="rId34" xr:uid="{00000000-0004-0000-0000-000021000000}"/>
-    <hyperlink ref="D36" r:id="rId35" xr:uid="{00000000-0004-0000-0000-000022000000}"/>
-    <hyperlink ref="D37" r:id="rId36" xr:uid="{00000000-0004-0000-0000-000023000000}"/>
-    <hyperlink ref="D38" r:id="rId37" xr:uid="{00000000-0004-0000-0000-000024000000}"/>
-    <hyperlink ref="D39" r:id="rId38" xr:uid="{00000000-0004-0000-0000-000025000000}"/>
-    <hyperlink ref="D40" r:id="rId39" xr:uid="{00000000-0004-0000-0000-000026000000}"/>
-    <hyperlink ref="D41" r:id="rId40" xr:uid="{00000000-0004-0000-0000-000027000000}"/>
+    <hyperlink r:id="rId1" ref="D2"/>
+    <hyperlink r:id="rId2" ref="D3"/>
+    <hyperlink r:id="rId3" ref="D4"/>
+    <hyperlink r:id="rId4" ref="D5"/>
+    <hyperlink r:id="rId5" ref="D6"/>
+    <hyperlink r:id="rId6" ref="D7"/>
+    <hyperlink r:id="rId7" ref="D8"/>
+    <hyperlink r:id="rId8" ref="D9"/>
+    <hyperlink r:id="rId9" ref="D10"/>
+    <hyperlink r:id="rId10" ref="D11"/>
+    <hyperlink r:id="rId11" ref="D12"/>
+    <hyperlink r:id="rId12" ref="D13"/>
+    <hyperlink r:id="rId13" ref="D14"/>
+    <hyperlink r:id="rId14" ref="D15"/>
+    <hyperlink r:id="rId15" ref="D16"/>
+    <hyperlink r:id="rId16" ref="D17"/>
+    <hyperlink r:id="rId17" ref="D18"/>
+    <hyperlink r:id="rId18" ref="D19"/>
+    <hyperlink r:id="rId19" ref="D20"/>
+    <hyperlink r:id="rId20" ref="D21"/>
+    <hyperlink r:id="rId21" ref="D22"/>
+    <hyperlink r:id="rId22" ref="D23"/>
+    <hyperlink r:id="rId23" ref="D24"/>
+    <hyperlink r:id="rId24" ref="D25"/>
+    <hyperlink r:id="rId25" ref="D26"/>
+    <hyperlink r:id="rId26" ref="D27"/>
+    <hyperlink r:id="rId27" ref="D28"/>
+    <hyperlink r:id="rId28" ref="D29"/>
+    <hyperlink r:id="rId29" ref="D30"/>
+    <hyperlink r:id="rId30" ref="D31"/>
+    <hyperlink r:id="rId31" ref="D32"/>
+    <hyperlink r:id="rId32" ref="D33"/>
+    <hyperlink r:id="rId33" ref="D34"/>
+    <hyperlink r:id="rId34" ref="D35"/>
+    <hyperlink r:id="rId35" ref="D36"/>
+    <hyperlink r:id="rId36" ref="D37"/>
+    <hyperlink r:id="rId37" ref="D38"/>
+    <hyperlink r:id="rId38" ref="D39"/>
+    <hyperlink r:id="rId39" ref="D40"/>
+    <hyperlink r:id="rId40" ref="D41"/>
+    <hyperlink r:id="rId41" ref="D42"/>
+    <hyperlink r:id="rId42" ref="D43"/>
+    <hyperlink r:id="rId43" ref="D44"/>
+    <hyperlink r:id="rId44" ref="D45"/>
+    <hyperlink r:id="rId45" ref="D46"/>
+    <hyperlink r:id="rId46" ref="D47"/>
+    <hyperlink r:id="rId47" ref="D48"/>
+    <hyperlink r:id="rId48" ref="D49"/>
+    <hyperlink r:id="rId49" ref="D50"/>
+    <hyperlink r:id="rId50" ref="D51"/>
+    <hyperlink r:id="rId51" ref="D52"/>
+    <hyperlink r:id="rId52" ref="D53"/>
+    <hyperlink r:id="rId53" ref="D54"/>
+    <hyperlink r:id="rId54" ref="D55"/>
+    <hyperlink r:id="rId55" ref="D56"/>
+    <hyperlink r:id="rId56" ref="D57"/>
+    <hyperlink r:id="rId57" ref="D58"/>
+    <hyperlink r:id="rId58" ref="D59"/>
+    <hyperlink r:id="rId59" ref="D60"/>
+    <hyperlink r:id="rId60" ref="D61"/>
+    <hyperlink r:id="rId61" ref="D62"/>
+    <hyperlink r:id="rId62" ref="D63"/>
+    <hyperlink r:id="rId63" ref="D64"/>
+    <hyperlink r:id="rId64" ref="D65"/>
+    <hyperlink r:id="rId65" ref="D66"/>
+    <hyperlink r:id="rId66" ref="D67"/>
+    <hyperlink r:id="rId67" ref="D68"/>
+    <hyperlink r:id="rId68" ref="D69"/>
+    <hyperlink r:id="rId69" ref="D70"/>
+    <hyperlink r:id="rId70" ref="D71"/>
+    <hyperlink r:id="rId71" ref="D72"/>
+    <hyperlink r:id="rId72" ref="D73"/>
+    <hyperlink r:id="rId73" ref="D74"/>
+    <hyperlink r:id="rId74" ref="D75"/>
+    <hyperlink r:id="rId75" ref="D76"/>
+    <hyperlink r:id="rId76" ref="D77"/>
+    <hyperlink r:id="rId77" ref="D78"/>
+    <hyperlink r:id="rId78" ref="D79"/>
+    <hyperlink r:id="rId79" ref="D80"/>
+    <hyperlink r:id="rId80" ref="D81"/>
+    <hyperlink r:id="rId81" ref="D82"/>
+    <hyperlink r:id="rId82" ref="D83"/>
+    <hyperlink r:id="rId83" ref="D84"/>
+    <hyperlink r:id="rId84" ref="D85"/>
+    <hyperlink r:id="rId85" ref="D86"/>
+    <hyperlink r:id="rId86" ref="D87"/>
+    <hyperlink r:id="rId87" ref="D88"/>
+    <hyperlink r:id="rId88" ref="D89"/>
+    <hyperlink r:id="rId89" ref="D90"/>
+    <hyperlink r:id="rId90" ref="D91"/>
+    <hyperlink r:id="rId91" ref="D92"/>
+    <hyperlink r:id="rId92" ref="D93"/>
+    <hyperlink r:id="rId93" ref="D94"/>
+    <hyperlink r:id="rId94" ref="D95"/>
+    <hyperlink r:id="rId95" ref="D96"/>
+    <hyperlink r:id="rId96" ref="D97"/>
   </hyperlinks>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId41"/>
+  <drawing r:id="rId97"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:G12"/>
-  <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1723,211 +3152,210 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="2">
       <c r="A2" s="1">
-        <v>1</v>
+        <v>1.0</v>
       </c>
       <c r="B2" s="2">
-        <v>46000</v>
+        <v>46000.0</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D2" s="3" t="s">
         <v>10</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="3">
       <c r="A3" s="1">
-        <v>2</v>
+        <v>2.0</v>
       </c>
       <c r="B3" s="2">
-        <v>46011</v>
+        <v>46011.0</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="4">
       <c r="A4" s="1">
-        <v>3</v>
+        <v>3.0</v>
       </c>
       <c r="B4" s="2">
-        <v>46011</v>
+        <v>46011.0</v>
       </c>
       <c r="C4" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1">
+        <v>4.0</v>
+      </c>
+      <c r="B5" s="2">
+        <v>46011.0</v>
+      </c>
+      <c r="C5" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="D4" s="3" t="s">
+      <c r="D5" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F5" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="E4" s="1" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A5" s="1">
-        <v>4</v>
-      </c>
-      <c r="B5" s="2">
-        <v>46011</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="D5" s="3" t="s">
+    </row>
+    <row r="6">
+      <c r="A6" s="1">
+        <v>5.0</v>
+      </c>
+      <c r="B6" s="2">
+        <v>46011.0</v>
+      </c>
+      <c r="C6" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="E5" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="F5" s="1" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A6" s="1">
-        <v>5</v>
-      </c>
-      <c r="B6" s="2">
-        <v>46011</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>33</v>
-      </c>
       <c r="D6" s="3" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1">
+        <v>6.0</v>
+      </c>
+      <c r="B7" s="2">
+        <v>46013.0</v>
+      </c>
+      <c r="C7" s="1" t="s">
         <v>34</v>
       </c>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A7" s="1">
-        <v>6</v>
-      </c>
-      <c r="B7" s="2">
-        <v>46013</v>
-      </c>
-      <c r="C7" s="1" t="s">
-        <v>38</v>
-      </c>
       <c r="D7" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1">
+        <v>7.0</v>
+      </c>
+      <c r="B8" s="2">
+        <v>46015.0</v>
+      </c>
+      <c r="C8" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="E7" s="1" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A8" s="1">
-        <v>7</v>
-      </c>
-      <c r="B8" s="2">
-        <v>46015</v>
-      </c>
-      <c r="C8" s="1" t="s">
-        <v>42</v>
-      </c>
       <c r="D8" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1">
+        <v>8.0</v>
+      </c>
+      <c r="B9" s="2">
+        <v>46017.0</v>
+      </c>
+      <c r="C9" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="E8" s="1" t="s">
+      <c r="D9" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1">
+        <v>9.0</v>
+      </c>
+      <c r="B10" s="2">
+        <v>46019.0</v>
+      </c>
+      <c r="C10" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="F8" s="1" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A9" s="1">
-        <v>8</v>
-      </c>
-      <c r="B9" s="2">
-        <v>46017</v>
-      </c>
-      <c r="C9" s="1" t="s">
+      <c r="D10" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="D9" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="E9" s="1" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A10" s="1">
-        <v>9</v>
-      </c>
-      <c r="B10" s="2">
-        <v>46019</v>
-      </c>
-      <c r="C10" s="1" t="s">
+      <c r="E10" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="D10" s="3" t="s">
+    </row>
+    <row r="11">
+      <c r="A11" s="1">
+        <v>10.0</v>
+      </c>
+      <c r="B11" s="2">
+        <v>46021.0</v>
+      </c>
+      <c r="C11" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="E10" s="1" t="s">
+      <c r="D11" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="E11" s="1" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1">
+        <v>11.0</v>
+      </c>
+      <c r="B12" s="2">
+        <v>46022.0</v>
+      </c>
+      <c r="C12" s="1" t="s">
         <v>58</v>
       </c>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A11" s="1">
-        <v>10</v>
-      </c>
-      <c r="B11" s="2">
-        <v>46021</v>
-      </c>
-      <c r="C11" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="D11" s="3" t="s">
+      <c r="D12" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="E11" s="1" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A12" s="1">
-        <v>11</v>
-      </c>
-      <c r="B12" s="2">
-        <v>46022</v>
-      </c>
-      <c r="C12" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="D12" s="3" t="s">
-        <v>67</v>
-      </c>
       <c r="E12" s="1" t="s">
-        <v>72</v>
+        <v>62</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="4" type="noConversion"/>
   <hyperlinks>
-    <hyperlink ref="D2" r:id="rId1" xr:uid="{00000000-0004-0000-0100-000000000000}"/>
-    <hyperlink ref="D3" r:id="rId2" xr:uid="{00000000-0004-0000-0100-000001000000}"/>
-    <hyperlink ref="D4" r:id="rId3" xr:uid="{00000000-0004-0000-0100-000002000000}"/>
-    <hyperlink ref="D5" r:id="rId4" xr:uid="{00000000-0004-0000-0100-000003000000}"/>
-    <hyperlink ref="D6" r:id="rId5" xr:uid="{00000000-0004-0000-0100-000004000000}"/>
-    <hyperlink ref="D7" r:id="rId6" xr:uid="{00000000-0004-0000-0100-000005000000}"/>
-    <hyperlink ref="D8" r:id="rId7" xr:uid="{00000000-0004-0000-0100-000006000000}"/>
-    <hyperlink ref="D9" r:id="rId8" xr:uid="{00000000-0004-0000-0100-000007000000}"/>
-    <hyperlink ref="D10" r:id="rId9" xr:uid="{00000000-0004-0000-0100-000008000000}"/>
-    <hyperlink ref="D11" r:id="rId10" xr:uid="{00000000-0004-0000-0100-000009000000}"/>
-    <hyperlink ref="D12" r:id="rId11" xr:uid="{00000000-0004-0000-0100-00000A000000}"/>
+    <hyperlink r:id="rId1" ref="D2"/>
+    <hyperlink r:id="rId2" ref="D3"/>
+    <hyperlink r:id="rId3" ref="D4"/>
+    <hyperlink r:id="rId4" ref="D5"/>
+    <hyperlink r:id="rId5" ref="D6"/>
+    <hyperlink r:id="rId6" ref="D7"/>
+    <hyperlink r:id="rId7" ref="D8"/>
+    <hyperlink r:id="rId8" ref="D9"/>
+    <hyperlink r:id="rId9" ref="D10"/>
+    <hyperlink r:id="rId10" ref="D11"/>
+    <hyperlink r:id="rId11" ref="D12"/>
   </hyperlinks>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId12"/>
 </worksheet>
 </file>
--- a/streams.xlsx
+++ b/streams.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="387" uniqueCount="305">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="480" uniqueCount="388">
   <si>
     <t>id</t>
   </si>
@@ -35,39 +35,45 @@
     <t>note</t>
   </si>
   <si>
+    <t>【幽李鈴】將在12/20 21:00 初配信啦！💗</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=jd0h91vnRxU</t>
+  </si>
+  <si>
     <t>【 生物名師】幽李鈴</t>
   </si>
   <si>
-    <t>【幽李鈴】將在12/20 21:00 初配信啦！💗</t>
-  </si>
-  <si>
     <t>https://www.youtube.com/watch?v=v0BAHTKUHho</t>
   </si>
   <si>
-    <t>https://www.youtube.com/watch?v=jd0h91vnRxU</t>
-  </si>
-  <si>
     <t>前導</t>
   </si>
   <si>
+    <t>【一人捉迷藏】恐怖！直播片段丟失！？</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=y_6XDNwD-Ks</t>
+  </si>
+  <si>
     <t>Twitch</t>
   </si>
   <si>
     <t>1⧸1 115年 生物老師 幽李鈴 第八節</t>
   </si>
   <si>
-    <t>【一人捉迷藏】恐怖！直播片段丟失！？</t>
-  </si>
-  <si>
-    <t>https://www.youtube.com/watch?v=y_6XDNwD-Ks</t>
-  </si>
-  <si>
     <t>【直播取消】感冒休養跟大家請個假！</t>
   </si>
   <si>
     <t>https://x.com/U00Vtuber/status/2007422926228689379</t>
   </si>
   <si>
+    <t>?????</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=BH_IHRUDy_Q</t>
+  </si>
+  <si>
     <t>X, 直播異動</t>
   </si>
   <si>
@@ -77,24 +83,18 @@
     <t>https://www.youtube.com/watch?v=dUhUhvbywD0</t>
   </si>
   <si>
-    <t>?????</t>
-  </si>
-  <si>
-    <t>https://www.youtube.com/watch?v=BH_IHRUDy_Q</t>
+    <t>【神回】直擊！醫院幽靈失蹤事件！</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=d0N94cT487Y</t>
   </si>
   <si>
     <t>直播異動, 連動</t>
   </si>
   <si>
-    <t>【神回】直擊！醫院幽靈失蹤事件！</t>
-  </si>
-  <si>
     <t>亞洛赫</t>
   </si>
   <si>
-    <t>https://www.youtube.com/watch?v=d0N94cT487Y</t>
-  </si>
-  <si>
     <t>大便糖速吃...我後悔了</t>
   </si>
   <si>
@@ -122,46 +122,55 @@
     <t>https://www.youtube.com/watch?v=kiGVfQRxg5w</t>
   </si>
   <si>
+    <t>【聖誕初連動】非誠勿擾，今晚能不能配對成功？ft.亞洛赫</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=G9uRcuHZTdM</t>
+  </si>
+  <si>
     <t>ASMR</t>
   </si>
   <si>
     <t>【會員限定】秘密</t>
   </si>
   <si>
+    <t>連動</t>
+  </si>
+  <si>
     <t>https://www.youtube.com/watch?v=KIAUz5M13wo</t>
   </si>
   <si>
-    <t>【聖誕初連動】非誠勿擾，今晚能不能配對成功？ft.亞洛赫</t>
-  </si>
-  <si>
-    <t>https://www.youtube.com/watch?v=G9uRcuHZTdM</t>
-  </si>
-  <si>
-    <t>連動</t>
+    <t>改成在圖奇開破防歌回！</t>
+  </si>
+  <si>
+    <t>https://x.com/U00Vtuber/status/2004465037411602451</t>
+  </si>
+  <si>
+    <t>X, 歌回, Twitch</t>
+  </si>
+  <si>
+    <t>【收益化慶祝酒雜】今天跟大家喝到掛！！！🥂乾杯！！！</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=3wkLHKQ5Uqo</t>
   </si>
   <si>
     <t>會限</t>
   </si>
   <si>
-    <t>改成在圖奇開破防歌回！</t>
-  </si>
-  <si>
-    <t>https://x.com/U00Vtuber/status/2004465037411602451</t>
-  </si>
-  <si>
     <t>【觀眾CALL IN】 夾子音醫院聯賽</t>
   </si>
   <si>
     <t>https://www.youtube.com/watch?v=HunY1CF0ezs</t>
   </si>
   <si>
-    <t>X, 歌回, Twitch</t>
-  </si>
-  <si>
-    <t>【收益化慶祝酒雜】今天跟大家喝到掛！！！🥂乾杯！！！</t>
-  </si>
-  <si>
-    <t>https://www.youtube.com/watch?v=3wkLHKQ5Uqo</t>
+    <t>酒雜</t>
+  </si>
+  <si>
+    <t>【觀眾CALL IN】進DC還要面試真的假的啦！？</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=3VejobEf1WM</t>
   </si>
   <si>
     <t>Twitch, 觀眾CALL IN</t>
@@ -176,33 +185,24 @@
     <t>https://www.youtube.com/watch?v=0IHJxtZ_8XE</t>
   </si>
   <si>
-    <t>酒雜</t>
-  </si>
-  <si>
-    <t>【觀眾CALL IN】進DC還要面試真的假的啦！？</t>
-  </si>
-  <si>
-    <t>https://www.youtube.com/watch?v=3VejobEf1WM</t>
-  </si>
-  <si>
     <t>觀眾CALL IN</t>
   </si>
   <si>
     <t>【會員限定】看沒看到的履歷！！順便跨年啦！！！</t>
   </si>
   <si>
+    <t>https://www.youtube.com/watch?v=7LmRg4qqk4M</t>
+  </si>
+  <si>
+    <t>會限, 直播異動</t>
+  </si>
+  <si>
     <t>手語讓觀眾猜出說甚麼才能宣傳新周邊！？(※禁止說話)</t>
   </si>
   <si>
-    <t>https://www.youtube.com/watch?v=7LmRg4qqk4M</t>
-  </si>
-  <si>
     <t>https://www.youtube.com/watch?v=HMSuYD7A6Pw</t>
   </si>
   <si>
-    <t>會限, 直播異動</t>
-  </si>
-  <si>
     <t>【觀眾參加型】 賭神降臨</t>
   </si>
   <si>
@@ -431,12 +431,15 @@
     <t>3⧸7 我遺失了重要的東西...</t>
   </si>
   <si>
+    <t>3/9 先等下載 晚點開始自虐</t>
+  </si>
+  <si>
+    <t>https://www.twitch.tv/videos/2717539963</t>
+  </si>
+  <si>
     <t>3⧸9 先等下載 晚點開始自虐</t>
   </si>
   <si>
-    <t>https://www.twitch.tv/videos/2717539963</t>
-  </si>
-  <si>
     <t>【銳評討論】Vtuber不該做的25件事情，真督假督？ ft.‪@u00_Vtuber‬ /幽李鈴【蕾蒂希婭 Letizia】</t>
   </si>
   <si>
@@ -491,15 +494,18 @@
     <t>https://www.youtube.com/watch?v=j08yhVNkPJk</t>
   </si>
   <si>
-    <t>醫護</t>
+    <t>醫護, QA</t>
+  </si>
+  <si>
+    <t>3/17 輔助瞄準開到10的孬種來玩遊戲了</t>
+  </si>
+  <si>
+    <t>https://www.twitch.tv/videos/2724688348</t>
   </si>
   <si>
     <t>3⧸17 輔助瞄準開到10的孬種來玩遊戲了</t>
   </si>
   <si>
-    <t>https://www.twitch.tv/videos/2724688348</t>
-  </si>
-  <si>
     <t>【🏮夜屋營夜中🍻】今晚來認識新的大姊姊！！！Ft. ‪@NKStellaEleanor‬ ‪@u00_Vtuber‬</t>
   </si>
   <si>
@@ -524,7 +530,7 @@
     <t>https://x.com/U00Vtuber/status/2035860731317641712</t>
   </si>
   <si>
-    <t>3⧸23 今天玩托里大冒險，和帕蘿妮、U00、橘編一起玩~</t>
+    <t>3/23 今天玩托里大冒險，和帕蘿妮、U00、橘編一起玩~</t>
   </si>
   <si>
     <t>https://www.twitch.tv/letizia0120/video/2729577832</t>
@@ -641,12 +647,15 @@
     <t>4⧸6  你現在在嘲笑一個贏家</t>
   </si>
   <si>
+    <t>4/7 用自瞄10打這ˇ遊戲是我對觀眾的尊重</t>
+  </si>
+  <si>
+    <t>https://www.twitch.tv/videos/2742177120</t>
+  </si>
+  <si>
     <t>4⧸7 用自瞄10打這ˇ遊戲是我對觀眾的尊重</t>
   </si>
   <si>
-    <t>https://www.twitch.tv/videos/2742177120</t>
-  </si>
-  <si>
     <t>【朋友夢想生活 試玩版】商業CP營業中</t>
   </si>
   <si>
@@ -722,171 +731,198 @@
     <t>https://youtu.be/ndjtD3GVxtg?t=6782</t>
   </si>
   <si>
+    <t>別人家, 歌回</t>
+  </si>
+  <si>
+    <t>諾鴉・奈菲墨</t>
+  </si>
+  <si>
+    <t>✧該誰說詞了#04✧我重生了，這一世我是一名火辣護士！！||希妮·亞里絲🤍SinnieAris✨ ‪@uchififi‬ ‪@u00_Vtuber‬ ‪@AoiHinamoriCh‬</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=57_XbTgSrs8</t>
+  </si>
+  <si>
+    <t>希妮·亞里絲, Aoi Hinamori, 羽芝扉扉</t>
+  </si>
+  <si>
+    <t>5/3 幽李鈴你在狗叫什麼 !手機殼 !官網</t>
+  </si>
+  <si>
+    <t>https://www.twitch.tv/videos/2762858494</t>
+  </si>
+  <si>
+    <t>5⧸3 幽李鈴你在狗叫什麼 !手機殼 !官網</t>
+  </si>
+  <si>
+    <t>【人生遊戲】跟新朋朋一起玩遊戲！重生之後我要做大女主 ft. 史黛菈、幽李鈴、Aoi【奇露琪露 Kirukiru】</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=GE9j9o3lQZQ</t>
+  </si>
+  <si>
+    <t>奇露琪露, 史黛菈 埃蕾諾亞, Aoi Hinamori</t>
+  </si>
+  <si>
+    <t>【通靈之戰】各方靈能者齊聚一堂，角逐最佳靈能者之位！ft.幽李鈴/真理果/羽芝扉扉/煌Kirali【瓦西瓦瓦 / Vaswawa】</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=5ORwZjOEgFU</t>
+  </si>
+  <si>
+    <t>瓦西瓦瓦, 真理果, 羽芝扉扉, 煌Kirali</t>
+  </si>
+  <si>
+    <t>5/23 #跑步接力歌回2 線上跑路 ｜ !手機殼 !官網 !DC</t>
+  </si>
+  <si>
+    <t>https://www.twitch.tv/videos/2778900185</t>
+  </si>
+  <si>
+    <t>Twitch, 歌回, 接力</t>
+  </si>
+  <si>
+    <t>5⧸23 #跑步接力歌回2 線上跑路 ｜ !手機殼 !官網 !DC</t>
+  </si>
+  <si>
+    <t>【特別企劃】不准笑ASMR♡誰會先忍不住笑出來？【羽芝扉扉 Uchi Fifi】</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=ZlHAwVwidVQ</t>
+  </si>
+  <si>
+    <t>羽芝扉扉, 麵音白湯, 夢寐愛姆, 瓦西瓦瓦, 崎塔</t>
+  </si>
+  <si>
+    <t>6/10  出生到現在第一次打麻將 還幫遊戲配音 好羞恥我真的不敢聽 #天月麻雀 !手機殼 !官網</t>
+  </si>
+  <si>
+    <t>https://www.twitch.tv/videos/2793248277</t>
+  </si>
+  <si>
+    <t>Twitch, 工商</t>
+  </si>
+  <si>
+    <t>6⧸10  出生到現在第一次打麻將 還幫遊戲配音 好羞恥我真的不敢聽 #天月麻雀 !手機殼 !官網</t>
+  </si>
+  <si>
+    <t>【會員限定】喝點小酒跟你們說說心裡話【幽李鈴／Uririn】</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=lU14OrwDTVM</t>
+  </si>
+  <si>
+    <t>會限, 酒雜</t>
+  </si>
+  <si>
+    <t>6/14  我將登基成為大王 !手機殼 !官網</t>
+  </si>
+  <si>
+    <t>https://www.twitch.tv/videos/2796370720</t>
+  </si>
+  <si>
+    <t>6⧸14  我將登基成為大王 !手機殼 !官網</t>
+  </si>
+  <si>
+    <t>6/25  我非常憤怒我相當憤怒   !手機殼 !官網</t>
+  </si>
+  <si>
+    <t>https://www.twitch.tv/videos/2805004582</t>
+  </si>
+  <si>
+    <t>Twitch, 酒雜</t>
+  </si>
+  <si>
+    <t>6⧸25  我非常憤怒我相當憤怒   !手機殼 !官網</t>
+  </si>
+  <si>
+    <t>【2026以聲傳豬系列★台V霹靂火】DIKA豚足姬 (·⚇·)❤️‍🔥我若是袂爽，我會送你一桶汽油、一支番仔火❤️‍🔥今仔日絕對是台灣上Hito ê 配信節目!!!</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=-Z9coQ4RyEE</t>
+  </si>
+  <si>
+    <t>DIKA豚足姬, 凌潮, 熙歌, 真理果, 伍一</t>
+  </si>
+  <si>
+    <t>消失兩個月，我...（養狗了）</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=feZ2gizB5C8</t>
+  </si>
+  <si>
+    <t>7/13  喔嗨喲學妹  !手機殼 !官網</t>
+  </si>
+  <si>
+    <t>https://www.twitch.tv/videos/2818713649</t>
+  </si>
+  <si>
+    <t>7⧸13  喔嗨喲學妹  !手機殼 !官網</t>
+  </si>
+  <si>
+    <t>【會員限定】偷偷摸摸講秘密</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=PyCcTrwdr9Q</t>
+  </si>
+  <si>
+    <t>會限, 雜談, 歌回</t>
+  </si>
+  <si>
+    <t>📢直播異動通知📢 阿金吃了不該吃的東西 現在要緊急帶他去看醫生 考慮到回來可能還要觀察一下所以晚上台先取消🙏🙏</t>
+  </si>
+  <si>
+    <t>https://x.com/U00Vtuber/status/2078431711214571541</t>
+  </si>
+  <si>
+    <t>7/19 精神上支持閃電日本隊 經濟上支持西班牙隊  ｜ 一日賭徒 晚點看世界盃 !指令 !手機殼 !官網</t>
+  </si>
+  <si>
+    <t>https://www.twitch.tv/videos/2823869944</t>
+  </si>
+  <si>
+    <t>7⧸19 精神上支持閃電日本隊 經濟上支持西班牙隊  ｜ 一日賭徒 晚點看世界盃 !指令 !手機殼 !官網</t>
+  </si>
+  <si>
+    <t>7/21 狗尿地毯還沒洗   !指令 !手機殼 !官網</t>
+  </si>
+  <si>
+    <t>https://www.twitch.tv/videos/2825431894</t>
+  </si>
+  <si>
+    <t>7⧸21 狗尿地毯還沒洗   !指令 !手機殼 !官網</t>
+  </si>
+  <si>
+    <t>【嘻嘻哈哈通知】今天開始到7/31 我要出國啦！！！</t>
+  </si>
+  <si>
+    <t>https://x.com/U00Vtuber/status/2080840467936334254</t>
+  </si>
+  <si>
+    <t>X</t>
+  </si>
+  <si>
+    <t>【完蛋】出國喝醉不小心曝光...</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=nHnCx2NXl6E</t>
+  </si>
+  <si>
+    <t>【急】會員快來幫我想辦法【幽李鈴／Uririn】</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=0-ISidVOhoM</t>
+  </si>
+  <si>
+    <t>【七夕企劃】新詩x聲音演出，才子詩詠佳人戲，預告第二部！ | 🌙鯨諾whalefall🐋 | #whalefall #鯨諾</t>
+  </si>
+  <si>
+    <t>https://youtu.be/Z-_aXBF3Mhg?t=44</t>
+  </si>
+  <si>
     <t>別人家</t>
   </si>
   <si>
-    <t>諾鴉・奈菲墨</t>
-  </si>
-  <si>
-    <t>✧該誰說詞了#04✧我重生了，這一世我是一名火辣護士！！||希妮·亞里絲🤍SinnieAris✨ ‪@uchififi‬ ‪@u00_Vtuber‬ ‪@AoiHinamoriCh‬</t>
-  </si>
-  <si>
-    <t>https://www.youtube.com/watch?v=57_XbTgSrs8</t>
-  </si>
-  <si>
-    <t>希妮·亞里絲, Aoi Hinamori, 羽芝扉扉</t>
-  </si>
-  <si>
-    <t>5⧸3 幽李鈴你在狗叫什麼 !手機殼 !官網</t>
-  </si>
-  <si>
-    <t>https://www.twitch.tv/videos/2762858494</t>
-  </si>
-  <si>
-    <t>【人生遊戲】跟新朋朋一起玩遊戲！重生之後我要做大女主 ft. 史黛菈、幽李鈴、Aoi【奇露琪露 Kirukiru】</t>
-  </si>
-  <si>
-    <t>https://www.youtube.com/watch?v=GE9j9o3lQZQ</t>
-  </si>
-  <si>
-    <t>奇露琪露, 史黛菈 埃蕾諾亞, Aoi Hinamori</t>
-  </si>
-  <si>
-    <t>【通靈之戰】各方靈能者齊聚一堂，角逐最佳靈能者之位！ft.幽李鈴/真理果/羽芝扉扉/煌Kirali【瓦西瓦瓦 / Vaswawa】</t>
-  </si>
-  <si>
-    <t>https://www.youtube.com/watch?v=5ORwZjOEgFU</t>
-  </si>
-  <si>
-    <t>瓦西瓦瓦, 真理果, 羽芝扉扉, 煌Kirali</t>
-  </si>
-  <si>
-    <t>5⧸23 #跑步接力歌回2 線上跑路 ｜ !手機殼 !官網 !DC</t>
-  </si>
-  <si>
-    <t>https://www.twitch.tv/videos/2778900185</t>
-  </si>
-  <si>
-    <t>Twitch, 歌回, 接力</t>
-  </si>
-  <si>
-    <t>【特別企劃】不准笑ASMR♡誰會先忍不住笑出來？【羽芝扉扉 Uchi Fifi】</t>
-  </si>
-  <si>
-    <t>https://www.youtube.com/watch?v=ZlHAwVwidVQ</t>
-  </si>
-  <si>
-    <t>羽芝扉扉, 麵音白湯, 夢寐愛姆, 瓦西瓦瓦, 崎塔</t>
-  </si>
-  <si>
-    <t>6⧸10  出生到現在第一次打麻將 還幫遊戲配音 好羞恥我真的不敢聽 #天月麻雀 !手機殼 !官網</t>
-  </si>
-  <si>
-    <t>https://www.twitch.tv/videos/2793248277</t>
-  </si>
-  <si>
-    <t>Twitch, 工商</t>
-  </si>
-  <si>
-    <t>【會員限定】喝點小酒跟你們說說心裡話【幽李鈴／Uririn】</t>
-  </si>
-  <si>
-    <t>https://www.youtube.com/watch?v=lU14OrwDTVM</t>
-  </si>
-  <si>
-    <t>會限, 酒雜</t>
-  </si>
-  <si>
-    <t>6⧸14  我將登基成為大王 !手機殼 !官網</t>
-  </si>
-  <si>
-    <t>https://www.twitch.tv/videos/2796370720</t>
-  </si>
-  <si>
-    <t>6⧸25  我非常憤怒我相當憤怒   !手機殼 !官網</t>
-  </si>
-  <si>
-    <t>https://www.twitch.tv/videos/2805004582</t>
-  </si>
-  <si>
-    <t>Twitch, 酒雜</t>
-  </si>
-  <si>
-    <t>【2026以聲傳豬系列★台V霹靂火】DIKA豚足姬 (·⚇·)❤️‍🔥我若是袂爽，我會送你一桶汽油、一支番仔火❤️‍🔥今仔日絕對是台灣上Hito ê 配信節目!!!</t>
-  </si>
-  <si>
-    <t>https://www.youtube.com/watch?v=-Z9coQ4RyEE</t>
-  </si>
-  <si>
-    <t>DIKA豚足姬, 凌潮, 熙歌, 真理果, 伍一</t>
-  </si>
-  <si>
-    <t>消失兩個月，我...（養狗了）</t>
-  </si>
-  <si>
-    <t>https://www.youtube.com/watch?v=feZ2gizB5C8</t>
-  </si>
-  <si>
-    <t>7⧸13  喔嗨喲學妹  !手機殼 !官網</t>
-  </si>
-  <si>
-    <t>https://www.twitch.tv/videos/2818713649</t>
-  </si>
-  <si>
-    <t>【會員限定】偷偷摸摸講秘密</t>
-  </si>
-  <si>
-    <t>https://www.youtube.com/watch?v=PyCcTrwdr9Q</t>
-  </si>
-  <si>
-    <t>會限, 雜談, 歌回</t>
-  </si>
-  <si>
-    <t>📢直播異動通知📢 阿金吃了不該吃的東西 現在要緊急帶他去看醫生 考慮到回來可能還要觀察一下所以晚上台先取消🙏🙏</t>
-  </si>
-  <si>
-    <t>https://x.com/U00Vtuber/status/2078431711214571541</t>
-  </si>
-  <si>
-    <t>7⧸19 精神上支持閃電日本隊 經濟上支持西班牙隊  ｜ 一日賭徒 晚點看世界盃 !指令 !手機殼 !官網</t>
-  </si>
-  <si>
-    <t>https://www.twitch.tv/videos/2823869944</t>
-  </si>
-  <si>
-    <t>7⧸21 狗尿地毯還沒洗   !指令 !手機殼 !官網</t>
-  </si>
-  <si>
-    <t>https://www.twitch.tv/videos/2825431894</t>
-  </si>
-  <si>
-    <t>【嘻嘻哈哈通知】今天開始到7/31 我要出國啦！！！</t>
-  </si>
-  <si>
-    <t>https://x.com/U00Vtuber/status/2080840467936334254</t>
-  </si>
-  <si>
-    <t>X</t>
-  </si>
-  <si>
-    <t>【完蛋】出國喝醉不小心曝光...</t>
-  </si>
-  <si>
-    <t>https://www.youtube.com/watch?v=nHnCx2NXl6E</t>
-  </si>
-  <si>
-    <t>【急】會員快來幫我想辦法【幽李鈴／Uririn】</t>
-  </si>
-  <si>
-    <t>https://www.youtube.com/watch?v=0-ISidVOhoM</t>
-  </si>
-  <si>
-    <t>【七夕企劃】新詩x聲音演出，才子詩詠佳人戲，預告第二部！ | 🌙鯨諾whalefall🐋 | #whalefall #鯨諾</t>
-  </si>
-  <si>
-    <t>https://youtu.be/Z-_aXBF3Mhg?t=44</t>
-  </si>
-  <si>
     <t>鯨諾</t>
   </si>
   <si>
@@ -917,16 +953,229 @@
     <t>https://www.youtube.com/watch?v=7_0pPSK_PFs</t>
   </si>
   <si>
+    <t>8/15 我在凶宅的第一天   !指令 !手機殼 !官網</t>
+  </si>
+  <si>
+    <t>https://www.twitch.tv/videos/2846934918</t>
+  </si>
+  <si>
     <t>8⧸15 我在凶宅的第一天   !指令 !手機殼 !官網</t>
   </si>
   <si>
-    <t>https://www.twitch.tv/videos/2846934918</t>
-  </si>
-  <si>
     <t>丟錢在西門町街頭...十萬訂閱才可以撿回來</t>
   </si>
   <si>
     <t>https://www.youtube.com/watch?v=hnMnC_Cqlyk</t>
+  </si>
+  <si>
+    <t>【偶像問答】歡迎來到！真理果主播＆U00主播都是偶像的世界線！？ ft. 真理果、幽李鈴 #初見歡迎 ｜福栗 Fukuri｜VerseLink</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=2Cd5rn6kLtA</t>
+  </si>
+  <si>
+    <t>福栗, 真理果</t>
+  </si>
+  <si>
+    <t>Bのリベンジ - Cover by 閃亮三姐妹（真理果、幽李鈴、福栗 Fukuri）</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=G_5bOFykGPs</t>
+  </si>
+  <si>
+    <t>連動, 別人家, Cover</t>
+  </si>
+  <si>
+    <t>【西瓜爆炸挑戰】沒抽到五星就＋橡皮筋...(※頂級非洲人)</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=r62Olb5-6kc</t>
+  </si>
+  <si>
+    <t>【七夕特企】新詩x聲音演出，來看看大家精湛的表演吧！ft. 羽芝扉扉 | 🌙鯨諾whalefall🐋 | #whalefall #鯨諾</t>
+  </si>
+  <si>
+    <t>https://youtu.be/cUEtHSVOrAo?t=6855</t>
+  </si>
+  <si>
+    <t>8/19 我埋Body的第一天 !指令 !手機殼 !官網</t>
+  </si>
+  <si>
+    <t>https://www.twitch.tv/videos/2850505127</t>
+  </si>
+  <si>
+    <t>【十萬匿名QA】這些問題是認真的嗎...</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=vrECNR1vsv4</t>
+  </si>
+  <si>
+    <t>QA</t>
+  </si>
+  <si>
+    <t>小心！點進來可能會愛上我...</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=hbJVlX9sZNc</t>
+  </si>
+  <si>
+    <t>8/23 趕上最後一班車 | !指令 !手機殼 !官網</t>
+  </si>
+  <si>
+    <t>https://www.twitch.tv/videos/2854367057</t>
+  </si>
+  <si>
+    <t>Twitch, 突發, 歌回</t>
+  </si>
+  <si>
+    <t>這些觀眾匿名爛笑話把主播逼瘋了…</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=sc-6cd7U6BM</t>
+  </si>
+  <si>
+    <t>8/26 我在中油的第一天 | !指令 !手機殼 !官網</t>
+  </si>
+  <si>
+    <t>https://www.twitch.tv/videos/2856971659</t>
+  </si>
+  <si>
+    <t>【會員限定】講秘密</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=zVMO5fCmqWw</t>
+  </si>
+  <si>
+    <t>8/29 嘎七慎入! 我跟我老公搬家了 | !指令 !手機殼 !官網</t>
+  </si>
+  <si>
+    <t>https://www.twitch.tv/videos/2859664919</t>
+  </si>
+  <si>
+    <t>Twitch, 觀眾, 歌回</t>
+  </si>
+  <si>
+    <t>【問卷調查】查過中之人？對主播有色心？這些回答你跟大家一樣嗎？</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=yTzouZrWQwI</t>
+  </si>
+  <si>
+    <t>9/1 我當攝影師的第一天 | !指令 !手機殼 !官網</t>
+  </si>
+  <si>
+    <t>https://www.twitch.tv/videos/2862393331</t>
+  </si>
+  <si>
+    <t>YT禮物測試</t>
+  </si>
+  <si>
+    <t>歌回, 直式直播</t>
+  </si>
+  <si>
+    <t>又酒後亂●...！？我們能成為ＣＰ嗎？</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=KfiNmi5OTiM</t>
+  </si>
+  <si>
+    <t>希妮·亞里絲</t>
+  </si>
+  <si>
+    <t>9/4 我找到新工作了 | !指令 !手機殼 !官網</t>
+  </si>
+  <si>
+    <t>https://www.twitch.tv/videos/2864996547</t>
+  </si>
+  <si>
+    <t>初歌回，但是送禮物就亂叫</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=AoREwbnvNbM</t>
+  </si>
+  <si>
+    <t>【幽李鈴】9/6 續攤繼續唱 !指令!手機殼!官網</t>
+  </si>
+  <si>
+    <t>https://www.twitch.tv/videos/2866937249</t>
+  </si>
+  <si>
+    <t>【幽李鈴】9/9 身上長了奇怪的肉球 !指令!手機殼!官網</t>
+  </si>
+  <si>
+    <t>https://www.twitch.tv/videos/2869340514</t>
+  </si>
+  <si>
+    <t>今天容許我再請一天😭忙來忙去搬電腦弄電腦太累了…</t>
+  </si>
+  <si>
+    <t>https://x.com/U00Vtuber/status/2100183984290546059</t>
+  </si>
+  <si>
+    <t>交友檔案評審團｜來電五十只當朋友復刻版！ ft. 希珥 @shir_ch 、詩雨蔻達 @SHIUCODA 、幽李鈴 @u00_Vtuber</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=RRMVAeiA5G0</t>
+  </si>
+  <si>
+    <t>宅宅軍團長, 希珥, 詩雨蔻達</t>
+  </si>
+  <si>
+    <t>🍜 【今天我有哪裡不一樣】一點都難不倒我吧 對吧...【白湯】</t>
+  </si>
+  <si>
+    <t>https://youtu.be/m2JKEnX83DI?t=6322</t>
+  </si>
+  <si>
+    <t>麵音白湯</t>
+  </si>
+  <si>
+    <t>【幽李鈴】9/19 當時退出模仿界是被全球反對的 !指令!手機殼!官網</t>
+  </si>
+  <si>
+    <t>https://www.twitch.tv/videos/2878328755</t>
+  </si>
+  <si>
+    <t>麵音白湯, 希妮·亞里絲, 洛可洛斯特</t>
+  </si>
+  <si>
+    <t>跟神燈精靈猜幾位我喜歡(或不喜歡)的網紅</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=wbvaHsFuLbI</t>
+  </si>
+  <si>
+    <t>【護理師V】認識多年的護校同學來了！口無遮攔大爆料！？</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=lTjaCutbGx0</t>
+  </si>
+  <si>
+    <t>幽李鈴 - 藍 / 百人白首 #61</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=zbOsJbnkhyk</t>
+  </si>
+  <si>
+    <t>神崎アルファ</t>
+  </si>
+  <si>
+    <t>【新手帶娃模擬室】來看看誰會是最合格的家長神隊友？ feat.格萊伊、幽李鈴、宵【希洛萊昂 Shiro Leon】</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=bx3NHXXtrhA</t>
+  </si>
+  <si>
+    <t>希洛萊昂, 宵Yoruno, 格萊伊</t>
+  </si>
+  <si>
+    <t>【Important Announcement】 我被盜了(就在剛剛)</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=miWiBkq9cAk</t>
+  </si>
+  <si>
+    <t>突發</t>
   </si>
 </sst>
 </file>
@@ -1242,16 +1491,16 @@
         <v>46023.0</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="3">
@@ -1268,7 +1517,7 @@
         <v>17</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
     </row>
     <row r="4">
@@ -1279,16 +1528,16 @@
         <v>46028.0</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="5">
@@ -1322,7 +1571,7 @@
         <v>33</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
     </row>
     <row r="7">
@@ -1333,13 +1582,13 @@
         <v>46035.0</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
     </row>
     <row r="8">
@@ -1350,16 +1599,16 @@
         <v>46037.0</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
     </row>
     <row r="9">
@@ -1370,10 +1619,10 @@
         <v>46039.0</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
     </row>
     <row r="10">
@@ -1384,10 +1633,10 @@
         <v>46042.0</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="11">
@@ -1444,7 +1693,7 @@
         <v>72</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
     </row>
     <row r="14">
@@ -1481,7 +1730,7 @@
         <v>78</v>
       </c>
       <c r="E15" s="5" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
     </row>
     <row r="16">
@@ -1538,7 +1787,7 @@
         <v>88</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="G18" s="1" t="s">
         <v>89</v>
@@ -1575,7 +1824,7 @@
         <v>94</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="G20" s="1" t="s">
         <v>95</v>
@@ -1595,7 +1844,7 @@
         <v>97</v>
       </c>
       <c r="E21" s="5" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
     </row>
     <row r="22">
@@ -1612,7 +1861,7 @@
         <v>99</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="G22" s="1" t="s">
         <v>100</v>
@@ -1632,7 +1881,7 @@
         <v>102</v>
       </c>
       <c r="E23" s="5" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
     </row>
     <row r="24">
@@ -1666,7 +1915,7 @@
         <v>107</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="26">
@@ -1683,7 +1932,7 @@
         <v>109</v>
       </c>
       <c r="E26" s="5" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
     </row>
     <row r="27">
@@ -1700,7 +1949,7 @@
         <v>111</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="G27" s="1" t="s">
         <v>112</v>
@@ -1737,7 +1986,7 @@
         <v>117</v>
       </c>
       <c r="E29" s="5" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
     </row>
     <row r="30">
@@ -1754,7 +2003,7 @@
         <v>119</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="G30" s="1" t="s">
         <v>120</v>
@@ -1774,7 +2023,7 @@
         <v>122</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="G31" s="1" t="s">
         <v>123</v>
@@ -1871,10 +2120,10 @@
         <v>140</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="G36" s="1" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
     </row>
     <row r="37">
@@ -1885,16 +2134,16 @@
         <v>46094.0</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="D37" s="3" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="E37" s="1" t="s">
         <v>133</v>
       </c>
       <c r="F37" s="1" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
     </row>
     <row r="38">
@@ -1905,16 +2154,16 @@
         <v>46094.0</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="D38" s="3" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="G38" s="1" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
     </row>
     <row r="39">
@@ -1925,13 +2174,13 @@
         <v>46095.0</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="D39" s="3" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
     </row>
     <row r="40">
@@ -1942,16 +2191,16 @@
         <v>46096.0</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="D40" s="3" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="E40" s="1" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="G40" s="1" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
     </row>
     <row r="41">
@@ -1962,16 +2211,16 @@
         <v>46097.0</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="D41" s="3" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="E41" s="1" t="s">
         <v>137</v>
       </c>
       <c r="G41" s="1" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
     </row>
     <row r="42">
@@ -1982,13 +2231,13 @@
         <v>46097.0</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="D42" s="3" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="E42" s="1" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
     </row>
     <row r="43">
@@ -1999,16 +2248,16 @@
         <v>46098.0</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="D43" s="3" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="E43" s="1" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="G43" s="1" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
     </row>
     <row r="44">
@@ -2019,16 +2268,16 @@
         <v>46102.0</v>
       </c>
       <c r="C44" s="1" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="D44" s="3" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="E44" s="1" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="F44" s="1" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
     </row>
     <row r="45">
@@ -2039,13 +2288,13 @@
         <v>46103.0</v>
       </c>
       <c r="C45" s="1" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="D45" s="3" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="E45" s="1" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
     </row>
     <row r="46">
@@ -2056,13 +2305,13 @@
         <v>46104.0</v>
       </c>
       <c r="C46" s="1" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="D46" s="3" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="E46" s="5" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
     </row>
     <row r="47">
@@ -2073,16 +2322,16 @@
         <v>46104.0</v>
       </c>
       <c r="C47" s="1" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="D47" s="3" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="E47" s="1" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="F47" s="1" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
     </row>
     <row r="48">
@@ -2093,10 +2342,10 @@
         <v>46106.0</v>
       </c>
       <c r="C48" s="1" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="D48" s="3" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
     </row>
     <row r="49">
@@ -2107,16 +2356,16 @@
         <v>46108.0</v>
       </c>
       <c r="C49" s="1" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="D49" s="3" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="E49" s="1" t="s">
         <v>137</v>
       </c>
       <c r="G49" s="1" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
     </row>
     <row r="50">
@@ -2127,16 +2376,16 @@
         <v>46108.0</v>
       </c>
       <c r="C50" s="1" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="D50" s="3" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="E50" s="1" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="G50" s="1" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
     </row>
     <row r="51">
@@ -2147,16 +2396,16 @@
         <v>46108.0</v>
       </c>
       <c r="C51" s="1" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="D51" s="3" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="E51" s="1" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="F51" s="1" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
     </row>
     <row r="52">
@@ -2167,10 +2416,10 @@
         <v>46109.0</v>
       </c>
       <c r="C52" s="1" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="D52" s="3" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="E52" s="1" t="s">
         <v>126</v>
@@ -2184,13 +2433,13 @@
         <v>46111.0</v>
       </c>
       <c r="C53" s="1" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="D53" s="3" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="E53" s="5" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
     </row>
     <row r="54">
@@ -2201,16 +2450,16 @@
         <v>46112.0</v>
       </c>
       <c r="C54" s="1" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="D54" s="3" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="E54" s="1" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="G54" s="1" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
     </row>
     <row r="55">
@@ -2221,16 +2470,16 @@
         <v>46112.0</v>
       </c>
       <c r="C55" s="1" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="D55" s="3" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="E55" s="1" t="s">
         <v>133</v>
       </c>
       <c r="F55" s="1" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
     </row>
     <row r="56">
@@ -2241,10 +2490,10 @@
         <v>46116.0</v>
       </c>
       <c r="C56" s="1" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="D56" s="3" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
     </row>
     <row r="57">
@@ -2255,13 +2504,13 @@
         <v>46117.0</v>
       </c>
       <c r="C57" s="1" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="D57" s="3" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="E57" s="1" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
     </row>
     <row r="58">
@@ -2272,16 +2521,16 @@
         <v>46117.0</v>
       </c>
       <c r="C58" s="1" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="D58" s="3" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="E58" s="1" t="s">
         <v>133</v>
       </c>
       <c r="F58" s="1" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
     </row>
     <row r="59">
@@ -2292,16 +2541,16 @@
         <v>46118.0</v>
       </c>
       <c r="C59" s="1" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="D59" s="3" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="E59" s="1" t="s">
         <v>133</v>
       </c>
       <c r="F59" s="1" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
     </row>
     <row r="60">
@@ -2312,16 +2561,16 @@
         <v>46118.0</v>
       </c>
       <c r="C60" s="1" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="D60" s="3" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="E60" s="1" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="G60" s="1" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
     </row>
     <row r="61">
@@ -2332,16 +2581,16 @@
         <v>46119.0</v>
       </c>
       <c r="C61" s="1" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="D61" s="3" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="E61" s="1" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="G61" s="1" t="s">
-        <v>209</v>
+        <v>213</v>
       </c>
     </row>
     <row r="62">
@@ -2352,19 +2601,19 @@
         <v>46120.0</v>
       </c>
       <c r="C62" s="1" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="D62" s="3" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="E62" s="1" t="s">
         <v>81</v>
       </c>
       <c r="F62" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G62" s="1" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
     </row>
     <row r="63">
@@ -2375,16 +2624,16 @@
         <v>46121.0</v>
       </c>
       <c r="C63" s="1" t="s">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="D63" s="3" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="E63" s="1" t="s">
         <v>133</v>
       </c>
       <c r="F63" s="1" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
     </row>
     <row r="64">
@@ -2395,13 +2644,13 @@
         <v>46124.0</v>
       </c>
       <c r="C64" s="1" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="D64" s="3" t="s">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="E64" s="1" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
     </row>
     <row r="65">
@@ -2412,16 +2661,16 @@
         <v>46125.0</v>
       </c>
       <c r="C65" s="1" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="D65" s="3" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="E65" s="1" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="G65" s="1" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
     </row>
     <row r="66">
@@ -2432,19 +2681,19 @@
         <v>46126.0</v>
       </c>
       <c r="C66" s="1" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="D66" s="3" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="E66" s="1" t="s">
         <v>81</v>
       </c>
       <c r="F66" s="1" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="G66" s="1" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
     </row>
     <row r="67">
@@ -2455,13 +2704,13 @@
         <v>46127.0</v>
       </c>
       <c r="C67" s="1" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="D67" s="3" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="E67" s="5" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
     </row>
     <row r="68">
@@ -2472,13 +2721,13 @@
         <v>46128.0</v>
       </c>
       <c r="C68" s="1" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="D68" s="3" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="E68" s="5" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
     </row>
     <row r="69">
@@ -2489,16 +2738,16 @@
         <v>46130.0</v>
       </c>
       <c r="C69" s="1" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="D69" s="3" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="E69" s="1" t="s">
         <v>137</v>
       </c>
       <c r="G69" s="1" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
     </row>
     <row r="70">
@@ -2509,16 +2758,16 @@
         <v>46139.0</v>
       </c>
       <c r="C70" s="1" t="s">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="D70" s="3" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="E70" s="1" t="s">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="F70" s="1" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
     </row>
     <row r="71">
@@ -2529,16 +2778,16 @@
         <v>46140.0</v>
       </c>
       <c r="C71" s="1" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="D71" s="3" t="s">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="E71" s="1" t="s">
         <v>133</v>
       </c>
       <c r="F71" s="1" t="s">
-        <v>240</v>
+        <v>243</v>
       </c>
     </row>
     <row r="72">
@@ -2549,16 +2798,16 @@
         <v>46145.0</v>
       </c>
       <c r="C72" s="1" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="D72" s="3" t="s">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="E72" s="1" t="s">
         <v>137</v>
       </c>
       <c r="G72" s="1" t="s">
-        <v>241</v>
+        <v>246</v>
       </c>
     </row>
     <row r="73">
@@ -2569,16 +2818,16 @@
         <v>46145.0</v>
       </c>
       <c r="C73" s="1" t="s">
-        <v>243</v>
+        <v>247</v>
       </c>
       <c r="D73" s="3" t="s">
-        <v>244</v>
+        <v>248</v>
       </c>
       <c r="E73" s="1" t="s">
         <v>133</v>
       </c>
       <c r="F73" s="1" t="s">
-        <v>245</v>
+        <v>249</v>
       </c>
     </row>
     <row r="74">
@@ -2589,16 +2838,16 @@
         <v>46155.0</v>
       </c>
       <c r="C74" s="1" t="s">
-        <v>246</v>
+        <v>250</v>
       </c>
       <c r="D74" s="3" t="s">
-        <v>247</v>
+        <v>251</v>
       </c>
       <c r="E74" s="1" t="s">
         <v>133</v>
       </c>
       <c r="F74" s="1" t="s">
-        <v>248</v>
+        <v>252</v>
       </c>
     </row>
     <row r="75">
@@ -2609,16 +2858,16 @@
         <v>46165.0</v>
       </c>
       <c r="C75" s="1" t="s">
-        <v>249</v>
+        <v>253</v>
       </c>
       <c r="D75" s="3" t="s">
-        <v>250</v>
+        <v>254</v>
       </c>
       <c r="E75" s="1" t="s">
-        <v>251</v>
+        <v>255</v>
       </c>
       <c r="G75" s="1" t="s">
-        <v>249</v>
+        <v>256</v>
       </c>
     </row>
     <row r="76">
@@ -2629,16 +2878,16 @@
         <v>46178.0</v>
       </c>
       <c r="C76" s="1" t="s">
-        <v>252</v>
+        <v>257</v>
       </c>
       <c r="D76" s="3" t="s">
-        <v>253</v>
+        <v>258</v>
       </c>
       <c r="E76" s="1" t="s">
         <v>133</v>
       </c>
       <c r="F76" s="1" t="s">
-        <v>254</v>
+        <v>259</v>
       </c>
     </row>
     <row r="77">
@@ -2649,16 +2898,16 @@
         <v>46183.0</v>
       </c>
       <c r="C77" s="1" t="s">
-        <v>255</v>
+        <v>260</v>
       </c>
       <c r="D77" s="3" t="s">
-        <v>256</v>
+        <v>261</v>
       </c>
       <c r="E77" s="1" t="s">
-        <v>257</v>
+        <v>262</v>
       </c>
       <c r="G77" s="1" t="s">
-        <v>255</v>
+        <v>263</v>
       </c>
     </row>
     <row r="78">
@@ -2669,13 +2918,13 @@
         <v>46184.0</v>
       </c>
       <c r="C78" s="1" t="s">
-        <v>258</v>
+        <v>264</v>
       </c>
       <c r="D78" s="3" t="s">
-        <v>259</v>
+        <v>265</v>
       </c>
       <c r="E78" s="1" t="s">
-        <v>260</v>
+        <v>266</v>
       </c>
     </row>
     <row r="79">
@@ -2686,16 +2935,16 @@
         <v>46187.0</v>
       </c>
       <c r="C79" s="1" t="s">
-        <v>261</v>
+        <v>267</v>
       </c>
       <c r="D79" s="3" t="s">
-        <v>262</v>
+        <v>268</v>
       </c>
       <c r="E79" s="1" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="G79" s="1" t="s">
-        <v>261</v>
+        <v>269</v>
       </c>
     </row>
     <row r="80">
@@ -2706,16 +2955,16 @@
         <v>46198.0</v>
       </c>
       <c r="C80" s="1" t="s">
-        <v>263</v>
+        <v>270</v>
       </c>
       <c r="D80" s="3" t="s">
-        <v>264</v>
+        <v>271</v>
       </c>
       <c r="E80" s="1" t="s">
-        <v>265</v>
+        <v>272</v>
       </c>
       <c r="G80" s="1" t="s">
-        <v>263</v>
+        <v>273</v>
       </c>
     </row>
     <row r="81">
@@ -2726,16 +2975,16 @@
         <v>46199.0</v>
       </c>
       <c r="C81" s="1" t="s">
-        <v>266</v>
+        <v>274</v>
       </c>
       <c r="D81" s="3" t="s">
-        <v>267</v>
+        <v>275</v>
       </c>
       <c r="E81" s="1" t="s">
         <v>133</v>
       </c>
       <c r="F81" s="1" t="s">
-        <v>268</v>
+        <v>276</v>
       </c>
     </row>
     <row r="82">
@@ -2746,10 +2995,10 @@
         <v>46215.0</v>
       </c>
       <c r="C82" s="1" t="s">
-        <v>269</v>
+        <v>277</v>
       </c>
       <c r="D82" s="3" t="s">
-        <v>270</v>
+        <v>278</v>
       </c>
     </row>
     <row r="83">
@@ -2760,16 +3009,16 @@
         <v>46216.0</v>
       </c>
       <c r="C83" s="1" t="s">
-        <v>271</v>
+        <v>279</v>
       </c>
       <c r="D83" s="3" t="s">
-        <v>272</v>
+        <v>280</v>
       </c>
       <c r="E83" s="1" t="s">
         <v>137</v>
       </c>
       <c r="G83" s="1" t="s">
-        <v>271</v>
+        <v>281</v>
       </c>
     </row>
     <row r="84">
@@ -2780,13 +3029,13 @@
         <v>46219.0</v>
       </c>
       <c r="C84" s="1" t="s">
-        <v>273</v>
+        <v>282</v>
       </c>
       <c r="D84" s="3" t="s">
-        <v>274</v>
+        <v>283</v>
       </c>
       <c r="E84" s="1" t="s">
-        <v>275</v>
+        <v>284</v>
       </c>
     </row>
     <row r="85">
@@ -2797,13 +3046,13 @@
         <v>46221.0</v>
       </c>
       <c r="C85" s="1" t="s">
-        <v>276</v>
+        <v>285</v>
       </c>
       <c r="D85" s="3" t="s">
-        <v>277</v>
+        <v>286</v>
       </c>
       <c r="E85" s="5" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
     </row>
     <row r="86">
@@ -2814,16 +3063,16 @@
         <v>46222.0</v>
       </c>
       <c r="C86" s="1" t="s">
-        <v>278</v>
+        <v>287</v>
       </c>
       <c r="D86" s="3" t="s">
-        <v>279</v>
+        <v>288</v>
       </c>
       <c r="E86" s="1" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="G86" s="1" t="s">
-        <v>278</v>
+        <v>289</v>
       </c>
     </row>
     <row r="87">
@@ -2834,16 +3083,16 @@
         <v>46224.0</v>
       </c>
       <c r="C87" s="1" t="s">
-        <v>280</v>
+        <v>290</v>
       </c>
       <c r="D87" s="3" t="s">
-        <v>281</v>
+        <v>291</v>
       </c>
       <c r="E87" s="1" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="G87" s="1" t="s">
-        <v>280</v>
+        <v>292</v>
       </c>
     </row>
     <row r="88">
@@ -2854,13 +3103,13 @@
         <v>46228.0</v>
       </c>
       <c r="C88" s="1" t="s">
-        <v>282</v>
+        <v>293</v>
       </c>
       <c r="D88" s="3" t="s">
-        <v>283</v>
+        <v>294</v>
       </c>
       <c r="E88" s="1" t="s">
-        <v>284</v>
+        <v>295</v>
       </c>
     </row>
     <row r="89">
@@ -2871,10 +3120,10 @@
         <v>46246.0</v>
       </c>
       <c r="C89" s="1" t="s">
-        <v>285</v>
+        <v>296</v>
       </c>
       <c r="D89" s="3" t="s">
-        <v>286</v>
+        <v>297</v>
       </c>
     </row>
     <row r="90">
@@ -2885,13 +3134,13 @@
         <v>46246.0</v>
       </c>
       <c r="C90" s="1" t="s">
-        <v>287</v>
+        <v>298</v>
       </c>
       <c r="D90" s="3" t="s">
-        <v>288</v>
+        <v>299</v>
       </c>
       <c r="E90" s="1" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
     </row>
     <row r="91">
@@ -2902,16 +3151,16 @@
         <v>46247.0</v>
       </c>
       <c r="C91" s="1" t="s">
-        <v>289</v>
+        <v>300</v>
       </c>
       <c r="D91" s="3" t="s">
-        <v>290</v>
+        <v>301</v>
       </c>
       <c r="E91" s="1" t="s">
-        <v>236</v>
+        <v>302</v>
       </c>
       <c r="F91" s="1" t="s">
-        <v>291</v>
+        <v>303</v>
       </c>
     </row>
     <row r="92">
@@ -2922,13 +3171,13 @@
         <v>46247.0</v>
       </c>
       <c r="C92" s="1" t="s">
-        <v>292</v>
+        <v>304</v>
       </c>
       <c r="D92" s="3" t="s">
-        <v>293</v>
+        <v>305</v>
       </c>
       <c r="E92" s="1" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
     </row>
     <row r="93">
@@ -2939,13 +3188,13 @@
         <v>46248.0</v>
       </c>
       <c r="C93" s="1" t="s">
-        <v>294</v>
+        <v>306</v>
       </c>
       <c r="D93" s="3" t="s">
-        <v>295</v>
+        <v>307</v>
       </c>
       <c r="E93" s="1" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
     </row>
     <row r="94">
@@ -2956,16 +3205,16 @@
         <v>46248.0</v>
       </c>
       <c r="C94" s="1" t="s">
-        <v>296</v>
+        <v>308</v>
       </c>
       <c r="D94" s="3" t="s">
-        <v>297</v>
+        <v>309</v>
       </c>
       <c r="E94" s="1" t="s">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="F94" s="1" t="s">
-        <v>298</v>
+        <v>310</v>
       </c>
     </row>
     <row r="95">
@@ -2976,13 +3225,13 @@
         <v>46249.0</v>
       </c>
       <c r="C95" s="1" t="s">
-        <v>299</v>
+        <v>311</v>
       </c>
       <c r="D95" s="3" t="s">
-        <v>300</v>
+        <v>312</v>
       </c>
       <c r="E95" s="1" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
     </row>
     <row r="96">
@@ -2993,16 +3242,16 @@
         <v>46249.0</v>
       </c>
       <c r="C96" s="1" t="s">
-        <v>301</v>
+        <v>313</v>
       </c>
       <c r="D96" s="3" t="s">
-        <v>302</v>
+        <v>314</v>
       </c>
       <c r="E96" s="1" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="G96" s="1" t="s">
-        <v>301</v>
+        <v>315</v>
       </c>
     </row>
     <row r="97">
@@ -3013,10 +3262,525 @@
         <v>46250.0</v>
       </c>
       <c r="C97" s="1" t="s">
+        <v>316</v>
+      </c>
+      <c r="D97" s="3" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="1">
+        <v>108.0</v>
+      </c>
+      <c r="B98" s="2">
+        <v>46251.0</v>
+      </c>
+      <c r="C98" s="1" t="s">
+        <v>318</v>
+      </c>
+      <c r="D98" s="3" t="s">
+        <v>319</v>
+      </c>
+      <c r="E98" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="F98" s="1" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="1">
+        <v>109.0</v>
+      </c>
+      <c r="B99" s="2">
+        <v>46251.0</v>
+      </c>
+      <c r="C99" s="1" t="s">
+        <v>321</v>
+      </c>
+      <c r="D99" s="3" t="s">
+        <v>322</v>
+      </c>
+      <c r="E99" s="1" t="s">
+        <v>323</v>
+      </c>
+      <c r="F99" s="1" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="1">
+        <v>110.0</v>
+      </c>
+      <c r="B100" s="2">
+        <v>46252.0</v>
+      </c>
+      <c r="C100" s="1" t="s">
+        <v>324</v>
+      </c>
+      <c r="D100" s="3" t="s">
+        <v>325</v>
+      </c>
+      <c r="E100" s="1" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="1">
+        <v>111.0</v>
+      </c>
+      <c r="B101" s="2">
+        <v>46252.0</v>
+      </c>
+      <c r="C101" s="1" t="s">
+        <v>326</v>
+      </c>
+      <c r="D101" s="3" t="s">
+        <v>327</v>
+      </c>
+      <c r="E101" s="1" t="s">
+        <v>302</v>
+      </c>
+      <c r="F101" s="1" t="s">
         <v>303</v>
       </c>
-      <c r="D97" s="3" t="s">
-        <v>304</v>
+    </row>
+    <row r="102">
+      <c r="A102" s="1">
+        <v>112.0</v>
+      </c>
+      <c r="B102" s="2">
+        <v>46253.0</v>
+      </c>
+      <c r="C102" s="1" t="s">
+        <v>328</v>
+      </c>
+      <c r="D102" s="3" t="s">
+        <v>329</v>
+      </c>
+      <c r="E102" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="1">
+        <v>113.0</v>
+      </c>
+      <c r="B103" s="2">
+        <v>46254.0</v>
+      </c>
+      <c r="C103" s="1" t="s">
+        <v>330</v>
+      </c>
+      <c r="D103" s="3" t="s">
+        <v>331</v>
+      </c>
+      <c r="E103" s="1" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="1">
+        <v>114.0</v>
+      </c>
+      <c r="B104" s="2">
+        <v>46256.0</v>
+      </c>
+      <c r="C104" s="1" t="s">
+        <v>333</v>
+      </c>
+      <c r="D104" s="3" t="s">
+        <v>334</v>
+      </c>
+      <c r="E104" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="1">
+        <v>115.0</v>
+      </c>
+      <c r="B105" s="2">
+        <v>46258.0</v>
+      </c>
+      <c r="C105" s="1" t="s">
+        <v>335</v>
+      </c>
+      <c r="D105" s="3" t="s">
+        <v>336</v>
+      </c>
+      <c r="E105" s="1" t="s">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="1">
+        <v>116.0</v>
+      </c>
+      <c r="B106" s="2">
+        <v>46260.0</v>
+      </c>
+      <c r="C106" s="1" t="s">
+        <v>338</v>
+      </c>
+      <c r="D106" s="3" t="s">
+        <v>339</v>
+      </c>
+      <c r="E106" s="1" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="1">
+        <v>117.0</v>
+      </c>
+      <c r="B107" s="2">
+        <v>46260.0</v>
+      </c>
+      <c r="C107" s="1" t="s">
+        <v>340</v>
+      </c>
+      <c r="D107" s="3" t="s">
+        <v>341</v>
+      </c>
+      <c r="E107" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="1">
+        <v>118.0</v>
+      </c>
+      <c r="B108" s="2">
+        <v>46261.0</v>
+      </c>
+      <c r="C108" s="1" t="s">
+        <v>342</v>
+      </c>
+      <c r="D108" s="3" t="s">
+        <v>343</v>
+      </c>
+      <c r="E108" s="1" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="1">
+        <v>119.0</v>
+      </c>
+      <c r="B109" s="2">
+        <v>46263.0</v>
+      </c>
+      <c r="C109" s="1" t="s">
+        <v>344</v>
+      </c>
+      <c r="D109" s="3" t="s">
+        <v>345</v>
+      </c>
+      <c r="E109" s="1" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="1">
+        <v>120.0</v>
+      </c>
+      <c r="B110" s="2">
+        <v>46264.0</v>
+      </c>
+      <c r="C110" s="1" t="s">
+        <v>347</v>
+      </c>
+      <c r="D110" s="3" t="s">
+        <v>348</v>
+      </c>
+      <c r="E110" s="1"/>
+    </row>
+    <row r="111">
+      <c r="A111" s="1">
+        <v>121.0</v>
+      </c>
+      <c r="B111" s="2">
+        <v>46266.0</v>
+      </c>
+      <c r="C111" s="1" t="s">
+        <v>349</v>
+      </c>
+      <c r="D111" s="3" t="s">
+        <v>350</v>
+      </c>
+      <c r="E111" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="1">
+        <v>122.0</v>
+      </c>
+      <c r="B112" s="2">
+        <v>46267.0</v>
+      </c>
+      <c r="C112" s="1" t="s">
+        <v>351</v>
+      </c>
+      <c r="D112" s="1"/>
+      <c r="E112" s="1" t="s">
+        <v>352</v>
+      </c>
+      <c r="F112" s="1"/>
+    </row>
+    <row r="113">
+      <c r="A113" s="1">
+        <v>123.0</v>
+      </c>
+      <c r="B113" s="2">
+        <v>46268.0</v>
+      </c>
+      <c r="C113" s="1" t="s">
+        <v>353</v>
+      </c>
+      <c r="D113" s="3" t="s">
+        <v>354</v>
+      </c>
+      <c r="E113" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="F113" s="1" t="s">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="1">
+        <v>124.0</v>
+      </c>
+      <c r="B114" s="2">
+        <v>46269.0</v>
+      </c>
+      <c r="C114" s="1" t="s">
+        <v>356</v>
+      </c>
+      <c r="D114" s="3" t="s">
+        <v>357</v>
+      </c>
+      <c r="E114" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="1">
+        <v>125.0</v>
+      </c>
+      <c r="B115" s="2">
+        <v>46271.0</v>
+      </c>
+      <c r="C115" s="1" t="s">
+        <v>358</v>
+      </c>
+      <c r="D115" s="3" t="s">
+        <v>359</v>
+      </c>
+      <c r="E115" s="1" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="1">
+        <v>126.0</v>
+      </c>
+      <c r="B116" s="2">
+        <v>46271.0</v>
+      </c>
+      <c r="C116" s="1" t="s">
+        <v>360</v>
+      </c>
+      <c r="D116" s="3" t="s">
+        <v>361</v>
+      </c>
+      <c r="E116" s="1" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="1">
+        <v>127.0</v>
+      </c>
+      <c r="B117" s="2">
+        <v>46274.0</v>
+      </c>
+      <c r="C117" s="1" t="s">
+        <v>362</v>
+      </c>
+      <c r="D117" s="3" t="s">
+        <v>363</v>
+      </c>
+      <c r="E117" s="1" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="1">
+        <v>128.0</v>
+      </c>
+      <c r="B118" s="2">
+        <v>46281.0</v>
+      </c>
+      <c r="C118" s="1" t="s">
+        <v>364</v>
+      </c>
+      <c r="D118" s="3" t="s">
+        <v>365</v>
+      </c>
+      <c r="E118" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="F118" s="1"/>
+    </row>
+    <row r="119">
+      <c r="A119" s="1">
+        <v>129.0</v>
+      </c>
+      <c r="B119" s="2">
+        <v>46282.0</v>
+      </c>
+      <c r="C119" s="1" t="s">
+        <v>366</v>
+      </c>
+      <c r="D119" s="3" t="s">
+        <v>367</v>
+      </c>
+      <c r="E119" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="F119" s="1" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="1">
+        <v>130.0</v>
+      </c>
+      <c r="B120" s="2">
+        <v>46283.0</v>
+      </c>
+      <c r="C120" s="1" t="s">
+        <v>369</v>
+      </c>
+      <c r="D120" s="3" t="s">
+        <v>370</v>
+      </c>
+      <c r="E120" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="F120" s="1" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="1">
+        <v>131.0</v>
+      </c>
+      <c r="B121" s="2">
+        <v>46284.0</v>
+      </c>
+      <c r="C121" s="1" t="s">
+        <v>372</v>
+      </c>
+      <c r="D121" s="3" t="s">
+        <v>373</v>
+      </c>
+      <c r="E121" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="F121" s="1" t="s">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="1">
+        <v>132.0</v>
+      </c>
+      <c r="B122" s="2">
+        <v>46285.0</v>
+      </c>
+      <c r="C122" s="1" t="s">
+        <v>375</v>
+      </c>
+      <c r="D122" s="3" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="1">
+        <v>133.0</v>
+      </c>
+      <c r="B123" s="2">
+        <v>46288.0</v>
+      </c>
+      <c r="C123" s="1" t="s">
+        <v>377</v>
+      </c>
+      <c r="D123" s="3" t="s">
+        <v>378</v>
+      </c>
+      <c r="E123" s="1" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="1">
+        <v>134.0</v>
+      </c>
+      <c r="B124" s="2">
+        <v>46295.0</v>
+      </c>
+      <c r="C124" s="1" t="s">
+        <v>379</v>
+      </c>
+      <c r="D124" s="3" t="s">
+        <v>380</v>
+      </c>
+      <c r="E124" s="1" t="s">
+        <v>323</v>
+      </c>
+      <c r="F124" s="1" t="s">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="1">
+        <v>135.0</v>
+      </c>
+      <c r="B125" s="2">
+        <v>46295.0</v>
+      </c>
+      <c r="C125" s="1" t="s">
+        <v>382</v>
+      </c>
+      <c r="D125" s="3" t="s">
+        <v>383</v>
+      </c>
+      <c r="E125" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="F125" s="1" t="s">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="1">
+        <v>136.0</v>
+      </c>
+      <c r="B126" s="2">
+        <v>46295.0</v>
+      </c>
+      <c r="C126" s="1" t="s">
+        <v>385</v>
+      </c>
+      <c r="D126" s="3" t="s">
+        <v>386</v>
+      </c>
+      <c r="E126" s="1" t="s">
+        <v>387</v>
       </c>
     </row>
   </sheetData>
@@ -3117,8 +3881,36 @@
     <hyperlink r:id="rId94" ref="D95"/>
     <hyperlink r:id="rId95" ref="D96"/>
     <hyperlink r:id="rId96" ref="D97"/>
+    <hyperlink r:id="rId97" ref="D98"/>
+    <hyperlink r:id="rId98" ref="D99"/>
+    <hyperlink r:id="rId99" ref="D100"/>
+    <hyperlink r:id="rId100" ref="D101"/>
+    <hyperlink r:id="rId101" ref="D102"/>
+    <hyperlink r:id="rId102" ref="D103"/>
+    <hyperlink r:id="rId103" ref="D104"/>
+    <hyperlink r:id="rId104" ref="D105"/>
+    <hyperlink r:id="rId105" ref="D106"/>
+    <hyperlink r:id="rId106" ref="D107"/>
+    <hyperlink r:id="rId107" ref="D108"/>
+    <hyperlink r:id="rId108" ref="D109"/>
+    <hyperlink r:id="rId109" ref="D110"/>
+    <hyperlink r:id="rId110" ref="D111"/>
+    <hyperlink r:id="rId111" ref="D113"/>
+    <hyperlink r:id="rId112" ref="D114"/>
+    <hyperlink r:id="rId113" ref="D115"/>
+    <hyperlink r:id="rId114" ref="D116"/>
+    <hyperlink r:id="rId115" ref="D117"/>
+    <hyperlink r:id="rId116" ref="D118"/>
+    <hyperlink r:id="rId117" ref="D119"/>
+    <hyperlink r:id="rId118" ref="D120"/>
+    <hyperlink r:id="rId119" ref="D121"/>
+    <hyperlink r:id="rId120" ref="D122"/>
+    <hyperlink r:id="rId121" ref="D123"/>
+    <hyperlink r:id="rId122" ref="D124"/>
+    <hyperlink r:id="rId123" ref="D125"/>
+    <hyperlink r:id="rId124" ref="D126"/>
   </hyperlinks>
-  <drawing r:id="rId97"/>
+  <drawing r:id="rId125"/>
 </worksheet>
 </file>
 
@@ -3160,10 +3952,10 @@
         <v>46000.0</v>
       </c>
       <c r="C2" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D2" s="3" t="s">
         <v>8</v>
-      </c>
-      <c r="D2" s="3" t="s">
-        <v>10</v>
       </c>
       <c r="E2" s="1" t="s">
         <v>11</v>
@@ -3177,10 +3969,10 @@
         <v>46011.0</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="E3" s="1" t="s">
         <v>11</v>
@@ -3194,10 +3986,10 @@
         <v>46011.0</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="E4" s="1" t="s">
         <v>11</v>
@@ -3211,16 +4003,16 @@
         <v>46011.0</v>
       </c>
       <c r="C5" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="D5" s="3" t="s">
         <v>24</v>
-      </c>
-      <c r="D5" s="3" t="s">
-        <v>26</v>
       </c>
       <c r="E5" s="1" t="s">
         <v>11</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="6">
@@ -3262,16 +4054,16 @@
         <v>46015.0</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="D8" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="E8" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="E8" s="1" t="s">
-        <v>41</v>
-      </c>
       <c r="F8" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="9">
@@ -3282,13 +4074,13 @@
         <v>46017.0</v>
       </c>
       <c r="C9" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="D9" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="D9" s="3" t="s">
+      <c r="E9" s="1" t="s">
         <v>44</v>
-      </c>
-      <c r="E9" s="1" t="s">
-        <v>47</v>
       </c>
     </row>
     <row r="10">
@@ -3299,13 +4091,13 @@
         <v>46019.0</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
     </row>
     <row r="11">
@@ -3316,10 +4108,10 @@
         <v>46021.0</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="E11" s="1" t="s">
         <v>57</v>
@@ -3336,10 +4128,10 @@
         <v>58</v>
       </c>
       <c r="D12" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="E12" s="1" t="s">
         <v>60</v>
-      </c>
-      <c r="E12" s="1" t="s">
-        <v>62</v>
       </c>
     </row>
   </sheetData>

--- a/streams.xlsx
+++ b/streams.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="480" uniqueCount="388">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="472" uniqueCount="382">
   <si>
     <t>id</t>
   </si>
@@ -77,55 +77,73 @@
     <t>X, 直播異動</t>
   </si>
   <si>
+    <t>【神回】直擊！醫院幽靈失蹤事件！</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=d0N94cT487Y</t>
+  </si>
+  <si>
     <t>關於今日發生的騷動說明 ft.亞洛赫</t>
   </si>
   <si>
     <t>https://www.youtube.com/watch?v=dUhUhvbywD0</t>
   </si>
   <si>
-    <t>【神回】直擊！醫院幽靈失蹤事件！</t>
-  </si>
-  <si>
-    <t>https://www.youtube.com/watch?v=d0N94cT487Y</t>
+    <t>亞洛赫</t>
+  </si>
+  <si>
+    <t>【初配信】初次見面！！我是幽李鈴！！</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=Yp2QhS2g0tU</t>
   </si>
   <si>
     <t>直播異動, 連動</t>
   </si>
   <si>
-    <t>亞洛赫</t>
-  </si>
-  <si>
     <t>大便糖速吃...我後悔了</t>
   </si>
   <si>
+    <t>【後日談QA】治安不好的棉花糖很多呢各位</t>
+  </si>
+  <si>
     <t>https://www.youtube.com/watch?v=v_O4YV6wZtk</t>
   </si>
   <si>
-    <t>【初配信】初次見面！！我是幽李鈴！！</t>
-  </si>
-  <si>
-    <t>https://www.youtube.com/watch?v=Yp2QhS2g0tU</t>
+    <t>https://www.youtube.com/watch?v=kiGVfQRxg5w</t>
   </si>
   <si>
     <t>QA, 棉花糖</t>
   </si>
   <si>
+    <t>【聖誕初連動】非誠勿擾，今晚能不能配對成功？ft.亞洛赫</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=G9uRcuHZTdM</t>
+  </si>
+  <si>
     <t>【A/S/M/R】嗯哼～♡人家是新手～♡【 NO Sleep /Relax /Whispering】</t>
   </si>
   <si>
     <t>https://www.youtube.com/watch?v=Vp-lbw9r880</t>
   </si>
   <si>
-    <t>【後日談QA】治安不好的棉花糖很多呢各位</t>
-  </si>
-  <si>
-    <t>https://www.youtube.com/watch?v=kiGVfQRxg5w</t>
-  </si>
-  <si>
-    <t>【聖誕初連動】非誠勿擾，今晚能不能配對成功？ft.亞洛赫</t>
-  </si>
-  <si>
-    <t>https://www.youtube.com/watch?v=G9uRcuHZTdM</t>
+    <t>連動</t>
+  </si>
+  <si>
+    <t>改成在圖奇開破防歌回！</t>
+  </si>
+  <si>
+    <t>https://x.com/U00Vtuber/status/2004465037411602451</t>
+  </si>
+  <si>
+    <t>X, 歌回, Twitch</t>
+  </si>
+  <si>
+    <t>【收益化慶祝酒雜】今天跟大家喝到掛！！！🥂乾杯！！！</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=3wkLHKQ5Uqo</t>
   </si>
   <si>
     <t>ASMR</t>
@@ -134,43 +152,37 @@
     <t>【會員限定】秘密</t>
   </si>
   <si>
-    <t>連動</t>
-  </si>
-  <si>
     <t>https://www.youtube.com/watch?v=KIAUz5M13wo</t>
   </si>
   <si>
-    <t>改成在圖奇開破防歌回！</t>
-  </si>
-  <si>
-    <t>https://x.com/U00Vtuber/status/2004465037411602451</t>
-  </si>
-  <si>
-    <t>X, 歌回, Twitch</t>
-  </si>
-  <si>
-    <t>【收益化慶祝酒雜】今天跟大家喝到掛！！！🥂乾杯！！！</t>
-  </si>
-  <si>
-    <t>https://www.youtube.com/watch?v=3wkLHKQ5Uqo</t>
+    <t>酒雜</t>
+  </si>
+  <si>
+    <t>【觀眾CALL IN】進DC還要面試真的假的啦！？</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=3VejobEf1WM</t>
   </si>
   <si>
     <t>會限</t>
   </si>
   <si>
+    <t>觀眾CALL IN</t>
+  </si>
+  <si>
     <t>【觀眾CALL IN】 夾子音醫院聯賽</t>
   </si>
   <si>
+    <t>【會員限定】看沒看到的履歷！！順便跨年啦！！！</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=7LmRg4qqk4M</t>
+  </si>
+  <si>
     <t>https://www.youtube.com/watch?v=HunY1CF0ezs</t>
   </si>
   <si>
-    <t>酒雜</t>
-  </si>
-  <si>
-    <t>【觀眾CALL IN】進DC還要面試真的假的啦！？</t>
-  </si>
-  <si>
-    <t>https://www.youtube.com/watch?v=3VejobEf1WM</t>
+    <t>會限, 直播異動</t>
   </si>
   <si>
     <t>Twitch, 觀眾CALL IN</t>
@@ -185,18 +197,6 @@
     <t>https://www.youtube.com/watch?v=0IHJxtZ_8XE</t>
   </si>
   <si>
-    <t>觀眾CALL IN</t>
-  </si>
-  <si>
-    <t>【會員限定】看沒看到的履歷！！順便跨年啦！！！</t>
-  </si>
-  <si>
-    <t>https://www.youtube.com/watch?v=7LmRg4qqk4M</t>
-  </si>
-  <si>
-    <t>會限, 直播異動</t>
-  </si>
-  <si>
     <t>手語讓觀眾猜出說甚麼才能宣傳新周邊！？(※禁止說話)</t>
   </si>
   <si>
@@ -731,219 +731,219 @@
     <t>https://youtu.be/ndjtD3GVxtg?t=6782</t>
   </si>
   <si>
+    <t>別人家</t>
+  </si>
+  <si>
+    <t>諾鴉・奈菲墨</t>
+  </si>
+  <si>
+    <t>✧該誰說詞了#04✧我重生了，這一世我是一名火辣護士！！||希妮·亞里絲🤍SinnieAris✨ ‪@uchififi‬ ‪@u00_Vtuber‬ ‪@AoiHinamoriCh‬</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=57_XbTgSrs8</t>
+  </si>
+  <si>
+    <t>希妮·亞里絲, Aoi Hinamori, 羽芝扉扉</t>
+  </si>
+  <si>
+    <t>5/3 幽李鈴你在狗叫什麼 !手機殼 !官網</t>
+  </si>
+  <si>
+    <t>https://www.twitch.tv/videos/2762858494</t>
+  </si>
+  <si>
+    <t>5⧸3 幽李鈴你在狗叫什麼 !手機殼 !官網</t>
+  </si>
+  <si>
+    <t>【人生遊戲】跟新朋朋一起玩遊戲！重生之後我要做大女主 ft. 史黛菈、幽李鈴、Aoi【奇露琪露 Kirukiru】</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=GE9j9o3lQZQ</t>
+  </si>
+  <si>
+    <t>奇露琪露, 史黛菈 埃蕾諾亞, Aoi Hinamori</t>
+  </si>
+  <si>
+    <t>【通靈之戰】各方靈能者齊聚一堂，角逐最佳靈能者之位！ft.幽李鈴/真理果/羽芝扉扉/煌Kirali【瓦西瓦瓦 / Vaswawa】</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=5ORwZjOEgFU</t>
+  </si>
+  <si>
+    <t>瓦西瓦瓦, 真理果, 羽芝扉扉, 煌Kirali</t>
+  </si>
+  <si>
+    <t>5/23 #跑步接力歌回2 線上跑路 ｜ !手機殼 !官網 !DC</t>
+  </si>
+  <si>
+    <t>https://www.twitch.tv/videos/2778900185</t>
+  </si>
+  <si>
+    <t>Twitch, 歌回, 接力</t>
+  </si>
+  <si>
+    <t>5⧸23 #跑步接力歌回2 線上跑路 ｜ !手機殼 !官網 !DC</t>
+  </si>
+  <si>
+    <t>【特別企劃】不准笑ASMR♡誰會先忍不住笑出來？【羽芝扉扉 Uchi Fifi】</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=ZlHAwVwidVQ</t>
+  </si>
+  <si>
+    <t>羽芝扉扉, 麵音白湯, 夢寐愛姆, 瓦西瓦瓦, 崎塔</t>
+  </si>
+  <si>
+    <t>6/10  出生到現在第一次打麻將 還幫遊戲配音 好羞恥我真的不敢聽 #天月麻雀 !手機殼 !官網</t>
+  </si>
+  <si>
+    <t>https://www.twitch.tv/videos/2793248277</t>
+  </si>
+  <si>
+    <t>Twitch, 工商</t>
+  </si>
+  <si>
+    <t>6⧸10  出生到現在第一次打麻將 還幫遊戲配音 好羞恥我真的不敢聽 #天月麻雀 !手機殼 !官網</t>
+  </si>
+  <si>
+    <t>【會員限定】喝點小酒跟你們說說心裡話【幽李鈴／Uririn】</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=lU14OrwDTVM</t>
+  </si>
+  <si>
+    <t>會限, 酒雜</t>
+  </si>
+  <si>
+    <t>6/14  我將登基成為大王 !手機殼 !官網</t>
+  </si>
+  <si>
+    <t>https://www.twitch.tv/videos/2796370720</t>
+  </si>
+  <si>
+    <t>6⧸14  我將登基成為大王 !手機殼 !官網</t>
+  </si>
+  <si>
+    <t>6/25  我非常憤怒我相當憤怒   !手機殼 !官網</t>
+  </si>
+  <si>
+    <t>https://www.twitch.tv/videos/2805004582</t>
+  </si>
+  <si>
+    <t>Twitch, 酒雜</t>
+  </si>
+  <si>
+    <t>6⧸25  我非常憤怒我相當憤怒   !手機殼 !官網</t>
+  </si>
+  <si>
+    <t>【2026以聲傳豬系列★台V霹靂火】DIKA豚足姬 (·⚇·)❤️‍🔥我若是袂爽，我會送你一桶汽油、一支番仔火❤️‍🔥今仔日絕對是台灣上Hito ê 配信節目!!!</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=-Z9coQ4RyEE</t>
+  </si>
+  <si>
+    <t>DIKA豚足姬, 凌潮, 熙歌, 真理果, 伍一</t>
+  </si>
+  <si>
+    <t>消失兩個月，我...（養狗了）</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=feZ2gizB5C8</t>
+  </si>
+  <si>
+    <t>7/13  喔嗨喲學妹  !手機殼 !官網</t>
+  </si>
+  <si>
+    <t>https://www.twitch.tv/videos/2818713649</t>
+  </si>
+  <si>
+    <t>7⧸13  喔嗨喲學妹  !手機殼 !官網</t>
+  </si>
+  <si>
+    <t>【會員限定】偷偷摸摸講秘密</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=PyCcTrwdr9Q</t>
+  </si>
+  <si>
+    <t>會限, 雜談, 歌回</t>
+  </si>
+  <si>
+    <t>📢直播異動通知📢 阿金吃了不該吃的東西 現在要緊急帶他去看醫生 考慮到回來可能還要觀察一下所以晚上台先取消🙏🙏</t>
+  </si>
+  <si>
+    <t>https://x.com/U00Vtuber/status/2078431711214571541</t>
+  </si>
+  <si>
+    <t>7/19 精神上支持閃電日本隊 經濟上支持西班牙隊  ｜ 一日賭徒 晚點看世界盃 !指令 !手機殼 !官網</t>
+  </si>
+  <si>
+    <t>https://www.twitch.tv/videos/2823869944</t>
+  </si>
+  <si>
+    <t>7⧸19 精神上支持閃電日本隊 經濟上支持西班牙隊  ｜ 一日賭徒 晚點看世界盃 !指令 !手機殼 !官網</t>
+  </si>
+  <si>
+    <t>7/21 狗尿地毯還沒洗   !指令 !手機殼 !官網</t>
+  </si>
+  <si>
+    <t>https://www.twitch.tv/videos/2825431894</t>
+  </si>
+  <si>
+    <t>7⧸21 狗尿地毯還沒洗   !指令 !手機殼 !官網</t>
+  </si>
+  <si>
+    <t>【嘻嘻哈哈通知】今天開始到7/31 我要出國啦！！！</t>
+  </si>
+  <si>
+    <t>https://x.com/U00Vtuber/status/2080840467936334254</t>
+  </si>
+  <si>
+    <t>X</t>
+  </si>
+  <si>
+    <t>【完蛋】出國喝醉不小心曝光...</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=nHnCx2NXl6E</t>
+  </si>
+  <si>
+    <t>【急】會員快來幫我想辦法【幽李鈴／Uririn】</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=0-ISidVOhoM</t>
+  </si>
+  <si>
+    <t>【七夕企劃】新詩x聲音演出，才子詩詠佳人戲，預告第二部！ | 🌙鯨諾whalefall🐋 | #whalefall #鯨諾</t>
+  </si>
+  <si>
+    <t>https://youtu.be/Z-_aXBF3Mhg?t=44</t>
+  </si>
+  <si>
+    <t>鯨諾</t>
+  </si>
+  <si>
+    <t>【對到眼20次】就當作新男友介紹給我媽【幽李鈴／Uririn】</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=icqz9tf0tkY</t>
+  </si>
+  <si>
+    <t>【公審】駭入觀眾電腦看裡面有什麼...！？【幽李鈴／Uririn】</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=muVj8LhiZ8E</t>
+  </si>
+  <si>
+    <t>【二週年新衣裝紀念合唱（下）】一生一次大合唱今天又要和V朋朋帶來哪些歌曲呢🔥🔥 | 知花Chika</t>
+  </si>
+  <si>
+    <t>https://youtu.be/bZn2uiXpNvE?t=13311</t>
+  </si>
+  <si>
     <t>別人家, 歌回</t>
   </si>
   <si>
-    <t>諾鴉・奈菲墨</t>
-  </si>
-  <si>
-    <t>✧該誰說詞了#04✧我重生了，這一世我是一名火辣護士！！||希妮·亞里絲🤍SinnieAris✨ ‪@uchififi‬ ‪@u00_Vtuber‬ ‪@AoiHinamoriCh‬</t>
-  </si>
-  <si>
-    <t>https://www.youtube.com/watch?v=57_XbTgSrs8</t>
-  </si>
-  <si>
-    <t>希妮·亞里絲, Aoi Hinamori, 羽芝扉扉</t>
-  </si>
-  <si>
-    <t>5/3 幽李鈴你在狗叫什麼 !手機殼 !官網</t>
-  </si>
-  <si>
-    <t>https://www.twitch.tv/videos/2762858494</t>
-  </si>
-  <si>
-    <t>5⧸3 幽李鈴你在狗叫什麼 !手機殼 !官網</t>
-  </si>
-  <si>
-    <t>【人生遊戲】跟新朋朋一起玩遊戲！重生之後我要做大女主 ft. 史黛菈、幽李鈴、Aoi【奇露琪露 Kirukiru】</t>
-  </si>
-  <si>
-    <t>https://www.youtube.com/watch?v=GE9j9o3lQZQ</t>
-  </si>
-  <si>
-    <t>奇露琪露, 史黛菈 埃蕾諾亞, Aoi Hinamori</t>
-  </si>
-  <si>
-    <t>【通靈之戰】各方靈能者齊聚一堂，角逐最佳靈能者之位！ft.幽李鈴/真理果/羽芝扉扉/煌Kirali【瓦西瓦瓦 / Vaswawa】</t>
-  </si>
-  <si>
-    <t>https://www.youtube.com/watch?v=5ORwZjOEgFU</t>
-  </si>
-  <si>
-    <t>瓦西瓦瓦, 真理果, 羽芝扉扉, 煌Kirali</t>
-  </si>
-  <si>
-    <t>5/23 #跑步接力歌回2 線上跑路 ｜ !手機殼 !官網 !DC</t>
-  </si>
-  <si>
-    <t>https://www.twitch.tv/videos/2778900185</t>
-  </si>
-  <si>
-    <t>Twitch, 歌回, 接力</t>
-  </si>
-  <si>
-    <t>5⧸23 #跑步接力歌回2 線上跑路 ｜ !手機殼 !官網 !DC</t>
-  </si>
-  <si>
-    <t>【特別企劃】不准笑ASMR♡誰會先忍不住笑出來？【羽芝扉扉 Uchi Fifi】</t>
-  </si>
-  <si>
-    <t>https://www.youtube.com/watch?v=ZlHAwVwidVQ</t>
-  </si>
-  <si>
-    <t>羽芝扉扉, 麵音白湯, 夢寐愛姆, 瓦西瓦瓦, 崎塔</t>
-  </si>
-  <si>
-    <t>6/10  出生到現在第一次打麻將 還幫遊戲配音 好羞恥我真的不敢聽 #天月麻雀 !手機殼 !官網</t>
-  </si>
-  <si>
-    <t>https://www.twitch.tv/videos/2793248277</t>
-  </si>
-  <si>
-    <t>Twitch, 工商</t>
-  </si>
-  <si>
-    <t>6⧸10  出生到現在第一次打麻將 還幫遊戲配音 好羞恥我真的不敢聽 #天月麻雀 !手機殼 !官網</t>
-  </si>
-  <si>
-    <t>【會員限定】喝點小酒跟你們說說心裡話【幽李鈴／Uririn】</t>
-  </si>
-  <si>
-    <t>https://www.youtube.com/watch?v=lU14OrwDTVM</t>
-  </si>
-  <si>
-    <t>會限, 酒雜</t>
-  </si>
-  <si>
-    <t>6/14  我將登基成為大王 !手機殼 !官網</t>
-  </si>
-  <si>
-    <t>https://www.twitch.tv/videos/2796370720</t>
-  </si>
-  <si>
-    <t>6⧸14  我將登基成為大王 !手機殼 !官網</t>
-  </si>
-  <si>
-    <t>6/25  我非常憤怒我相當憤怒   !手機殼 !官網</t>
-  </si>
-  <si>
-    <t>https://www.twitch.tv/videos/2805004582</t>
-  </si>
-  <si>
-    <t>Twitch, 酒雜</t>
-  </si>
-  <si>
-    <t>6⧸25  我非常憤怒我相當憤怒   !手機殼 !官網</t>
-  </si>
-  <si>
-    <t>【2026以聲傳豬系列★台V霹靂火】DIKA豚足姬 (·⚇·)❤️‍🔥我若是袂爽，我會送你一桶汽油、一支番仔火❤️‍🔥今仔日絕對是台灣上Hito ê 配信節目!!!</t>
-  </si>
-  <si>
-    <t>https://www.youtube.com/watch?v=-Z9coQ4RyEE</t>
-  </si>
-  <si>
-    <t>DIKA豚足姬, 凌潮, 熙歌, 真理果, 伍一</t>
-  </si>
-  <si>
-    <t>消失兩個月，我...（養狗了）</t>
-  </si>
-  <si>
-    <t>https://www.youtube.com/watch?v=feZ2gizB5C8</t>
-  </si>
-  <si>
-    <t>7/13  喔嗨喲學妹  !手機殼 !官網</t>
-  </si>
-  <si>
-    <t>https://www.twitch.tv/videos/2818713649</t>
-  </si>
-  <si>
-    <t>7⧸13  喔嗨喲學妹  !手機殼 !官網</t>
-  </si>
-  <si>
-    <t>【會員限定】偷偷摸摸講秘密</t>
-  </si>
-  <si>
-    <t>https://www.youtube.com/watch?v=PyCcTrwdr9Q</t>
-  </si>
-  <si>
-    <t>會限, 雜談, 歌回</t>
-  </si>
-  <si>
-    <t>📢直播異動通知📢 阿金吃了不該吃的東西 現在要緊急帶他去看醫生 考慮到回來可能還要觀察一下所以晚上台先取消🙏🙏</t>
-  </si>
-  <si>
-    <t>https://x.com/U00Vtuber/status/2078431711214571541</t>
-  </si>
-  <si>
-    <t>7/19 精神上支持閃電日本隊 經濟上支持西班牙隊  ｜ 一日賭徒 晚點看世界盃 !指令 !手機殼 !官網</t>
-  </si>
-  <si>
-    <t>https://www.twitch.tv/videos/2823869944</t>
-  </si>
-  <si>
-    <t>7⧸19 精神上支持閃電日本隊 經濟上支持西班牙隊  ｜ 一日賭徒 晚點看世界盃 !指令 !手機殼 !官網</t>
-  </si>
-  <si>
-    <t>7/21 狗尿地毯還沒洗   !指令 !手機殼 !官網</t>
-  </si>
-  <si>
-    <t>https://www.twitch.tv/videos/2825431894</t>
-  </si>
-  <si>
-    <t>7⧸21 狗尿地毯還沒洗   !指令 !手機殼 !官網</t>
-  </si>
-  <si>
-    <t>【嘻嘻哈哈通知】今天開始到7/31 我要出國啦！！！</t>
-  </si>
-  <si>
-    <t>https://x.com/U00Vtuber/status/2080840467936334254</t>
-  </si>
-  <si>
-    <t>X</t>
-  </si>
-  <si>
-    <t>【完蛋】出國喝醉不小心曝光...</t>
-  </si>
-  <si>
-    <t>https://www.youtube.com/watch?v=nHnCx2NXl6E</t>
-  </si>
-  <si>
-    <t>【急】會員快來幫我想辦法【幽李鈴／Uririn】</t>
-  </si>
-  <si>
-    <t>https://www.youtube.com/watch?v=0-ISidVOhoM</t>
-  </si>
-  <si>
-    <t>【七夕企劃】新詩x聲音演出，才子詩詠佳人戲，預告第二部！ | 🌙鯨諾whalefall🐋 | #whalefall #鯨諾</t>
-  </si>
-  <si>
-    <t>https://youtu.be/Z-_aXBF3Mhg?t=44</t>
-  </si>
-  <si>
-    <t>別人家</t>
-  </si>
-  <si>
-    <t>鯨諾</t>
-  </si>
-  <si>
-    <t>【對到眼20次】就當作新男友介紹給我媽【幽李鈴／Uririn】</t>
-  </si>
-  <si>
-    <t>https://www.youtube.com/watch?v=icqz9tf0tkY</t>
-  </si>
-  <si>
-    <t>【公審】駭入觀眾電腦看裡面有什麼...！？【幽李鈴／Uririn】</t>
-  </si>
-  <si>
-    <t>https://www.youtube.com/watch?v=muVj8LhiZ8E</t>
-  </si>
-  <si>
-    <t>【二週年新衣裝紀念合唱（下）】一生一次大合唱今天又要和V朋朋帶來哪些歌曲呢🔥🔥 | 知花Chika</t>
-  </si>
-  <si>
-    <t>https://youtu.be/bZn2uiXpNvE?t=13311</t>
-  </si>
-  <si>
     <t>知花</t>
   </si>
   <si>
@@ -977,15 +977,6 @@
     <t>福栗, 真理果</t>
   </si>
   <si>
-    <t>Bのリベンジ - Cover by 閃亮三姐妹（真理果、幽李鈴、福栗 Fukuri）</t>
-  </si>
-  <si>
-    <t>https://www.youtube.com/watch?v=G_5bOFykGPs</t>
-  </si>
-  <si>
-    <t>連動, 別人家, Cover</t>
-  </si>
-  <si>
     <t>【西瓜爆炸挑戰】沒抽到五星就＋橡皮筋...(※頂級非洲人)</t>
   </si>
   <si>
@@ -1149,15 +1140,6 @@
   </si>
   <si>
     <t>https://www.youtube.com/watch?v=lTjaCutbGx0</t>
-  </si>
-  <si>
-    <t>幽李鈴 - 藍 / 百人白首 #61</t>
-  </si>
-  <si>
-    <t>https://www.youtube.com/watch?v=zbOsJbnkhyk</t>
-  </si>
-  <si>
-    <t>神崎アルファ</t>
   </si>
   <si>
     <t>【新手帶娃模擬室】來看看誰會是最合格的家長神隊友？ feat.格萊伊、幽李鈴、宵【希洛萊昂 Shiro Leon】</t>
@@ -1528,16 +1510,16 @@
         <v>46028.0</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="E4" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="F4" s="1" t="s">
         <v>25</v>
-      </c>
-      <c r="F4" s="1" t="s">
-        <v>26</v>
       </c>
     </row>
     <row r="5">
@@ -1548,13 +1530,13 @@
         <v>46030.0</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
     </row>
     <row r="6">
@@ -1565,13 +1547,13 @@
         <v>46032.0</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
     </row>
     <row r="7">
@@ -1582,13 +1564,13 @@
         <v>46035.0</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
     </row>
     <row r="8">
@@ -1599,16 +1581,16 @@
         <v>46037.0</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
     </row>
     <row r="9">
@@ -1619,10 +1601,10 @@
         <v>46039.0</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
     </row>
     <row r="10">
@@ -1693,7 +1675,7 @@
         <v>72</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
     </row>
     <row r="14">
@@ -1915,7 +1897,7 @@
         <v>107</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="26">
@@ -2294,7 +2276,7 @@
         <v>169</v>
       </c>
       <c r="E45" s="1" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
     </row>
     <row r="46">
@@ -2510,7 +2492,7 @@
         <v>201</v>
       </c>
       <c r="E57" s="1" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
     </row>
     <row r="58">
@@ -2610,7 +2592,7 @@
         <v>81</v>
       </c>
       <c r="F62" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G62" s="1" t="s">
         <v>216</v>
@@ -3140,7 +3122,7 @@
         <v>299</v>
       </c>
       <c r="E90" s="1" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
     </row>
     <row r="91">
@@ -3157,10 +3139,10 @@
         <v>301</v>
       </c>
       <c r="E91" s="1" t="s">
+        <v>239</v>
+      </c>
+      <c r="F91" s="1" t="s">
         <v>302</v>
-      </c>
-      <c r="F91" s="1" t="s">
-        <v>303</v>
       </c>
     </row>
     <row r="92">
@@ -3171,13 +3153,13 @@
         <v>46247.0</v>
       </c>
       <c r="C92" s="1" t="s">
+        <v>303</v>
+      </c>
+      <c r="D92" s="3" t="s">
         <v>304</v>
       </c>
-      <c r="D92" s="3" t="s">
-        <v>305</v>
-      </c>
       <c r="E92" s="1" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
     </row>
     <row r="93">
@@ -3188,10 +3170,10 @@
         <v>46248.0</v>
       </c>
       <c r="C93" s="1" t="s">
+        <v>305</v>
+      </c>
+      <c r="D93" s="3" t="s">
         <v>306</v>
-      </c>
-      <c r="D93" s="3" t="s">
-        <v>307</v>
       </c>
       <c r="E93" s="1" t="s">
         <v>150</v>
@@ -3205,13 +3187,13 @@
         <v>46248.0</v>
       </c>
       <c r="C94" s="1" t="s">
+        <v>307</v>
+      </c>
+      <c r="D94" s="3" t="s">
         <v>308</v>
       </c>
-      <c r="D94" s="3" t="s">
+      <c r="E94" s="1" t="s">
         <v>309</v>
-      </c>
-      <c r="E94" s="1" t="s">
-        <v>239</v>
       </c>
       <c r="F94" s="1" t="s">
         <v>310</v>
@@ -3293,7 +3275,7 @@
         <v>109.0</v>
       </c>
       <c r="B99" s="2">
-        <v>46251.0</v>
+        <v>46252.0</v>
       </c>
       <c r="C99" s="1" t="s">
         <v>321</v>
@@ -3302,10 +3284,7 @@
         <v>322</v>
       </c>
       <c r="E99" s="1" t="s">
-        <v>323</v>
-      </c>
-      <c r="F99" s="1" t="s">
-        <v>320</v>
+        <v>222</v>
       </c>
     </row>
     <row r="100">
@@ -3316,13 +3295,16 @@
         <v>46252.0</v>
       </c>
       <c r="C100" s="1" t="s">
+        <v>323</v>
+      </c>
+      <c r="D100" s="3" t="s">
         <v>324</v>
       </c>
-      <c r="D100" s="3" t="s">
-        <v>325</v>
-      </c>
       <c r="E100" s="1" t="s">
-        <v>222</v>
+        <v>239</v>
+      </c>
+      <c r="F100" s="1" t="s">
+        <v>302</v>
       </c>
     </row>
     <row r="101">
@@ -3330,19 +3312,16 @@
         <v>111.0</v>
       </c>
       <c r="B101" s="2">
-        <v>46252.0</v>
+        <v>46253.0</v>
       </c>
       <c r="C101" s="1" t="s">
+        <v>325</v>
+      </c>
+      <c r="D101" s="3" t="s">
         <v>326</v>
       </c>
-      <c r="D101" s="3" t="s">
-        <v>327</v>
-      </c>
       <c r="E101" s="1" t="s">
-        <v>302</v>
-      </c>
-      <c r="F101" s="1" t="s">
-        <v>303</v>
+        <v>14</v>
       </c>
     </row>
     <row r="102">
@@ -3350,16 +3329,16 @@
         <v>112.0</v>
       </c>
       <c r="B102" s="2">
-        <v>46253.0</v>
+        <v>46254.0</v>
       </c>
       <c r="C102" s="1" t="s">
+        <v>327</v>
+      </c>
+      <c r="D102" s="3" t="s">
         <v>328</v>
       </c>
-      <c r="D102" s="3" t="s">
+      <c r="E102" s="1" t="s">
         <v>329</v>
-      </c>
-      <c r="E102" s="1" t="s">
-        <v>14</v>
       </c>
     </row>
     <row r="103">
@@ -3367,7 +3346,7 @@
         <v>113.0</v>
       </c>
       <c r="B103" s="2">
-        <v>46254.0</v>
+        <v>46256.0</v>
       </c>
       <c r="C103" s="1" t="s">
         <v>330</v>
@@ -3376,7 +3355,7 @@
         <v>331</v>
       </c>
       <c r="E103" s="1" t="s">
-        <v>332</v>
+        <v>47</v>
       </c>
     </row>
     <row r="104">
@@ -3384,16 +3363,16 @@
         <v>114.0</v>
       </c>
       <c r="B104" s="2">
-        <v>46256.0</v>
+        <v>46258.0</v>
       </c>
       <c r="C104" s="1" t="s">
+        <v>332</v>
+      </c>
+      <c r="D104" s="3" t="s">
         <v>333</v>
       </c>
-      <c r="D104" s="3" t="s">
+      <c r="E104" s="1" t="s">
         <v>334</v>
-      </c>
-      <c r="E104" s="1" t="s">
-        <v>50</v>
       </c>
     </row>
     <row r="105">
@@ -3401,7 +3380,7 @@
         <v>115.0</v>
       </c>
       <c r="B105" s="2">
-        <v>46258.0</v>
+        <v>46260.0</v>
       </c>
       <c r="C105" s="1" t="s">
         <v>335</v>
@@ -3410,7 +3389,7 @@
         <v>336</v>
       </c>
       <c r="E105" s="1" t="s">
-        <v>337</v>
+        <v>33</v>
       </c>
     </row>
     <row r="106">
@@ -3421,13 +3400,13 @@
         <v>46260.0</v>
       </c>
       <c r="C106" s="1" t="s">
+        <v>337</v>
+      </c>
+      <c r="D106" s="3" t="s">
         <v>338</v>
       </c>
-      <c r="D106" s="3" t="s">
-        <v>339</v>
-      </c>
       <c r="E106" s="1" t="s">
-        <v>31</v>
+        <v>14</v>
       </c>
     </row>
     <row r="107">
@@ -3435,16 +3414,16 @@
         <v>117.0</v>
       </c>
       <c r="B107" s="2">
-        <v>46260.0</v>
+        <v>46261.0</v>
       </c>
       <c r="C107" s="1" t="s">
+        <v>339</v>
+      </c>
+      <c r="D107" s="3" t="s">
         <v>340</v>
       </c>
-      <c r="D107" s="3" t="s">
-        <v>341</v>
-      </c>
       <c r="E107" s="1" t="s">
-        <v>14</v>
+        <v>50</v>
       </c>
     </row>
     <row r="108">
@@ -3452,16 +3431,16 @@
         <v>118.0</v>
       </c>
       <c r="B108" s="2">
-        <v>46261.0</v>
+        <v>46263.0</v>
       </c>
       <c r="C108" s="1" t="s">
+        <v>341</v>
+      </c>
+      <c r="D108" s="3" t="s">
         <v>342</v>
       </c>
-      <c r="D108" s="3" t="s">
+      <c r="E108" s="1" t="s">
         <v>343</v>
-      </c>
-      <c r="E108" s="1" t="s">
-        <v>47</v>
       </c>
     </row>
     <row r="109">
@@ -3469,7 +3448,7 @@
         <v>119.0</v>
       </c>
       <c r="B109" s="2">
-        <v>46263.0</v>
+        <v>46264.0</v>
       </c>
       <c r="C109" s="1" t="s">
         <v>344</v>
@@ -3477,64 +3456,67 @@
       <c r="D109" s="3" t="s">
         <v>345</v>
       </c>
-      <c r="E109" s="1" t="s">
-        <v>346</v>
-      </c>
+      <c r="E109" s="1"/>
     </row>
     <row r="110">
       <c r="A110" s="1">
         <v>120.0</v>
       </c>
       <c r="B110" s="2">
-        <v>46264.0</v>
+        <v>46266.0</v>
       </c>
       <c r="C110" s="1" t="s">
+        <v>346</v>
+      </c>
+      <c r="D110" s="3" t="s">
         <v>347</v>
       </c>
-      <c r="D110" s="3" t="s">
-        <v>348</v>
-      </c>
-      <c r="E110" s="1"/>
+      <c r="E110" s="1" t="s">
+        <v>14</v>
+      </c>
     </row>
     <row r="111">
       <c r="A111" s="1">
         <v>121.0</v>
       </c>
       <c r="B111" s="2">
-        <v>46266.0</v>
+        <v>46267.0</v>
       </c>
       <c r="C111" s="1" t="s">
+        <v>348</v>
+      </c>
+      <c r="D111" s="1"/>
+      <c r="E111" s="1" t="s">
         <v>349</v>
       </c>
-      <c r="D111" s="3" t="s">
-        <v>350</v>
-      </c>
-      <c r="E111" s="1" t="s">
-        <v>14</v>
-      </c>
+      <c r="F111" s="1"/>
     </row>
     <row r="112">
       <c r="A112" s="1">
         <v>122.0</v>
       </c>
       <c r="B112" s="2">
-        <v>46267.0</v>
+        <v>46268.0</v>
       </c>
       <c r="C112" s="1" t="s">
+        <v>350</v>
+      </c>
+      <c r="D112" s="3" t="s">
         <v>351</v>
       </c>
-      <c r="D112" s="1"/>
       <c r="E112" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="F112" s="1" t="s">
         <v>352</v>
       </c>
-      <c r="F112" s="1"/>
     </row>
     <row r="113">
       <c r="A113" s="1">
         <v>123.0</v>
       </c>
       <c r="B113" s="2">
-        <v>46268.0</v>
+        <v>46269.0</v>
       </c>
       <c r="C113" s="1" t="s">
         <v>353</v>
@@ -3543,10 +3525,7 @@
         <v>354</v>
       </c>
       <c r="E113" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="F113" s="1" t="s">
-        <v>355</v>
+        <v>14</v>
       </c>
     </row>
     <row r="114">
@@ -3554,16 +3533,16 @@
         <v>124.0</v>
       </c>
       <c r="B114" s="2">
-        <v>46269.0</v>
+        <v>46271.0</v>
       </c>
       <c r="C114" s="1" t="s">
+        <v>355</v>
+      </c>
+      <c r="D114" s="3" t="s">
         <v>356</v>
       </c>
-      <c r="D114" s="3" t="s">
-        <v>357</v>
-      </c>
       <c r="E114" s="1" t="s">
-        <v>14</v>
+        <v>349</v>
       </c>
     </row>
     <row r="115">
@@ -3574,13 +3553,13 @@
         <v>46271.0</v>
       </c>
       <c r="C115" s="1" t="s">
+        <v>357</v>
+      </c>
+      <c r="D115" s="3" t="s">
         <v>358</v>
       </c>
-      <c r="D115" s="3" t="s">
-        <v>359</v>
-      </c>
       <c r="E115" s="1" t="s">
-        <v>352</v>
+        <v>183</v>
       </c>
     </row>
     <row r="116">
@@ -3588,16 +3567,16 @@
         <v>126.0</v>
       </c>
       <c r="B116" s="2">
-        <v>46271.0</v>
+        <v>46274.0</v>
       </c>
       <c r="C116" s="1" t="s">
+        <v>359</v>
+      </c>
+      <c r="D116" s="3" t="s">
         <v>360</v>
       </c>
-      <c r="D116" s="3" t="s">
-        <v>361</v>
-      </c>
       <c r="E116" s="1" t="s">
-        <v>183</v>
+        <v>137</v>
       </c>
     </row>
     <row r="117">
@@ -3605,42 +3584,45 @@
         <v>127.0</v>
       </c>
       <c r="B117" s="2">
-        <v>46274.0</v>
+        <v>46281.0</v>
       </c>
       <c r="C117" s="1" t="s">
+        <v>361</v>
+      </c>
+      <c r="D117" s="3" t="s">
         <v>362</v>
       </c>
-      <c r="D117" s="3" t="s">
-        <v>363</v>
-      </c>
-      <c r="E117" s="1" t="s">
-        <v>137</v>
-      </c>
+      <c r="E117" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="F117" s="1"/>
     </row>
     <row r="118">
       <c r="A118" s="1">
         <v>128.0</v>
       </c>
       <c r="B118" s="2">
-        <v>46281.0</v>
+        <v>46282.0</v>
       </c>
       <c r="C118" s="1" t="s">
+        <v>363</v>
+      </c>
+      <c r="D118" s="3" t="s">
         <v>364</v>
       </c>
-      <c r="D118" s="3" t="s">
+      <c r="E118" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="F118" s="1" t="s">
         <v>365</v>
       </c>
-      <c r="E118" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="F118" s="1"/>
     </row>
     <row r="119">
       <c r="A119" s="1">
         <v>129.0</v>
       </c>
       <c r="B119" s="2">
-        <v>46282.0</v>
+        <v>46283.0</v>
       </c>
       <c r="C119" s="1" t="s">
         <v>366</v>
@@ -3660,7 +3642,7 @@
         <v>130.0</v>
       </c>
       <c r="B120" s="2">
-        <v>46283.0</v>
+        <v>46284.0</v>
       </c>
       <c r="C120" s="1" t="s">
         <v>369</v>
@@ -3669,7 +3651,7 @@
         <v>370</v>
       </c>
       <c r="E120" s="1" t="s">
-        <v>133</v>
+        <v>81</v>
       </c>
       <c r="F120" s="1" t="s">
         <v>371</v>
@@ -3680,19 +3662,13 @@
         <v>131.0</v>
       </c>
       <c r="B121" s="2">
-        <v>46284.0</v>
+        <v>46285.0</v>
       </c>
       <c r="C121" s="1" t="s">
         <v>372</v>
       </c>
       <c r="D121" s="3" t="s">
         <v>373</v>
-      </c>
-      <c r="E121" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="F121" s="1" t="s">
-        <v>374</v>
       </c>
     </row>
     <row r="122">
@@ -3700,13 +3676,16 @@
         <v>132.0</v>
       </c>
       <c r="B122" s="2">
-        <v>46285.0</v>
+        <v>46288.0</v>
       </c>
       <c r="C122" s="1" t="s">
+        <v>374</v>
+      </c>
+      <c r="D122" s="3" t="s">
         <v>375</v>
       </c>
-      <c r="D122" s="3" t="s">
-        <v>376</v>
+      <c r="E122" s="1" t="s">
+        <v>160</v>
       </c>
     </row>
     <row r="123">
@@ -3714,16 +3693,19 @@
         <v>133.0</v>
       </c>
       <c r="B123" s="2">
-        <v>46288.0</v>
+        <v>46295.0</v>
       </c>
       <c r="C123" s="1" t="s">
+        <v>376</v>
+      </c>
+      <c r="D123" s="3" t="s">
         <v>377</v>
       </c>
-      <c r="D123" s="3" t="s">
+      <c r="E123" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="F123" s="1" t="s">
         <v>378</v>
-      </c>
-      <c r="E123" s="1" t="s">
-        <v>160</v>
       </c>
     </row>
     <row r="124">
@@ -3740,47 +3722,7 @@
         <v>380</v>
       </c>
       <c r="E124" s="1" t="s">
-        <v>323</v>
-      </c>
-      <c r="F124" s="1" t="s">
         <v>381</v>
-      </c>
-    </row>
-    <row r="125">
-      <c r="A125" s="1">
-        <v>135.0</v>
-      </c>
-      <c r="B125" s="2">
-        <v>46295.0</v>
-      </c>
-      <c r="C125" s="1" t="s">
-        <v>382</v>
-      </c>
-      <c r="D125" s="3" t="s">
-        <v>383</v>
-      </c>
-      <c r="E125" s="1" t="s">
-        <v>133</v>
-      </c>
-      <c r="F125" s="1" t="s">
-        <v>384</v>
-      </c>
-    </row>
-    <row r="126">
-      <c r="A126" s="1">
-        <v>136.0</v>
-      </c>
-      <c r="B126" s="2">
-        <v>46295.0</v>
-      </c>
-      <c r="C126" s="1" t="s">
-        <v>385</v>
-      </c>
-      <c r="D126" s="3" t="s">
-        <v>386</v>
-      </c>
-      <c r="E126" s="1" t="s">
-        <v>387</v>
       </c>
     </row>
   </sheetData>
@@ -3894,7 +3836,7 @@
     <hyperlink r:id="rId107" ref="D108"/>
     <hyperlink r:id="rId108" ref="D109"/>
     <hyperlink r:id="rId109" ref="D110"/>
-    <hyperlink r:id="rId110" ref="D111"/>
+    <hyperlink r:id="rId110" ref="D112"/>
     <hyperlink r:id="rId111" ref="D113"/>
     <hyperlink r:id="rId112" ref="D114"/>
     <hyperlink r:id="rId113" ref="D115"/>
@@ -3907,10 +3849,8 @@
     <hyperlink r:id="rId120" ref="D122"/>
     <hyperlink r:id="rId121" ref="D123"/>
     <hyperlink r:id="rId122" ref="D124"/>
-    <hyperlink r:id="rId123" ref="D125"/>
-    <hyperlink r:id="rId124" ref="D126"/>
   </hyperlinks>
-  <drawing r:id="rId125"/>
+  <drawing r:id="rId123"/>
 </worksheet>
 </file>
 
@@ -4003,16 +3943,16 @@
         <v>46011.0</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="E5" s="1" t="s">
         <v>11</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="6">
@@ -4023,10 +3963,10 @@
         <v>46011.0</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
     </row>
     <row r="7">
@@ -4037,13 +3977,13 @@
         <v>46013.0</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
     </row>
     <row r="8">
@@ -4054,16 +3994,16 @@
         <v>46015.0</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="9">
@@ -4074,13 +4014,13 @@
         <v>46017.0</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
     </row>
     <row r="10">
@@ -4091,13 +4031,13 @@
         <v>46019.0</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
     </row>
     <row r="11">
@@ -4108,13 +4048,13 @@
         <v>46021.0</v>
       </c>
       <c r="C11" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="D11" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="E11" s="1" t="s">
         <v>51</v>
-      </c>
-      <c r="D11" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="E11" s="1" t="s">
-        <v>57</v>
       </c>
     </row>
     <row r="12">
@@ -4125,13 +4065,13 @@
         <v>46022.0</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
     </row>
   </sheetData>

--- a/streams.xlsx
+++ b/streams.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="472" uniqueCount="382">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="472" uniqueCount="383">
   <si>
     <t>id</t>
   </si>
@@ -35,46 +35,64 @@
     <t>note</t>
   </si>
   <si>
+    <t>【 生物名師】幽李鈴</t>
+  </si>
+  <si>
     <t>【幽李鈴】將在12/20 21:00 初配信啦！💗</t>
   </si>
   <si>
+    <t>https://www.youtube.com/watch?v=v0BAHTKUHho</t>
+  </si>
+  <si>
     <t>https://www.youtube.com/watch?v=jd0h91vnRxU</t>
   </si>
   <si>
-    <t>【 生物名師】幽李鈴</t>
-  </si>
-  <si>
-    <t>https://www.youtube.com/watch?v=v0BAHTKUHho</t>
+    <t>Twitch</t>
   </si>
   <si>
     <t>前導</t>
   </si>
   <si>
+    <t>1⧸1 115年 生物老師 幽李鈴 第八節</t>
+  </si>
+  <si>
     <t>【一人捉迷藏】恐怖！直播片段丟失！？</t>
   </si>
   <si>
+    <t>【直播取消】感冒休養跟大家請個假！</t>
+  </si>
+  <si>
     <t>https://www.youtube.com/watch?v=y_6XDNwD-Ks</t>
   </si>
   <si>
-    <t>Twitch</t>
-  </si>
-  <si>
-    <t>1⧸1 115年 生物老師 幽李鈴 第八節</t>
-  </si>
-  <si>
-    <t>【直播取消】感冒休養跟大家請個假！</t>
-  </si>
-  <si>
     <t>https://x.com/U00Vtuber/status/2007422926228689379</t>
   </si>
   <si>
+    <t>X, 直播異動</t>
+  </si>
+  <si>
+    <t>關於今日發生的騷動說明 ft.亞洛赫</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=dUhUhvbywD0</t>
+  </si>
+  <si>
     <t>?????</t>
   </si>
   <si>
     <t>https://www.youtube.com/watch?v=BH_IHRUDy_Q</t>
   </si>
   <si>
-    <t>X, 直播異動</t>
+    <t>直播異動, 連動</t>
+  </si>
+  <si>
+    <t>亞洛赫</t>
+  </si>
+  <si>
+    <t>大便糖速吃...我後悔了</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=v_O4YV6wZtk</t>
   </si>
   <si>
     <t>【神回】直擊！醫院幽靈失蹤事件！</t>
@@ -83,13 +101,13 @@
     <t>https://www.youtube.com/watch?v=d0N94cT487Y</t>
   </si>
   <si>
-    <t>關於今日發生的騷動說明 ft.亞洛赫</t>
-  </si>
-  <si>
-    <t>https://www.youtube.com/watch?v=dUhUhvbywD0</t>
-  </si>
-  <si>
-    <t>亞洛赫</t>
+    <t>QA, 棉花糖</t>
+  </si>
+  <si>
+    <t>【A/S/M/R】嗯哼～♡人家是新手～♡【 NO Sleep /Relax /Whispering】</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=Vp-lbw9r880</t>
   </si>
   <si>
     <t>【初配信】初次見面！！我是幽李鈴！！</t>
@@ -98,22 +116,28 @@
     <t>https://www.youtube.com/watch?v=Yp2QhS2g0tU</t>
   </si>
   <si>
-    <t>直播異動, 連動</t>
-  </si>
-  <si>
-    <t>大便糖速吃...我後悔了</t>
+    <t>ASMR</t>
+  </si>
+  <si>
+    <t>【會員限定】秘密</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=KIAUz5M13wo</t>
   </si>
   <si>
     <t>【後日談QA】治安不好的棉花糖很多呢各位</t>
   </si>
   <si>
-    <t>https://www.youtube.com/watch?v=v_O4YV6wZtk</t>
-  </si>
-  <si>
     <t>https://www.youtube.com/watch?v=kiGVfQRxg5w</t>
   </si>
   <si>
-    <t>QA, 棉花糖</t>
+    <t>會限</t>
+  </si>
+  <si>
+    <t>【觀眾CALL IN】 夾子音醫院聯賽</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=HunY1CF0ezs</t>
   </si>
   <si>
     <t>【聖誕初連動】非誠勿擾，今晚能不能配對成功？ft.亞洛赫</t>
@@ -122,10 +146,16 @@
     <t>https://www.youtube.com/watch?v=G9uRcuHZTdM</t>
   </si>
   <si>
-    <t>【A/S/M/R】嗯哼～♡人家是新手～♡【 NO Sleep /Relax /Whispering】</t>
-  </si>
-  <si>
-    <t>https://www.youtube.com/watch?v=Vp-lbw9r880</t>
+    <t>Twitch, 觀眾CALL IN</t>
+  </si>
+  <si>
+    <t>1⧸15 夾子音醫院聯賽  BO5賽事 CALLIN</t>
+  </si>
+  <si>
+    <t>小朋友們！你們最愛的水毒姐姐來囉！(※手超級會動)</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=0IHJxtZ_8XE</t>
   </si>
   <si>
     <t>連動</t>
@@ -137,6 +167,12 @@
     <t>https://x.com/U00Vtuber/status/2004465037411602451</t>
   </si>
   <si>
+    <t>手語讓觀眾猜出說甚麼才能宣傳新周邊！？(※禁止說話)</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=HMSuYD7A6Pw</t>
+  </si>
+  <si>
     <t>X, 歌回, Twitch</t>
   </si>
   <si>
@@ -146,13 +182,10 @@
     <t>https://www.youtube.com/watch?v=3wkLHKQ5Uqo</t>
   </si>
   <si>
-    <t>ASMR</t>
-  </si>
-  <si>
-    <t>【會員限定】秘密</t>
-  </si>
-  <si>
-    <t>https://www.youtube.com/watch?v=KIAUz5M13wo</t>
+    <t>【觀眾參加型】 賭神降臨</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=GOTc2xgBHq4</t>
   </si>
   <si>
     <t>酒雜</t>
@@ -164,13 +197,19 @@
     <t>https://www.youtube.com/watch?v=3VejobEf1WM</t>
   </si>
   <si>
-    <t>會限</t>
+    <t>Twitch, 直播異動, 觀眾參加型</t>
+  </si>
+  <si>
+    <t>1⧸22 賭賭賭 嘟嘟嘟</t>
+  </si>
+  <si>
+    <t>讓你想起我是護理師</t>
   </si>
   <si>
     <t>觀眾CALL IN</t>
   </si>
   <si>
-    <t>【觀眾CALL IN】 夾子音醫院聯賽</t>
+    <t>https://www.youtube.com/watch?v=Q3ffqBot4OI</t>
   </si>
   <si>
     <t>【會員限定】看沒看到的履歷！！順便跨年啦！！！</t>
@@ -179,54 +218,15 @@
     <t>https://www.youtube.com/watch?v=7LmRg4qqk4M</t>
   </si>
   <si>
-    <t>https://www.youtube.com/watch?v=HunY1CF0ezs</t>
+    <t>Twitch, 直播異動</t>
+  </si>
+  <si>
+    <t>1⧸23 讓大家回想起我是護理師</t>
   </si>
   <si>
     <t>會限, 直播異動</t>
   </si>
   <si>
-    <t>Twitch, 觀眾CALL IN</t>
-  </si>
-  <si>
-    <t>1⧸15 夾子音醫院聯賽  BO5賽事 CALLIN</t>
-  </si>
-  <si>
-    <t>小朋友們！你們最愛的水毒姐姐來囉！(※手超級會動)</t>
-  </si>
-  <si>
-    <t>https://www.youtube.com/watch?v=0IHJxtZ_8XE</t>
-  </si>
-  <si>
-    <t>手語讓觀眾猜出說甚麼才能宣傳新周邊！？(※禁止說話)</t>
-  </si>
-  <si>
-    <t>https://www.youtube.com/watch?v=HMSuYD7A6Pw</t>
-  </si>
-  <si>
-    <t>【觀眾參加型】 賭神降臨</t>
-  </si>
-  <si>
-    <t>https://www.youtube.com/watch?v=GOTc2xgBHq4</t>
-  </si>
-  <si>
-    <t>Twitch, 直播異動, 觀眾參加型</t>
-  </si>
-  <si>
-    <t>1⧸22 賭賭賭 嘟嘟嘟</t>
-  </si>
-  <si>
-    <t>讓你想起我是護理師</t>
-  </si>
-  <si>
-    <t>https://www.youtube.com/watch?v=Q3ffqBot4OI</t>
-  </si>
-  <si>
-    <t>Twitch, 直播異動</t>
-  </si>
-  <si>
-    <t>1⧸23 讓大家回想起我是護理師</t>
-  </si>
-  <si>
     <t>【夜間巡房】滿月慶祝酒雜！一起不醉不歸的時間又到了！！</t>
   </si>
   <si>
@@ -1061,28 +1061,31 @@
     <t>YT禮物測試</t>
   </si>
   <si>
+    <t>歌回, 直式直播, 突發</t>
+  </si>
+  <si>
+    <t>又酒後亂●...！？我們能成為ＣＰ嗎？</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=KfiNmi5OTiM</t>
+  </si>
+  <si>
+    <t>希妮·亞里絲</t>
+  </si>
+  <si>
+    <t>9/4 我找到新工作了 | !指令 !手機殼 !官網</t>
+  </si>
+  <si>
+    <t>https://www.twitch.tv/videos/2864996547</t>
+  </si>
+  <si>
+    <t>初歌回，但是送禮物就亂叫</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=AoREwbnvNbM</t>
+  </si>
+  <si>
     <t>歌回, 直式直播</t>
-  </si>
-  <si>
-    <t>又酒後亂●...！？我們能成為ＣＰ嗎？</t>
-  </si>
-  <si>
-    <t>https://www.youtube.com/watch?v=KfiNmi5OTiM</t>
-  </si>
-  <si>
-    <t>希妮·亞里絲</t>
-  </si>
-  <si>
-    <t>9/4 我找到新工作了 | !指令 !手機殼 !官網</t>
-  </si>
-  <si>
-    <t>https://www.twitch.tv/videos/2864996547</t>
-  </si>
-  <si>
-    <t>初歌回，但是送禮物就亂叫</t>
-  </si>
-  <si>
-    <t>https://www.youtube.com/watch?v=AoREwbnvNbM</t>
   </si>
   <si>
     <t>【幽李鈴】9/6 續攤繼續唱 !指令!手機殼!官網</t>
@@ -1473,16 +1476,16 @@
         <v>46023.0</v>
       </c>
       <c r="C2" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D2" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="D2" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="E2" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="3">
@@ -1493,13 +1496,13 @@
         <v>46025.0</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D3" s="3" t="s">
         <v>17</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
     </row>
     <row r="4">
@@ -1510,16 +1513,16 @@
         <v>46028.0</v>
       </c>
       <c r="C4" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="E4" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="D4" s="3" t="s">
+      <c r="F4" s="1" t="s">
         <v>24</v>
-      </c>
-      <c r="E4" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="F4" s="1" t="s">
-        <v>25</v>
       </c>
     </row>
     <row r="5">
@@ -1530,13 +1533,13 @@
         <v>46030.0</v>
       </c>
       <c r="C5" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E5" s="1" t="s">
         <v>29</v>
-      </c>
-      <c r="D5" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="E5" s="1" t="s">
-        <v>33</v>
       </c>
     </row>
     <row r="6">
@@ -1547,13 +1550,13 @@
         <v>46032.0</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>44</v>
+        <v>34</v>
       </c>
     </row>
     <row r="7">
@@ -1564,13 +1567,13 @@
         <v>46035.0</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>45</v>
+        <v>35</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>50</v>
+        <v>39</v>
       </c>
     </row>
     <row r="8">
@@ -1581,16 +1584,16 @@
         <v>46037.0</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>52</v>
+        <v>40</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>55</v>
+        <v>41</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>57</v>
+        <v>44</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>58</v>
+        <v>45</v>
       </c>
     </row>
     <row r="9">
@@ -1601,10 +1604,10 @@
         <v>46039.0</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>59</v>
+        <v>46</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>60</v>
+        <v>47</v>
       </c>
     </row>
     <row r="10">
@@ -1615,10 +1618,10 @@
         <v>46042.0</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>61</v>
+        <v>51</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>62</v>
+        <v>52</v>
       </c>
     </row>
     <row r="11">
@@ -1629,16 +1632,16 @@
         <v>46044.0</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>63</v>
+        <v>56</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>64</v>
+        <v>57</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
     </row>
     <row r="12">
@@ -1649,16 +1652,16 @@
         <v>46045.0</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="D12" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="E12" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="E12" s="1" t="s">
+      <c r="G12" s="1" t="s">
         <v>69</v>
-      </c>
-      <c r="G12" s="1" t="s">
-        <v>70</v>
       </c>
     </row>
     <row r="13">
@@ -1675,7 +1678,7 @@
         <v>72</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>47</v>
+        <v>58</v>
       </c>
     </row>
     <row r="14">
@@ -1712,7 +1715,7 @@
         <v>78</v>
       </c>
       <c r="E15" s="5" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
     </row>
     <row r="16">
@@ -1769,7 +1772,7 @@
         <v>88</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="G18" s="1" t="s">
         <v>89</v>
@@ -1806,7 +1809,7 @@
         <v>94</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="G20" s="1" t="s">
         <v>95</v>
@@ -1826,7 +1829,7 @@
         <v>97</v>
       </c>
       <c r="E21" s="5" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
     </row>
     <row r="22">
@@ -1843,7 +1846,7 @@
         <v>99</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="G22" s="1" t="s">
         <v>100</v>
@@ -1863,7 +1866,7 @@
         <v>102</v>
       </c>
       <c r="E23" s="5" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
     </row>
     <row r="24">
@@ -1897,7 +1900,7 @@
         <v>107</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="26">
@@ -1914,7 +1917,7 @@
         <v>109</v>
       </c>
       <c r="E26" s="5" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
     </row>
     <row r="27">
@@ -1931,7 +1934,7 @@
         <v>111</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="G27" s="1" t="s">
         <v>112</v>
@@ -1968,7 +1971,7 @@
         <v>117</v>
       </c>
       <c r="E29" s="5" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
     </row>
     <row r="30">
@@ -1985,7 +1988,7 @@
         <v>119</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="G30" s="1" t="s">
         <v>120</v>
@@ -2005,7 +2008,7 @@
         <v>122</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="G31" s="1" t="s">
         <v>123</v>
@@ -2102,7 +2105,7 @@
         <v>140</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="G36" s="1" t="s">
         <v>141</v>
@@ -2142,7 +2145,7 @@
         <v>146</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="G38" s="1" t="s">
         <v>147</v>
@@ -2236,7 +2239,7 @@
         <v>162</v>
       </c>
       <c r="E43" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="G43" s="1" t="s">
         <v>163</v>
@@ -2276,7 +2279,7 @@
         <v>169</v>
       </c>
       <c r="E45" s="1" t="s">
-        <v>47</v>
+        <v>58</v>
       </c>
     </row>
     <row r="46">
@@ -2293,7 +2296,7 @@
         <v>171</v>
       </c>
       <c r="E46" s="5" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
     </row>
     <row r="47">
@@ -2421,7 +2424,7 @@
         <v>191</v>
       </c>
       <c r="E53" s="5" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
     </row>
     <row r="54">
@@ -2438,7 +2441,7 @@
         <v>193</v>
       </c>
       <c r="E54" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="G54" s="1" t="s">
         <v>194</v>
@@ -2492,7 +2495,7 @@
         <v>201</v>
       </c>
       <c r="E57" s="1" t="s">
-        <v>47</v>
+        <v>58</v>
       </c>
     </row>
     <row r="58">
@@ -2549,7 +2552,7 @@
         <v>209</v>
       </c>
       <c r="E60" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="G60" s="1" t="s">
         <v>210</v>
@@ -2569,7 +2572,7 @@
         <v>212</v>
       </c>
       <c r="E61" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="G61" s="1" t="s">
         <v>213</v>
@@ -2592,7 +2595,7 @@
         <v>81</v>
       </c>
       <c r="F62" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="G62" s="1" t="s">
         <v>216</v>
@@ -2692,7 +2695,7 @@
         <v>231</v>
       </c>
       <c r="E67" s="5" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
     </row>
     <row r="68">
@@ -2709,7 +2712,7 @@
         <v>233</v>
       </c>
       <c r="E68" s="5" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
     </row>
     <row r="69">
@@ -2923,7 +2926,7 @@
         <v>268</v>
       </c>
       <c r="E79" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="G79" s="1" t="s">
         <v>269</v>
@@ -3034,7 +3037,7 @@
         <v>286</v>
       </c>
       <c r="E85" s="5" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
     </row>
     <row r="86">
@@ -3051,7 +3054,7 @@
         <v>288</v>
       </c>
       <c r="E86" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="G86" s="1" t="s">
         <v>289</v>
@@ -3122,7 +3125,7 @@
         <v>299</v>
       </c>
       <c r="E90" s="1" t="s">
-        <v>50</v>
+        <v>39</v>
       </c>
     </row>
     <row r="91">
@@ -3159,7 +3162,7 @@
         <v>304</v>
       </c>
       <c r="E92" s="1" t="s">
-        <v>50</v>
+        <v>39</v>
       </c>
     </row>
     <row r="93">
@@ -3230,7 +3233,7 @@
         <v>314</v>
       </c>
       <c r="E96" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="G96" s="1" t="s">
         <v>315</v>
@@ -3321,7 +3324,7 @@
         <v>326</v>
       </c>
       <c r="E101" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
     </row>
     <row r="102">
@@ -3355,7 +3358,7 @@
         <v>331</v>
       </c>
       <c r="E103" s="1" t="s">
-        <v>47</v>
+        <v>58</v>
       </c>
     </row>
     <row r="104">
@@ -3389,7 +3392,7 @@
         <v>336</v>
       </c>
       <c r="E105" s="1" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
     </row>
     <row r="106">
@@ -3406,7 +3409,7 @@
         <v>338</v>
       </c>
       <c r="E106" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
     </row>
     <row r="107">
@@ -3423,7 +3426,7 @@
         <v>340</v>
       </c>
       <c r="E107" s="1" t="s">
-        <v>50</v>
+        <v>39</v>
       </c>
     </row>
     <row r="108">
@@ -3472,7 +3475,7 @@
         <v>347</v>
       </c>
       <c r="E110" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
     </row>
     <row r="111">
@@ -3505,7 +3508,7 @@
         <v>351</v>
       </c>
       <c r="E112" s="1" t="s">
-        <v>38</v>
+        <v>48</v>
       </c>
       <c r="F112" s="1" t="s">
         <v>352</v>
@@ -3525,7 +3528,7 @@
         <v>354</v>
       </c>
       <c r="E113" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
     </row>
     <row r="114">
@@ -3542,7 +3545,7 @@
         <v>356</v>
       </c>
       <c r="E114" s="1" t="s">
-        <v>349</v>
+        <v>357</v>
       </c>
     </row>
     <row r="115">
@@ -3553,10 +3556,10 @@
         <v>46271.0</v>
       </c>
       <c r="C115" s="1" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="D115" s="3" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="E115" s="1" t="s">
         <v>183</v>
@@ -3570,10 +3573,10 @@
         <v>46274.0</v>
       </c>
       <c r="C116" s="1" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="D116" s="3" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="E116" s="1" t="s">
         <v>137</v>
@@ -3587,13 +3590,13 @@
         <v>46281.0</v>
       </c>
       <c r="C117" s="1" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="D117" s="3" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="E117" s="5" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="F117" s="1"/>
     </row>
@@ -3605,16 +3608,16 @@
         <v>46282.0</v>
       </c>
       <c r="C118" s="1" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="D118" s="3" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="E118" s="1" t="s">
         <v>133</v>
       </c>
       <c r="F118" s="1" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
     </row>
     <row r="119">
@@ -3625,16 +3628,16 @@
         <v>46283.0</v>
       </c>
       <c r="C119" s="1" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="D119" s="3" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="E119" s="1" t="s">
         <v>133</v>
       </c>
       <c r="F119" s="1" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
     </row>
     <row r="120">
@@ -3645,16 +3648,16 @@
         <v>46284.0</v>
       </c>
       <c r="C120" s="1" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="D120" s="3" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="E120" s="1" t="s">
         <v>81</v>
       </c>
       <c r="F120" s="1" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
     </row>
     <row r="121">
@@ -3665,10 +3668,10 @@
         <v>46285.0</v>
       </c>
       <c r="C121" s="1" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="D121" s="3" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
     </row>
     <row r="122">
@@ -3679,10 +3682,10 @@
         <v>46288.0</v>
       </c>
       <c r="C122" s="1" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="D122" s="3" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="E122" s="1" t="s">
         <v>160</v>
@@ -3696,16 +3699,16 @@
         <v>46295.0</v>
       </c>
       <c r="C123" s="1" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="D123" s="3" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="E123" s="1" t="s">
         <v>133</v>
       </c>
       <c r="F123" s="1" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
     </row>
     <row r="124">
@@ -3716,13 +3719,13 @@
         <v>46295.0</v>
       </c>
       <c r="C124" s="1" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="D124" s="3" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="E124" s="1" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
     </row>
   </sheetData>
@@ -3892,13 +3895,13 @@
         <v>46000.0</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="3">
@@ -3909,13 +3912,13 @@
         <v>46011.0</v>
       </c>
       <c r="C3" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E3" s="1" t="s">
         <v>12</v>
-      </c>
-      <c r="D3" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>11</v>
       </c>
     </row>
     <row r="4">
@@ -3926,13 +3929,13 @@
         <v>46011.0</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="5">
@@ -3943,16 +3946,16 @@
         <v>46011.0</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="6">
@@ -3963,10 +3966,10 @@
         <v>46011.0</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
     </row>
     <row r="7">
@@ -3977,13 +3980,13 @@
         <v>46013.0</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>30</v>
+        <v>37</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
     </row>
     <row r="8">
@@ -3994,16 +3997,16 @@
         <v>46015.0</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>38</v>
+        <v>48</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="9">
@@ -4014,13 +4017,13 @@
         <v>46017.0</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>39</v>
+        <v>49</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>41</v>
+        <v>53</v>
       </c>
     </row>
     <row r="10">
@@ -4031,13 +4034,13 @@
         <v>46019.0</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>42</v>
+        <v>54</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>43</v>
+        <v>55</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>47</v>
+        <v>58</v>
       </c>
     </row>
     <row r="11">
@@ -4048,13 +4051,13 @@
         <v>46021.0</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>48</v>
+        <v>59</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>49</v>
+        <v>60</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>51</v>
+        <v>64</v>
       </c>
     </row>
     <row r="12">
@@ -4065,13 +4068,13 @@
         <v>46022.0</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>53</v>
+        <v>66</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>54</v>
+        <v>67</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>56</v>
+        <v>70</v>
       </c>
     </row>
   </sheetData>
